--- a/冒险岛.xlsx
+++ b/冒险岛.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyPrograms\BossTimer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25FD4400-BBC5-4D13-9B78-1FE48D26524F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9D8117-680B-407B-80E2-FDB8357CBF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-36135" yWindow="465" windowWidth="28995" windowHeight="20115" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32055" yWindow="690" windowWidth="28995" windowHeight="20115" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="盈利比" sheetId="4" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="196">
   <si>
     <t>卷概率</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -628,9 +628,6 @@
     <t>工地手套+7G</t>
   </si>
   <si>
-    <t>工地手套+8G</t>
-  </si>
-  <si>
     <t>攻击</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -837,6 +834,18 @@
   </si>
   <si>
     <t>鳄鱼大乱斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Link</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第5天</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -956,6 +965,41 @@
     <dxf>
       <font>
         <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
         <family val="3"/>
         <charset val="134"/>
       </font>
@@ -1018,41 +1062,6 @@
         <scheme val="minor"/>
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -3093,23 +3102,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>72</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>123638</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>171406</xdr:rowOff>
+      <xdr:colOff>494987</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>47568</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1">
+        <xdr:cNvPr id="7" name="图片 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{93CA43B5-2D26-DB3B-9D83-8FD934B3F517}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D3106FA-550D-16E0-2EA4-3E1747D47909}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3125,52 +3134,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12258675" y="13030200"/>
-          <a:ext cx="1495238" cy="352381"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>455861</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>133101</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B8E1F9F-D054-54E3-21C2-61D4326407EF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6800850" y="7372350"/>
-          <a:ext cx="10714286" cy="1990476"/>
+          <a:off x="11620500" y="10629900"/>
+          <a:ext cx="2504762" cy="457143"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3448,8 +3413,8 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{2379A92D-1113-45ED-A8A4-AAAB3DC71906}" name="攻击表" displayName="攻击表" ref="D26:E32" totalsRowCount="1">
-  <autoFilter ref="D26:E31" xr:uid="{453710CF-D8F7-433B-9269-A34A821A80FA}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{2379A92D-1113-45ED-A8A4-AAAB3DC71906}" name="攻击表" displayName="攻击表" ref="D26:E33" totalsRowCount="1">
+  <autoFilter ref="D26:E32" xr:uid="{453710CF-D8F7-433B-9269-A34A821A80FA}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
@@ -3464,8 +3429,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BE2FFAE1-2AEB-45EB-B34C-6FFADA37B88A}" name="伤害计算" displayName="伤害计算" ref="D38:E46" totalsRowShown="0">
-  <autoFilter ref="D38:E46" xr:uid="{0542DBDB-921E-4262-A38E-4EE365BD29C8}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BE2FFAE1-2AEB-45EB-B34C-6FFADA37B88A}" name="伤害计算" displayName="伤害计算" ref="D39:E47" totalsRowShown="0">
+  <autoFilter ref="D39:E47" xr:uid="{0542DBDB-921E-4262-A38E-4EE365BD29C8}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
   </autoFilter>
@@ -3536,44 +3501,44 @@
     <tableColumn id="1" xr3:uid="{5D631460-1878-4992-B4F1-C11DD2022B97}" name="攻击" dataDxfId="10">
       <calculatedColumnFormula>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="9"/>
-    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="8"/>
-    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="7">
+    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="1"/>
+    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="0"/>
+    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="9">
       <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="6">
+    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="8">
       <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="攻击max" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="攻击max" dataDxfId="7">
       <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="攻击min" dataDxfId="4">
+    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="攻击min" dataDxfId="6">
       <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="3">
+    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="5">
       <calculatedColumnFormula array="1">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="2">
+    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="4">
       <calculatedColumnFormula array="1">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{CDE151F5-6122-4088-B163-44E497C31795}" name="实际伤害max" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{CDE151F5-6122-4088-B163-44E497C31795}" name="实际伤害max" dataDxfId="3">
       <calculatedColumnFormula array="1">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{16FD9281-FFFB-49BE-B43A-61A44174EE38}" name="实际伤害min" dataDxfId="0">
+    <tableColumn id="9" xr3:uid="{16FD9281-FFFB-49BE-B43A-61A44174EE38}" name="实际伤害min" dataDxfId="2">
       <calculatedColumnFormula array="1">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3648,8 +3613,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}" name="表5" displayName="表5" ref="E32:L64" totalsRowShown="0">
-  <autoFilter ref="E32:L64" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}" name="表5" displayName="表5" ref="E32:L66" totalsRowShown="0">
+  <autoFilter ref="E32:L66" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4188,7 +4153,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>116</v>
@@ -4196,32 +4161,32 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
-        <v>0.24310000000000001</v>
+        <v>0.2225</v>
       </c>
       <c r="C6">
         <f>金价表[[#This Row],[当前金价1w]]/0.95</f>
-        <v>0.25589473684210529</v>
+        <v>0.23421052631578948</v>
       </c>
       <c r="D6" s="5">
-        <v>34.880000000000003</v>
+        <v>3088</v>
       </c>
       <c r="E6">
         <f>金价表[[#This Row],[出售商品价格]]*金价表[[#This Row],[当前金价1w]]*0.95</f>
-        <v>8.0553615999999995</v>
+        <v>652.726</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I8" cm="1">
         <f t="array" ref="I8">555*金价表[税后金价]</f>
-        <v>142.02157894736843</v>
+        <v>129.98684210526315</v>
       </c>
       <c r="J8" cm="1">
         <f t="array" ref="J8">2888.8888*金价表[当前金价1w]</f>
-        <v>702.28886728000009</v>
+        <v>642.77775800000006</v>
       </c>
       <c r="K8" cm="1">
         <f t="array" ref="K8">2888.8888*金价表[当前金价1w]</f>
-        <v>702.28886728000009</v>
+        <v>642.77775800000006</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -4261,7 +4226,7 @@
       </c>
       <c r="L13" s="3" cm="1">
         <f t="array" ref="L13">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>59.879368421052639</v>
+        <v>54.805263157894736</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -4285,14 +4250,14 @@
       </c>
       <c r="L14" s="3" cm="1">
         <f t="array" ref="L14">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>142.16360052631578</v>
+        <v>130.11682894736842</v>
       </c>
       <c r="M14" s="3">
         <v>1</v>
       </c>
       <c r="N14" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>82.284232105263129</v>
+        <v>75.31156578947369</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
@@ -4309,14 +4274,14 @@
       </c>
       <c r="L15" s="3" cm="1">
         <f t="array" ref="L15">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>253.05143924210526</v>
+        <v>231.60816631578948</v>
       </c>
       <c r="M15" s="3">
         <v>2</v>
       </c>
       <c r="N15" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>96.586035410526307</v>
+        <v>88.401451578947373</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
@@ -4333,14 +4298,14 @@
       </c>
       <c r="L16" s="3" cm="1">
         <f t="array" ref="L16">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>380.99880766315789</v>
+        <v>348.71342947368419</v>
       </c>
       <c r="M16" s="3">
         <v>3</v>
       </c>
       <c r="N16" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>107.03981308070176</v>
+        <v>97.969388771929815</v>
       </c>
     </row>
     <row r="17" spans="8:20" x14ac:dyDescent="0.2">
@@ -4357,14 +4322,14 @@
       </c>
       <c r="L17" cm="1">
         <f t="array" ref="L17">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>435.02105263157898</v>
+        <v>398.15789473684214</v>
       </c>
       <c r="M17">
         <v>4</v>
       </c>
       <c r="N17" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>93.785421052631591</v>
+        <v>85.838157894736852</v>
       </c>
     </row>
     <row r="18" spans="8:20" x14ac:dyDescent="0.2">
@@ -4381,14 +4346,14 @@
       </c>
       <c r="L18" cm="1">
         <f t="array" ref="L18">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>767.68421052631584</v>
+        <v>702.63157894736844</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>141.56096842105265</v>
+        <v>129.56526315789475</v>
       </c>
       <c r="Q18">
         <f>555.555+98</f>
@@ -4396,7 +4361,7 @@
       </c>
       <c r="R18" s="1" cm="1">
         <f t="array" ref="R18">Q18*金价表[当前金价1w]</f>
-        <v>158.8792205</v>
+        <v>145.4159875</v>
       </c>
     </row>
     <row r="19" spans="8:20" x14ac:dyDescent="0.2">
@@ -4413,19 +4378,19 @@
       </c>
       <c r="L19" cm="1">
         <f t="array" ref="L19">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>764.84091292631592</v>
+        <v>700.02921894736846</v>
       </c>
       <c r="M19">
         <v>6</v>
       </c>
       <c r="N19" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>117.49359075087722</v>
+        <v>107.53732596491228</v>
       </c>
     </row>
     <row r="20" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H20" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="I20" s="2">
         <v>8000</v>
@@ -4437,19 +4402,19 @@
       </c>
       <c r="L20" cm="1">
         <f t="array" ref="L20">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>2047.1578947368423</v>
+        <v>1873.6842105263158</v>
       </c>
       <c r="M20">
         <v>7</v>
       </c>
       <c r="N20" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>283.8969323308271</v>
+        <v>259.83984962406015</v>
       </c>
     </row>
     <row r="21" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H21" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I21" s="2">
         <v>2666</v>
@@ -4464,7 +4429,7 @@
       </c>
       <c r="L21" cm="1">
         <f t="array" ref="L21">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>682.21536842105274</v>
+        <v>624.40526315789475</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -4476,7 +4441,7 @@
     </row>
     <row r="22" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H22" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I22" s="2">
         <v>2888</v>
@@ -4491,19 +4456,19 @@
       </c>
       <c r="L22" cm="1">
         <f t="array" ref="L22">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>739.02400000000011</v>
+        <v>676.4</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>56.80863157894737</v>
+        <v>51.994736842105226</v>
       </c>
     </row>
     <row r="23" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H23" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2">
         <v>7777</v>
@@ -4518,13 +4483,13 @@
       </c>
       <c r="L23" cm="1">
         <f t="array" ref="L23">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1990.0933684210529</v>
+        <v>1821.4552631578947</v>
       </c>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H24" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2">
@@ -4537,19 +4502,19 @@
       </c>
       <c r="L24" cm="1">
         <f t="array" ref="L24">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1289.1692287157896</v>
+        <v>1179.926587368421</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
       <c r="N24" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>303.47693014736842</v>
+        <v>277.76066210526312</v>
       </c>
     </row>
     <row r="25" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H25" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -4566,21 +4531,21 @@
       </c>
       <c r="N25" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-227.40512280701759</v>
+        <v>-208.13508771929824</v>
       </c>
       <c r="Q25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="R25" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="S25" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -4597,7 +4562,7 @@
       </c>
       <c r="N26" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-170.55384210526319</v>
+        <v>-156.10131578947369</v>
       </c>
       <c r="Q26">
         <v>200</v>
@@ -4612,7 +4577,7 @@
     </row>
     <row r="27" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -4629,7 +4594,7 @@
       </c>
       <c r="N27" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-136.44307368421056</v>
+        <v>-124.88105263157895</v>
       </c>
       <c r="R27" s="1">
         <f>SUM(Q26:S26)</f>
@@ -4637,12 +4602,12 @@
       </c>
       <c r="T27" cm="1">
         <f t="array" ref="T27">R27/金价表[税后金价]</f>
-        <v>1254.4220485396954</v>
+        <v>1370.5617977528088</v>
       </c>
     </row>
     <row r="28" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H28" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -4659,12 +4624,12 @@
       </c>
       <c r="N28" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-97.45933834586468</v>
+        <v>-89.200751879699254</v>
       </c>
     </row>
     <row r="29" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H29" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -4681,22 +4646,22 @@
       </c>
       <c r="N29" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-85.276921052631593</v>
+        <v>-78.050657894736844</v>
       </c>
       <c r="Q29" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="R29">
         <f>4*140</f>
         <v>560</v>
       </c>
       <c r="S29" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H30" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -4713,10 +4678,10 @@
       </c>
       <c r="N30" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-75.801707602339192</v>
+        <v>-69.378362573099423</v>
       </c>
       <c r="Q30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="R30" s="1">
         <f>L28-R29</f>
@@ -4737,7 +4702,7 @@
       </c>
       <c r="L31" cm="1">
         <f t="array" ref="L31">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>60.39115789473685</v>
+        <v>55.273684210526319</v>
       </c>
     </row>
     <row r="32" spans="8:20" x14ac:dyDescent="0.2">
@@ -4754,7 +4719,7 @@
       </c>
       <c r="L32" cm="1">
         <f t="array" ref="L32">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>98.775368421052647</v>
+        <v>90.405263157894737</v>
       </c>
       <c r="R32">
         <f>2200/0.35</f>
@@ -4775,7 +4740,7 @@
       </c>
       <c r="L33" cm="1">
         <f t="array" ref="L33">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>29.172000000000004</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="34" spans="8:17" x14ac:dyDescent="0.2">
@@ -4792,7 +4757,7 @@
       </c>
       <c r="L34" cm="1">
         <f t="array" ref="L34">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>83.421684210526323</v>
+        <v>76.352631578947367</v>
       </c>
     </row>
     <row r="41" spans="8:17" x14ac:dyDescent="0.2">
@@ -4870,7 +4835,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
@@ -5312,7 +5277,7 @@
         <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>
@@ -6050,7 +6015,7 @@
         <v>46.844999999999999</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F47" s="2">
         <v>53</v>
@@ -6102,7 +6067,7 @@
         <v>51.042000000000002</v>
       </c>
       <c r="E48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F48" s="2">
         <v>55</v>
@@ -6141,7 +6106,7 @@
         <v>12.3568</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>47</v>
       </c>
@@ -6153,7 +6118,7 @@
         <v>55.567999999999998</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F49" s="2">
         <v>56</v>
@@ -6193,7 +6158,7 @@
         <v>25.019500000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>48</v>
       </c>
@@ -6205,7 +6170,7 @@
         <v>60.441600000000001</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F50" s="2">
         <v>59</v>
@@ -6245,7 +6210,7 @@
         <v>29.929388888888887</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>49</v>
       </c>
@@ -6257,7 +6222,7 @@
         <v>65.52</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F51" s="2">
         <v>61</v>
@@ -6297,7 +6262,7 @@
         <v>24.320122222222221</v>
       </c>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>50</v>
       </c>
@@ -6309,7 +6274,7 @@
         <v>70.971599999999995</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F52" s="2">
         <v>70</v>
@@ -6349,7 +6314,7 @@
         <v>26.075022357723583</v>
       </c>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>51</v>
       </c>
@@ -6361,7 +6326,7 @@
         <v>74.860799999999998</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F53" s="2">
         <v>70</v>
@@ -6401,7 +6366,7 @@
         <v>26.2879</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>52</v>
       </c>
@@ -6413,7 +6378,7 @@
         <v>78.963099999999997</v>
       </c>
       <c r="E54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F54" s="2">
         <v>71</v>
@@ -6452,7 +6417,7 @@
         <v>22.258258064516131</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>53</v>
       </c>
@@ -6464,7 +6429,7 @@
         <v>83.290199999999999</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F55" s="2">
         <v>71</v>
@@ -6503,8 +6468,11 @@
 /10000</f>
         <v>28.725629999999999</v>
       </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="S55" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>54</v>
       </c>
@@ -6516,7 +6484,7 @@
         <v>87.854500000000002</v>
       </c>
       <c r="E56" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F56" s="2">
         <v>73</v>
@@ -6555,7 +6523,7 @@
         <v>28.186536585365854</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>55</v>
       </c>
@@ -6567,7 +6535,7 @@
         <v>92.668899999999994</v>
       </c>
       <c r="E57" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F57" s="2">
         <v>21</v>
@@ -6606,7 +6574,7 @@
         <v>4.5727500000000001</v>
       </c>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>56</v>
       </c>
@@ -6618,7 +6586,7 @@
         <v>97.747100000000003</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F58" s="2">
         <v>73</v>
@@ -6657,7 +6625,7 @@
         <v>25.477480000000003</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>57</v>
       </c>
@@ -6669,7 +6637,7 @@
         <v>103.1036</v>
       </c>
       <c r="E59" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F59" s="2">
         <v>73</v>
@@ -6708,7 +6676,7 @@
         <v>26.0138</v>
       </c>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>58</v>
       </c>
@@ -6720,7 +6688,7 @@
         <v>108.75360000000001</v>
       </c>
       <c r="E60" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F60" s="2">
         <v>74</v>
@@ -6759,7 +6727,7 @@
         <v>30.158571428571431</v>
       </c>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>59</v>
       </c>
@@ -6771,7 +6739,7 @@
         <v>114.7132</v>
       </c>
       <c r="E61" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F61" s="2">
         <v>74</v>
@@ -6810,7 +6778,7 @@
         <v>30.140369747899157</v>
       </c>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>60</v>
       </c>
@@ -6822,7 +6790,7 @@
         <v>120.99939999999999</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F62" s="2">
         <v>74</v>
@@ -6862,7 +6830,7 @@
         <v>24.602250000000002</v>
       </c>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>61</v>
       </c>
@@ -6874,7 +6842,7 @@
         <v>127.6301</v>
       </c>
       <c r="E63" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F63" s="2">
         <v>75</v>
@@ -6888,7 +6856,7 @@
       <c r="I63" s="2">
         <v>2141632</v>
       </c>
-      <c r="J63" s="10">
+      <c r="J63" s="2">
         <f>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -6901,7 +6869,7 @@
       <c r="K63">
         <v>16</v>
       </c>
-      <c r="L63" s="11">
+      <c r="L63">
         <f>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -6913,7 +6881,7 @@
         <v>25.361999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>62</v>
       </c>
@@ -6925,7 +6893,7 @@
         <v>134.6242</v>
       </c>
       <c r="E64" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F64" s="2">
         <v>75</v>
@@ -6939,7 +6907,7 @@
       <c r="I64" s="2">
         <v>1000000</v>
       </c>
-      <c r="J64" s="10">
+      <c r="J64" s="2">
         <f>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -6953,7 +6921,7 @@
         <f>9*60</f>
         <v>540</v>
       </c>
-      <c r="L64" s="11">
+      <c r="L64">
         <f>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -6965,7 +6933,7 @@
         <v>27.614433333333331</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>63</v>
       </c>
@@ -6976,8 +6944,47 @@
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>142.0016</v>
       </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E65" t="s">
+        <v>178</v>
+      </c>
+      <c r="F65" s="2">
+        <v>77</v>
+      </c>
+      <c r="G65" s="2">
+        <v>1439018</v>
+      </c>
+      <c r="H65" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" s="2">
+        <v>1584954</v>
+      </c>
+      <c r="J65" s="10">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>14.5936</v>
+      </c>
+      <c r="K65">
+        <v>30.5</v>
+      </c>
+      <c r="L65" s="11">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>28.708721311475408</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>64</v>
       </c>
@@ -6988,8 +6995,48 @@
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>149.78319999999999</v>
       </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E66" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F66" s="2">
+        <v>77</v>
+      </c>
+      <c r="G66" s="2">
+        <v>2996910</v>
+      </c>
+      <c r="H66" s="2">
+        <v>80</v>
+      </c>
+      <c r="I66" s="2">
+        <v>0</v>
+      </c>
+      <c r="J66" s="10">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>649.55100000000004</v>
+      </c>
+      <c r="K66">
+        <f>24*60</f>
+        <v>1440</v>
+      </c>
+      <c r="L66" s="11">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>27.064624999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>65</v>
       </c>
@@ -7001,7 +7048,7 @@
         <v>157.9913</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>66</v>
       </c>
@@ -7013,7 +7060,7 @@
         <v>166.64920000000001</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>67</v>
       </c>
@@ -7025,7 +7072,7 @@
         <v>175.78149999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>68</v>
       </c>
@@ -7037,7 +7084,7 @@
         <v>185.4143</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>69</v>
       </c>
@@ -7049,7 +7096,7 @@
         <v>195.57499999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>70</v>
       </c>
@@ -7061,7 +7108,7 @@
         <v>206.29249999999999</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>71</v>
       </c>
@@ -7073,7 +7120,7 @@
         <v>217.59729999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>72</v>
       </c>
@@ -7085,7 +7132,7 @@
         <v>229.52160000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>73</v>
       </c>
@@ -7097,7 +7144,7 @@
         <v>242.0993</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>74</v>
       </c>
@@ -7109,7 +7156,7 @@
         <v>255.3663</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>75</v>
       </c>
@@ -7121,7 +7168,7 @@
         <v>269.3603</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>76</v>
       </c>
@@ -7133,7 +7180,7 @@
         <v>284.12119999999999</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>77</v>
       </c>
@@ -7145,7 +7192,7 @@
         <v>299.69099999999997</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>78</v>
       </c>
@@ -7473,7 +7520,7 @@
       </c>
       <c r="E4" cm="1">
         <f t="array" ref="E4">卷轴参数[[#This Row],[卷拍卖行价w]]*金价表[税后金价]</f>
-        <v>28.14842105263158</v>
+        <v>25.763157894736842</v>
       </c>
     </row>
     <row r="6" spans="2:29" x14ac:dyDescent="0.2">
@@ -7549,7 +7596,7 @@
       </c>
       <c r="D11" cm="1">
         <f t="array" ref="D11">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>361.99101147931532</v>
+        <v>331.31633095083367</v>
       </c>
     </row>
     <row r="12" spans="2:29" x14ac:dyDescent="0.2">
@@ -7562,7 +7609,7 @@
       </c>
       <c r="D12" cm="1">
         <f t="array" ref="D12">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>120.66367049310523</v>
+        <v>110.43877698361132</v>
       </c>
     </row>
     <row r="13" spans="2:29" x14ac:dyDescent="0.2">
@@ -7575,7 +7622,7 @@
       </c>
       <c r="D13" cm="1">
         <f t="array" ref="D13">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>67.035372496169572</v>
+        <v>61.354876102006294</v>
       </c>
     </row>
     <row r="14" spans="2:29" x14ac:dyDescent="0.2">
@@ -7588,7 +7635,7 @@
       </c>
       <c r="D14" cm="1">
         <f t="array" ref="D14">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>47.381022444936598</v>
+        <v>43.366011904559414</v>
       </c>
     </row>
     <row r="15" spans="2:29" x14ac:dyDescent="0.2">
@@ -7601,7 +7648,7 @@
       </c>
       <c r="D15" cm="1">
         <f t="array" ref="D15">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>38.379030055058905</v>
+        <v>35.126837462980696</v>
       </c>
       <c r="Q15" t="s">
         <v>0</v>
@@ -7653,7 +7700,7 @@
       </c>
       <c r="D16" cm="1">
         <f t="array" ref="D16">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>33.760763747063635</v>
+        <v>30.899917456691316</v>
       </c>
       <c r="Q16" s="6">
         <v>0.1</v>
@@ -7672,12 +7719,12 @@
       </c>
       <c r="V16" cm="1">
         <f t="array" ref="V16">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>4.8620000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="W16">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>9.7240000000000002</v>
+        <v>8.9</v>
       </c>
       <c r="X16" s="2">
         <v>6</v>
@@ -7691,16 +7738,16 @@
       </c>
       <c r="AA16">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
-        <v>29.172000000000001</v>
+        <v>26.700000000000003</v>
       </c>
       <c r="AB16">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
-        <v>145.86000000000001</v>
+        <v>133.5</v>
       </c>
       <c r="AC16">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
-        <v>1840.5047318611953</v>
+        <v>1684.5425867507856</v>
       </c>
     </row>
     <row r="17" spans="17:29" x14ac:dyDescent="0.2">
@@ -7719,12 +7766,12 @@
       </c>
       <c r="V17" cm="1">
         <f t="array" ref="V17">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>35.057578947368427</v>
+        <v>32.086842105263159</v>
       </c>
       <c r="W17">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>29.214649122807025</v>
+        <v>26.739035087719301</v>
       </c>
       <c r="X17" s="2">
         <v>0</v>
@@ -7765,12 +7812,12 @@
       </c>
       <c r="V18" cm="1">
         <f t="array" ref="V18">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>0.89563157894736856</v>
+        <v>0.81973684210526321</v>
       </c>
       <c r="W18">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>0.89563157894736856</v>
+        <v>0.81973684210526321</v>
       </c>
       <c r="X18" s="2">
         <v>4</v>
@@ -7785,16 +7832,16 @@
       </c>
       <c r="AA18">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
-        <v>3.5825263157894742</v>
+        <v>3.2789473684210528</v>
       </c>
       <c r="AB18">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
-        <v>3.5825263157894742</v>
+        <v>3.2789473684210528</v>
       </c>
       <c r="AC18">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
-        <v>3.5825263157894742</v>
+        <v>3.2789473684210528</v>
       </c>
     </row>
     <row r="19" spans="17:29" x14ac:dyDescent="0.2">
@@ -7809,11 +7856,11 @@
       </c>
       <c r="AA19">
         <f>SUM(表7[成本造价])</f>
-        <v>32.754526315789477</v>
+        <v>29.978947368421057</v>
       </c>
       <c r="AB19">
         <f>SUM(表7[总价格])</f>
-        <v>149.44252631578948</v>
+        <v>136.77894736842106</v>
       </c>
       <c r="AC19" t="e">
         <f>SUM(表7[风险造价])</f>
@@ -7876,12 +7923,12 @@
       </c>
       <c r="V27" cm="1">
         <f t="array" ref="V27">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>4.8620000000000001</v>
+        <v>4.45</v>
       </c>
       <c r="W27">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>9.7240000000000002</v>
+        <v>8.9</v>
       </c>
       <c r="X27" s="2">
         <v>7</v>
@@ -7895,12 +7942,12 @@
       </c>
       <c r="AA27">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
-        <v>34.033999999999999</v>
+        <v>31.150000000000002</v>
       </c>
       <c r="AB27">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
-        <v>378.49094058346179</v>
+        <v>346.41807601736014</v>
       </c>
     </row>
     <row r="28" spans="17:29" x14ac:dyDescent="0.2">
@@ -7919,12 +7966,12 @@
       </c>
       <c r="V28" cm="1">
         <f t="array" ref="V28">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>35.057578947368427</v>
+        <v>32.086842105263159</v>
       </c>
       <c r="W28">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>29.214649122807025</v>
+        <v>26.739035087719301</v>
       </c>
       <c r="X28" s="2">
         <v>3</v>
@@ -7938,12 +7985,12 @@
       </c>
       <c r="AA28">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
-        <v>105.17273684210528</v>
+        <v>96.260526315789477</v>
       </c>
       <c r="AB28">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
-        <v>135.25300519818069</v>
+        <v>123.7918291098116</v>
       </c>
     </row>
     <row r="29" spans="17:29" x14ac:dyDescent="0.2">
@@ -7960,12 +8007,12 @@
       </c>
       <c r="V29" cm="1">
         <f t="array" ref="V29">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>0.89563157894736856</v>
+        <v>0.81973684210526321</v>
       </c>
       <c r="W29">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>0.89563157894736856</v>
+        <v>0.81973684210526321</v>
       </c>
       <c r="X29" s="2">
         <v>0</v>
@@ -8000,11 +8047,11 @@
       </c>
       <c r="AA30">
         <f>SUM(表7_9[造价])</f>
-        <v>139.20673684210527</v>
+        <v>127.41052631578948</v>
       </c>
       <c r="AB30">
         <f>SUM(表7_9[风险造价])</f>
-        <v>513.74394578164242</v>
+        <v>470.20990512717174</v>
       </c>
     </row>
   </sheetData>
@@ -8022,7 +8069,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C898E4F5-1983-43C5-86AB-660F992C424E}">
-  <dimension ref="B2:W46"/>
+  <dimension ref="B2:W47"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="17.25" customWidth="1"/>
@@ -8079,10 +8126,10 @@
         <v>107</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>167</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>67</v>
@@ -8220,7 +8267,7 @@
         <v>79</v>
       </c>
       <c r="E27">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="4:23" x14ac:dyDescent="0.2">
@@ -8248,20 +8295,19 @@
     </row>
     <row r="32" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D32" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="E32">
-        <f>SUM(攻击表[值])</f>
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="K32" t="s">
         <v>111</v>
       </c>
       <c r="L32" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M32" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N32" t="s">
         <v>110</v>
@@ -8270,10 +8316,10 @@
         <v>38</v>
       </c>
       <c r="P32" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q32" t="s">
         <v>164</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>165</v>
       </c>
       <c r="R32" t="s">
         <v>108</v>
@@ -8295,6 +8341,13 @@
       </c>
     </row>
     <row r="33" spans="4:23" x14ac:dyDescent="0.2">
+      <c r="D33" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33">
+        <f>SUM(攻击表[值])</f>
+        <v>69</v>
+      </c>
       <c r="K33" s="8" t="s">
         <v>112</v>
       </c>
@@ -8303,13 +8356,13 @@
       </c>
       <c r="M33" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N33" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O33" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P33" cm="1">
         <f t="array" ref="P33">表15[[#This Row],[攻击]]
@@ -8317,7 +8370,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>773.76</v>
+        <v>919.63199999999995</v>
       </c>
       <c r="Q33" cm="1">
         <f t="array" ref="Q33">表15[[#This Row],[攻击]]
@@ -8325,37 +8378,37 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>450.50880000000006</v>
+        <v>533.41967999999997</v>
       </c>
       <c r="R33" cm="1">
         <f t="array" ref="R33">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>976</v>
+        <v>1166.0999999999999</v>
       </c>
       <c r="S33" cm="1">
         <f t="array" ref="S33">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>326.39999999999998</v>
+        <v>351.9</v>
       </c>
       <c r="T33" cm="1">
         <f t="array" ref="T33">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2440</v>
+        <v>2915.25</v>
       </c>
       <c r="U33" cm="1">
         <f t="array" ref="U33">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>816</v>
+        <v>879.75</v>
       </c>
       <c r="V33" s="1" cm="1">
         <f t="array" ref="V33">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>1986</v>
+        <v>2413.7249999999999</v>
       </c>
       <c r="W33" s="1" cm="1">
         <f t="array" ref="W33">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>482.4</v>
+        <v>539.77499999999998</v>
       </c>
     </row>
     <row r="34" spans="4:23" x14ac:dyDescent="0.2">
@@ -8367,13 +8420,13 @@
       </c>
       <c r="M34" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N34" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O34" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P34" cm="1">
         <f t="array" ref="P34">表15[[#This Row],[攻击]]
@@ -8381,7 +8434,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>785.85</v>
+        <v>932.96</v>
       </c>
       <c r="Q34" cm="1">
         <f t="array" ref="Q34">表15[[#This Row],[攻击]]
@@ -8389,37 +8442,37 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>457.548</v>
+        <v>541.15039999999999</v>
       </c>
       <c r="R34" cm="1">
         <f t="array" ref="R34">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>991.25</v>
+        <v>1183</v>
       </c>
       <c r="S34" cm="1">
         <f t="array" ref="S34">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>331.5</v>
+        <v>357</v>
       </c>
       <c r="T34" cm="1">
         <f t="array" ref="T34">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2478.125</v>
+        <v>2957.5</v>
       </c>
       <c r="U34" cm="1">
         <f t="array" ref="U34">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>828.75</v>
+        <v>892.5</v>
       </c>
       <c r="V34" s="1" cm="1">
         <f t="array" ref="V34">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2020.3125</v>
+        <v>2451.75</v>
       </c>
       <c r="W34" s="1" cm="1">
         <f t="array" ref="W34">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>493.875</v>
+        <v>551.25</v>
       </c>
     </row>
     <row r="35" spans="4:23" x14ac:dyDescent="0.2">
@@ -8431,13 +8484,13 @@
       </c>
       <c r="M35" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N35" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O35" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P35" cm="1">
         <f t="array" ref="P35">表15[[#This Row],[攻击]]
@@ -8445,7 +8498,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>797.94</v>
+        <v>946.28800000000001</v>
       </c>
       <c r="Q35" cm="1">
         <f t="array" ref="Q35">表15[[#This Row],[攻击]]
@@ -8453,37 +8506,37 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>464.5872</v>
+        <v>548.88112000000001</v>
       </c>
       <c r="R35" cm="1">
         <f t="array" ref="R35">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>1006.5</v>
+        <v>1199.9000000000001</v>
       </c>
       <c r="S35" cm="1">
         <f t="array" ref="S35">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>336.6</v>
+        <v>362.1</v>
       </c>
       <c r="T35" cm="1">
         <f t="array" ref="T35">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2516.25</v>
+        <v>2999.75</v>
       </c>
       <c r="U35" cm="1">
         <f t="array" ref="U35">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>841.5</v>
+        <v>905.25</v>
       </c>
       <c r="V35" s="1" cm="1">
         <f t="array" ref="V35">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2054.625</v>
+        <v>2489.7750000000001</v>
       </c>
       <c r="W35" s="1" cm="1">
         <f t="array" ref="W35">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>505.35</v>
+        <v>562.72500000000002</v>
       </c>
     </row>
     <row r="36" spans="4:23" x14ac:dyDescent="0.2">
@@ -8495,13 +8548,13 @@
       </c>
       <c r="M36" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="N36" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O36" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P36" cm="1">
         <f t="array" ref="P36">表15[[#This Row],[攻击]]
@@ -8509,7 +8562,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>810.03</v>
+        <v>959.61599999999987</v>
       </c>
       <c r="Q36" cm="1">
         <f t="array" ref="Q36">表15[[#This Row],[攻击]]
@@ -8517,43 +8570,40 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>471.62640000000005</v>
+        <v>556.61184000000003</v>
       </c>
       <c r="R36" cm="1">
         <f t="array" ref="R36">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>1021.75</v>
+        <v>1216.8</v>
       </c>
       <c r="S36" cm="1">
         <f t="array" ref="S36">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>341.7</v>
+        <v>367.2</v>
       </c>
       <c r="T36" cm="1">
         <f t="array" ref="T36">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2554.375</v>
+        <v>3042</v>
       </c>
       <c r="U36" cm="1">
         <f t="array" ref="U36">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>854.25</v>
+        <v>918</v>
       </c>
       <c r="V36" s="1" cm="1">
         <f t="array" ref="V36">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2088.9375</v>
+        <v>2527.8000000000002</v>
       </c>
       <c r="W36" s="1" cm="1">
         <f t="array" ref="W36">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>516.82500000000005</v>
+        <v>574.20000000000005</v>
       </c>
     </row>
     <row r="37" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D37" t="s">
-        <v>85</v>
-      </c>
       <c r="K37" s="8" t="s">
         <v>134</v>
       </c>
@@ -8562,13 +8612,13 @@
       </c>
       <c r="M37" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="N37" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O37" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P37" cm="1">
         <f t="array" ref="P37">表15[[#This Row],[攻击]]
@@ -8576,7 +8626,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>822.12</v>
+        <v>972.94399999999996</v>
       </c>
       <c r="Q37" cm="1">
         <f t="array" ref="Q37">表15[[#This Row],[攻击]]
@@ -8584,45 +8634,42 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>478.66560000000004</v>
+        <v>564.34256000000005</v>
       </c>
       <c r="R37" cm="1">
         <f t="array" ref="R37">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>1037</v>
+        <v>1233.7</v>
       </c>
       <c r="S37" cm="1">
         <f t="array" ref="S37">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>346.8</v>
+        <v>372.3</v>
       </c>
       <c r="T37" cm="1">
         <f t="array" ref="T37">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2592.5</v>
+        <v>3084.25</v>
       </c>
       <c r="U37" cm="1">
         <f t="array" ref="U37">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>867</v>
+        <v>930.75</v>
       </c>
       <c r="V37" s="1" cm="1">
         <f t="array" ref="V37">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2123.25</v>
+        <v>2565.8250000000003</v>
       </c>
       <c r="W37" s="1" cm="1">
         <f t="array" ref="W37">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>528.30000000000007</v>
+        <v>585.67500000000007</v>
       </c>
     </row>
     <row r="38" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D38" t="s">
-        <v>86</v>
-      </c>
-      <c r="E38" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="K38" s="8" t="s">
         <v>135</v>
@@ -8632,13 +8679,13 @@
       </c>
       <c r="M38" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="N38" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O38" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P38" cm="1">
         <f t="array" ref="P38">表15[[#This Row],[攻击]]
@@ -8646,7 +8693,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>834.21</v>
+        <v>986.27199999999993</v>
       </c>
       <c r="Q38" cm="1">
         <f t="array" ref="Q38">表15[[#This Row],[攻击]]
@@ -8654,47 +8701,45 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>485.70480000000003</v>
+        <v>572.07328000000007</v>
       </c>
       <c r="R38" cm="1">
         <f t="array" ref="R38">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>1052.25</v>
+        <v>1250.5999999999999</v>
       </c>
       <c r="S38" cm="1">
         <f t="array" ref="S38">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>351.9</v>
+        <v>377.4</v>
       </c>
       <c r="T38" cm="1">
         <f t="array" ref="T38">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2630.625</v>
+        <v>3126.5</v>
       </c>
       <c r="U38" cm="1">
         <f t="array" ref="U38">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>879.75</v>
+        <v>943.5</v>
       </c>
       <c r="V38" s="1" cm="1">
         <f t="array" ref="V38">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2157.5625</v>
+        <v>2603.85</v>
       </c>
       <c r="W38" s="1" cm="1">
         <f t="array" ref="W38">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>539.77499999999998</v>
+        <v>597.15</v>
       </c>
     </row>
     <row r="39" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D39" t="s">
-        <v>87</v>
-      </c>
-      <c r="E39" cm="1">
-        <f t="array" ref="E39">攻击表[[#Totals],[值]]
-*(1+(属性表[运气]*常量表[主属性系数]+SUM(属性表[力量],属性表[敏捷])*常量表[面板副属性系数])/100)</f>
-        <v>773.76</v>
+        <v>86</v>
+      </c>
+      <c r="E39" t="s">
+        <v>78</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>136</v>
@@ -8704,13 +8749,13 @@
       </c>
       <c r="M39" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N39" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O39" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P39" cm="1">
         <f t="array" ref="P39">表15[[#This Row],[攻击]]
@@ -8718,7 +8763,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>846.3</v>
+        <v>999.6</v>
       </c>
       <c r="Q39" cm="1">
         <f t="array" ref="Q39">表15[[#This Row],[攻击]]
@@ -8726,47 +8771,47 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>492.74400000000009</v>
+        <v>579.80399999999997</v>
       </c>
       <c r="R39" cm="1">
         <f t="array" ref="R39">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>1067.5</v>
+        <v>1267.5</v>
       </c>
       <c r="S39" cm="1">
         <f t="array" ref="S39">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>357</v>
+        <v>382.5</v>
       </c>
       <c r="T39" cm="1">
         <f t="array" ref="T39">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2668.75</v>
+        <v>3168.75</v>
       </c>
       <c r="U39" cm="1">
         <f t="array" ref="U39">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>892.5</v>
+        <v>956.25</v>
       </c>
       <c r="V39" s="1" cm="1">
         <f t="array" ref="V39">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2191.875</v>
+        <v>2641.875</v>
       </c>
       <c r="W39" s="1" cm="1">
         <f t="array" ref="W39">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>551.25</v>
+        <v>608.625</v>
       </c>
     </row>
     <row r="40" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D40" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E40" cm="1">
         <f t="array" ref="E40">攻击表[[#Totals],[值]]
-*(常量表[伤害下限系数]+(属性表[运气]*常量表[主属性系数]*常量表[熟练度系数]+SUM(属性表[力量],属性表[敏捷])*常量表[面板副属性系数])/100)</f>
-        <v>447.87200000000001</v>
+*(1+(属性表[运气]*常量表[主属性系数]+SUM(属性表[力量],属性表[敏捷])*常量表[面板副属性系数])/100)</f>
+        <v>834.21</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>137</v>
@@ -8776,13 +8821,13 @@
       </c>
       <c r="M40" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N40" s="2">
-        <v>305</v>
+        <v>338</v>
       </c>
       <c r="O40" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="P40" s="1" cm="1">
         <f t="array" ref="P40">表15[[#This Row],[攻击]]
@@ -8790,7 +8835,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>858.39</v>
+        <v>1012.928</v>
       </c>
       <c r="Q40" s="1" cm="1">
         <f t="array" ref="Q40">表15[[#This Row],[攻击]]
@@ -8798,153 +8843,163 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>499.78320000000008</v>
+        <v>587.53471999999999</v>
       </c>
       <c r="R40" s="1" cm="1">
         <f t="array" ref="R40">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>1082.75</v>
+        <v>1284.4000000000001</v>
       </c>
       <c r="S40" s="1" cm="1">
         <f t="array" ref="S40">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>362.1</v>
+        <v>387.6</v>
       </c>
       <c r="T40" s="1" cm="1">
         <f t="array" ref="T40">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2706.875</v>
+        <v>3211</v>
       </c>
       <c r="U40" s="1" cm="1">
         <f t="array" ref="U40">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>905.25</v>
+        <v>969</v>
       </c>
       <c r="V40" s="1" cm="1">
         <f t="array" ref="V40">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2226.1875</v>
+        <v>2679.9</v>
       </c>
       <c r="W40" s="1" cm="1">
         <f t="array" ref="W40">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>562.72500000000002</v>
+        <v>620.1</v>
       </c>
     </row>
     <row r="41" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D41" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E41" cm="1">
-        <f t="array" ref="E41">E39*常量表[技能倍率]</f>
-        <v>1160.6399999999999</v>
+        <f t="array" ref="E41">攻击表[[#Totals],[值]]
+*(常量表[伤害下限系数]+(属性表[运气]*常量表[主属性系数]*常量表[熟练度系数]+SUM(属性表[力量],属性表[敏捷])*常量表[面板副属性系数])/100)</f>
+        <v>482.86200000000002</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L41" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M41" s="2">
         <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="N41" s="2">
-        <v>305</v>
+        <v>343</v>
       </c>
       <c r="O41" s="2">
-        <v>105</v>
-      </c>
-      <c r="P41" cm="1">
+        <v>104</v>
+      </c>
+      <c r="P41" s="1" cm="1">
         <f t="array" ref="P41">表15[[#This Row],[攻击]]
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>870.48</v>
-      </c>
-      <c r="Q41" cm="1">
+        <v>1008.6</v>
+      </c>
+      <c r="Q41" s="1" cm="1">
         <f t="array" ref="Q41">表15[[#This Row],[攻击]]
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>506.82240000000007</v>
-      </c>
-      <c r="R41" cm="1">
+        <v>582.59400000000005</v>
+      </c>
+      <c r="R41" s="1" cm="1">
         <f t="array" ref="R41">表15[[#This Row],[攻击]]
 *(
  常量表[主属性系数]*表15[[#This Row],[运气]]
 )/100</f>
-        <v>1098</v>
-      </c>
-      <c r="S41" cm="1">
+        <v>1286.25</v>
+      </c>
+      <c r="S41" s="1" cm="1">
         <f t="array" ref="S41">表15[[#This Row],[攻击]]
 *(
  0.5*常量表[主属性系数]*属性表[运气]
 )/100</f>
-        <v>367.2</v>
-      </c>
-      <c r="T41" cm="1">
+        <v>382.5</v>
+      </c>
+      <c r="T41" s="1" cm="1">
         <f t="array" ref="T41">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2745</v>
-      </c>
-      <c r="U41" cm="1">
+        <v>3215.625</v>
+      </c>
+      <c r="U41" s="1" cm="1">
         <f t="array" ref="U41">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>918</v>
+        <v>956.25</v>
       </c>
       <c r="V41" s="1" cm="1">
         <f t="array" ref="V41">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2260.5</v>
+        <v>2684.0625</v>
       </c>
       <c r="W41" s="1" cm="1">
         <f t="array" ref="W41">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>574.20000000000005</v>
+        <v>608.625</v>
       </c>
     </row>
     <row r="42" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D42" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E42" cm="1">
         <f t="array" ref="E42">E40*常量表[技能倍率]</f>
-        <v>671.80799999999999</v>
+        <v>1251.3150000000001</v>
       </c>
     </row>
     <row r="43" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D43" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="E43" cm="1">
-        <f t="array" ref="E43">E41*常量表[暴击倍率]</f>
-        <v>1160.6399999999999</v>
+        <f t="array" ref="E43">E41*常量表[技能倍率]</f>
+        <v>724.29300000000001</v>
       </c>
     </row>
     <row r="44" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D44" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E44" cm="1">
         <f t="array" ref="E44">E42*常量表[暴击倍率]</f>
-        <v>671.80799999999999</v>
+        <v>1251.3150000000001</v>
       </c>
     </row>
     <row r="45" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D45" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E45" cm="1">
-        <f t="array" ref="E45">E43*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>834.57600000000002</v>
+        <f t="array" ref="E45">E43*常量表[暴击倍率]</f>
+        <v>724.29300000000001</v>
       </c>
     </row>
     <row r="46" spans="4:23" x14ac:dyDescent="0.2">
       <c r="D46" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" cm="1">
+        <f t="array" ref="E46">E44*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>916.18350000000009</v>
+      </c>
+    </row>
+    <row r="47" spans="4:23" x14ac:dyDescent="0.2">
+      <c r="D47" t="s">
         <v>105</v>
       </c>
-      <c r="E46" cm="1">
-        <f t="array" ref="E46">E44*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>352.62720000000002</v>
+      <c r="E47" cm="1">
+        <f t="array" ref="E47">E45*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>399.86369999999999</v>
       </c>
     </row>
   </sheetData>
@@ -8973,62 +9028,62 @@
   <sheetData>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" t="s">
         <v>168</v>
-      </c>
-      <c r="D4" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" t="s">
         <v>174</v>
-      </c>
-      <c r="C5" t="s">
-        <v>171</v>
-      </c>
-      <c r="D5" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D6" t="s">
         <v>174</v>
-      </c>
-      <c r="C6" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" t="s">
         <v>174</v>
-      </c>
-      <c r="C7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D7" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -9050,7 +9105,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="105" spans="7:15" x14ac:dyDescent="0.2">
@@ -9058,7 +9113,7 @@
         <v>2</v>
       </c>
       <c r="H105" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="106" spans="7:15" x14ac:dyDescent="0.2">
@@ -9066,7 +9121,7 @@
         <v>3</v>
       </c>
       <c r="H106" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="107" spans="7:15" x14ac:dyDescent="0.2">
@@ -9074,7 +9129,7 @@
         <v>31</v>
       </c>
       <c r="O107" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="108" spans="7:15" x14ac:dyDescent="0.2">
@@ -9082,7 +9137,7 @@
         <v>32</v>
       </c>
       <c r="O108" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109" spans="7:15" x14ac:dyDescent="0.2">
@@ -9090,13 +9145,13 @@
         <v>19</v>
       </c>
       <c r="H109" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N109">
         <v>33</v>
       </c>
       <c r="O109" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="110" spans="7:15" x14ac:dyDescent="0.2">
@@ -9104,13 +9159,13 @@
         <v>23</v>
       </c>
       <c r="H110" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="N110">
         <v>36</v>
       </c>
       <c r="O110" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="111" spans="7:15" x14ac:dyDescent="0.2">
@@ -9118,7 +9173,7 @@
         <v>39</v>
       </c>
       <c r="O111" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="112" spans="7:15" x14ac:dyDescent="0.2">
@@ -9126,7 +9181,7 @@
         <v>41</v>
       </c>
       <c r="O112" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="113" spans="14:15" x14ac:dyDescent="0.2">
@@ -9134,7 +9189,7 @@
         <v>54</v>
       </c>
       <c r="O113" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/冒险岛.xlsx
+++ b/冒险岛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyPrograms\BossTimer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\BossTimer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D9D8117-680B-407B-80E2-FDB8357CBF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCDECB5-6CCE-4202-85F6-B49101714D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32055" yWindow="690" windowWidth="28995" windowHeight="20115" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-33660" yWindow="2970" windowWidth="30090" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="盈利比" sheetId="4" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="181">
   <si>
     <t>卷概率</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -362,490 +362,438 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>主属性系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>熟练度系数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>属性表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>力量</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>敏捷</t>
+    <t>MAX = TotalWATK × (1.0 + (LUK × 2.5 + STR + DEX) / 100 + AttackPower / 50)</t>
+  </si>
+  <si>
+    <t>MIN = TotalWATK × (0.8 + (LUK × M × 2.5 + STR + DEX) / 100 + AttackPower / 50)</t>
+  </si>
+  <si>
+    <t>技能倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击倍率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击几率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害min</t>
+  </si>
+  <si>
+    <t>暴击伤害max</t>
+  </si>
+  <si>
+    <t>怪物防御</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怪物参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>min系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实际伤害max</t>
+  </si>
+  <si>
+    <t>实际伤害min</t>
+  </si>
+  <si>
+    <t>等级差</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害下限系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等价rmb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工地手套+6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>提升</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>每点提升价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工地手套+7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工地手套+5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工地手套+2</t>
+  </si>
+  <si>
+    <t>工地手套+3</t>
+  </si>
+  <si>
+    <t>工地手套+4</t>
+  </si>
+  <si>
+    <t>购买价格w</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制作价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套攻击卷轴10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套攻击卷轴60%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工地手套+8</t>
+  </si>
+  <si>
+    <t>差价（含税）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳套攻击卷轴10%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳套攻击卷轴60%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>工地手套+9</t>
+  </si>
+  <si>
+    <t>代练 2026/8/16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗迹2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>出售商品价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比40攻便宜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卷轴成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳套成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成品价格</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>去掉卷轴成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100卷成本</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无魂蘑菇王</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代练 2026/8/18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳套+43</t>
+  </si>
+  <si>
+    <t>拳套+44</t>
+  </si>
+  <si>
+    <t>拳套+45</t>
+  </si>
+  <si>
+    <t>拳套+46</t>
+  </si>
+  <si>
+    <t>代练 2026/8/19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>总经验(万)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>代练 2026/8/20</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级所需(万)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有人蹲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有眼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>有眼x2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面板max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面板min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面板主属性系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>面板副属性系数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Boss</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/找人 神罗天正</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/找人 三千雷幻身</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/找人 关你吊事</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝙蝠怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>扫线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/找人 UUUD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/找人 油炸派大星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>70_80预估</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰冷的摇篮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>拳套+47</t>
+  </si>
+  <si>
+    <t>拳套+48</t>
+  </si>
+  <si>
+    <t>拳套+49</t>
+  </si>
+  <si>
+    <t>拳套+50</t>
+  </si>
+  <si>
+    <t>拳套+51</t>
+  </si>
+  <si>
+    <t>拳套+52</t>
+  </si>
+  <si>
+    <t>第1天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第2天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地铁一号线&lt;4&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>月妙</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第3天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨人之森大乱斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第4天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鳄鱼大乱斗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第5天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>智力</t>
-  </si>
-  <si>
-    <t>运气</t>
-  </si>
-  <si>
-    <t>MAX = TotalWATK × (1.0 + (LUK × 2.5 + STR + DEX) / 100 + AttackPower / 50)</t>
-  </si>
-  <si>
-    <t>MIN = TotalWATK × (0.8 + (LUK × M × 2.5 + STR + DEX) / 100 + AttackPower / 50)</t>
-  </si>
-  <si>
-    <t>攻击表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击来源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳套</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>飞镖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手套</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>披风</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>药水</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SUM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害计算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>项目</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击下限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>技能倍率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础伤害min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>基础伤害max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击倍率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击几率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害min</t>
-  </si>
-  <si>
-    <t>暴击伤害min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>暴击伤害max</t>
-  </si>
-  <si>
-    <t>暴击伤害max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物防御</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>怪物参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>min系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>max系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际伤害max</t>
-  </si>
-  <si>
-    <t>实际伤害max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实际伤害min</t>
-  </si>
-  <si>
-    <t>实际伤害min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等级差</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伤害下限系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>攻击min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>运气</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+2G</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+1G</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>商品名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>等价rmb</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提升</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>每点提升价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+7</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+2</t>
-  </si>
-  <si>
-    <t>工地手套+3</t>
-  </si>
-  <si>
-    <t>工地手套+4</t>
-  </si>
-  <si>
-    <t>购买价格w</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>制作价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手套攻击卷轴10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>手套攻击卷轴60%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+8</t>
-  </si>
-  <si>
-    <t>差价（含税）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳套攻击卷轴10%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳套攻击卷轴60%</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+3G</t>
-  </si>
-  <si>
-    <t>工地手套+4G</t>
-  </si>
-  <si>
-    <t>工地手套+5G</t>
-  </si>
-  <si>
-    <t>工地手套+6G</t>
-  </si>
-  <si>
-    <t>工地手套+7G</t>
-  </si>
-  <si>
-    <t>攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>额外攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>工地手套+9</t>
-  </si>
-  <si>
-    <t>代练 2026/8/16</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>遗迹2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>出售商品价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比40攻便宜</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>卷轴成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳套成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成品价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>去掉卷轴成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100卷成本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>无魂蘑菇王</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>代练 2026/8/18</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳套+43</t>
-  </si>
-  <si>
-    <t>拳套+44</t>
-  </si>
-  <si>
-    <t>拳套+45</t>
-  </si>
-  <si>
-    <t>拳套+46</t>
-  </si>
-  <si>
-    <t>代练 2026/8/19</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总经验(万)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>代练 2026/8/20</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>升级所需(万)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有人蹲</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有眼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>有眼x2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>面板max</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>面板min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>面板主属性系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>面板副属性系数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 神罗天正</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 三千雷幻身</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 关你吊事</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蝙蝠怪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扫线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 UUUD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 油炸派大星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>70_80预估</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>冰冷的摇篮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>拳套+47</t>
-  </si>
-  <si>
-    <t>拳套+48</t>
-  </si>
-  <si>
-    <t>拳套+49</t>
-  </si>
-  <si>
-    <t>拳套+50</t>
-  </si>
-  <si>
-    <t>拳套+51</t>
-  </si>
-  <si>
-    <t>拳套+52</t>
-  </si>
-  <si>
-    <t>第1天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第2天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>地铁一号线&lt;4&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>月妙</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第3天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>巨人之森大乱斗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第4天</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鳄鱼大乱斗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Link</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>第5天</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武器攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>飞镖攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Link攻击</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双飞斩max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双飞斩min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双飞斩运气系数min</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>双飞斩运气系数max</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套+1G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套+2G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套+3G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无手套</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套+4G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套+5G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套+6G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>手套+7G</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏刀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力刀60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力刀70</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -853,7 +801,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -919,6 +867,15 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -940,7 +897,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -955,48 +912,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="58">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
+  <dxfs count="63">
     <dxf>
       <font>
         <b/>
@@ -1010,18 +931,6 @@
         <family val="3"/>
         <charset val="134"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1061,12 +970,30 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
         <b/>
         <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1078,6 +1005,141 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
@@ -1113,9 +1175,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1363,12 +1422,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -3151,16 +3204,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>161648</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>161520</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>456923</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>142470</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3183,7 +3236,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6953250" y="3438525"/>
+          <a:off x="20278725" y="3781425"/>
           <a:ext cx="2219048" cy="3238095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3197,6 +3250,143 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>599773</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>142519</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF3FE499-FEB5-AE79-0DBD-9FF3F6165CA1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8410575" y="7791450"/>
+          <a:ext cx="2419048" cy="2847619"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>466421</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>113943</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6496F5E4-B82E-D009-25E8-08C940AB76FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5715000" y="7753350"/>
+          <a:ext cx="2428571" cy="2857143"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>733425</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>113988</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>171098</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="图片 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB9E67B5-49F5-9251-9020-D068D007A6A0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10963275" y="7848600"/>
+          <a:ext cx="2495238" cy="2819048"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -3349,34 +3539,34 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D2F5DA31-758D-4974-A8DB-D862E9E685DC}" name="表7_9" displayName="表7_9" ref="Q26:AB30" totalsRowCount="1">
-  <autoFilter ref="Q26:AB29" xr:uid="{D2F5DA31-758D-4974-A8DB-D862E9E685DC}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{D2F5DA31-758D-4974-A8DB-D862E9E685DC}" name="表7_9" displayName="表7_9" ref="C39:N43" totalsRowCount="1">
+  <autoFilter ref="C39:N42" xr:uid="{D2F5DA31-758D-4974-A8DB-D862E9E685DC}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{C9A11298-FA96-49C6-A3A1-A77A91972722}" name="卷概率"/>
-    <tableColumn id="8" xr3:uid="{BEDD0CAD-6AB0-4C30-A86C-19070711828D}" name="敏捷" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{BEDD0CAD-6AB0-4C30-A86C-19070711828D}" name="敏捷" dataDxfId="31"/>
     <tableColumn id="9" xr3:uid="{DB11AE09-BC1F-400F-8121-26D0BBD40CE3}" name="命中"/>
     <tableColumn id="10" xr3:uid="{419A6181-B2C8-4E1A-BD6F-47425EDBEDC1}" name="移速"/>
-    <tableColumn id="3" xr3:uid="{06987FE9-FC9A-467C-8516-1C8A6991EFD3}" name="单价" dataDxfId="23" totalsRowDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{EC81E847-7526-4094-88CA-6860A893C3B1}" name="rmb" dataDxfId="21">
+    <tableColumn id="3" xr3:uid="{06987FE9-FC9A-467C-8516-1C8A6991EFD3}" name="单价" dataDxfId="30" totalsRowDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{EC81E847-7526-4094-88CA-6860A893C3B1}" name="rmb" dataDxfId="28">
       <calculatedColumnFormula array="1">表7_9[[#This Row],[单价]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{C26F07DB-AA65-4261-A542-9FF829521DAC}" name="敏捷价格" dataDxfId="20">
+    <tableColumn id="7" xr3:uid="{C26F07DB-AA65-4261-A542-9FF829521DAC}" name="敏捷价格" dataDxfId="27">
       <calculatedColumnFormula>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{247B50C8-19A4-4B64-A6C4-FEFA5C146E13}" name="模拟数量" totalsRowFunction="custom" dataDxfId="19">
+    <tableColumn id="11" xr3:uid="{247B50C8-19A4-4B64-A6C4-FEFA5C146E13}" name="模拟数量" totalsRowFunction="custom" dataDxfId="26">
       <totalsRowFormula>SUM(表7_9[模拟数量])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E46A5CC0-4EA5-480B-A804-F448C4FD1200}" name="成功数量" dataDxfId="18"/>
-    <tableColumn id="13" xr3:uid="{4297568D-CFCF-46D6-99EB-6BE373700BA1}" name="总敏捷" totalsRowFunction="custom" dataDxfId="17">
+    <tableColumn id="12" xr3:uid="{E46A5CC0-4EA5-480B-A804-F448C4FD1200}" name="成功数量" dataDxfId="25"/>
+    <tableColumn id="13" xr3:uid="{4297568D-CFCF-46D6-99EB-6BE373700BA1}" name="总敏捷" totalsRowFunction="custom" dataDxfId="24">
       <calculatedColumnFormula>表7_9[[#This Row],[成功数量]]*表7_9[[#This Row],[敏捷]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[总敏捷])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{DF214F81-3AC6-44F7-A044-188A8853DA6B}" name="造价" totalsRowFunction="custom" dataDxfId="16">
+    <tableColumn id="14" xr3:uid="{DF214F81-3AC6-44F7-A044-188A8853DA6B}" name="造价" totalsRowFunction="custom" dataDxfId="23">
       <calculatedColumnFormula>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[造价])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2749CEFB-FAB2-4688-B950-EB889079A869}" name="风险造价" totalsRowFunction="custom" dataDxfId="15">
+    <tableColumn id="15" xr3:uid="{2749CEFB-FAB2-4688-B950-EB889079A869}" name="风险造价" totalsRowFunction="custom" dataDxfId="22">
       <calculatedColumnFormula>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[风险造价])</totalsRowFormula>
@@ -3387,8 +3577,8 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4EBDEB06-9EAF-4C59-8B85-E07E60337705}" name="常量表" displayName="常量表" ref="D8:K9" totalsRowShown="0" headerRowDxfId="14">
-  <autoFilter ref="D8:K9" xr:uid="{1EC169C2-1CE1-41D3-B5C2-AF9DACDA284A}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4EBDEB06-9EAF-4C59-8B85-E07E60337705}" name="常量表" displayName="常量表" ref="D8:L9" totalsRowShown="0" headerRowDxfId="21">
+  <autoFilter ref="D8:L9" xr:uid="{1EC169C2-1CE1-41D3-B5C2-AF9DACDA284A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3397,13 +3587,15 @@
     <filterColumn colId="5" hiddenButton="1"/>
     <filterColumn colId="6" hiddenButton="1"/>
     <filterColumn colId="7" hiddenButton="1"/>
+    <filterColumn colId="8" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="8">
+  <tableColumns count="9">
     <tableColumn id="8" xr3:uid="{02FA7E59-ADA0-406F-B856-E1772F9DECCA}" name="伤害下限系数"/>
     <tableColumn id="7" xr3:uid="{F24798D5-BC76-45A3-818D-0FCECBFED9DC}" name="面板主属性系数"/>
     <tableColumn id="4" xr3:uid="{946824A2-E4E6-4FAF-B63F-6061471C271A}" name="面板副属性系数"/>
-    <tableColumn id="1" xr3:uid="{83F963E2-50F9-4858-B270-A61447FE684F}" name="主属性系数"/>
-    <tableColumn id="5" xr3:uid="{656C8470-9335-4994-8946-E5F9E636C442}" name="熟练度系数"/>
+    <tableColumn id="9" xr3:uid="{506D121F-8A88-467A-82FA-67D094100910}" name="熟练度系数"/>
+    <tableColumn id="1" xr3:uid="{83F963E2-50F9-4858-B270-A61447FE684F}" name="双飞斩运气系数max"/>
+    <tableColumn id="5" xr3:uid="{656C8470-9335-4994-8946-E5F9E636C442}" name="双飞斩运气系数min"/>
     <tableColumn id="2" xr3:uid="{C35B97EA-302A-4601-A83D-3B4AD4CCFA8E}" name="技能倍率"/>
     <tableColumn id="3" xr3:uid="{45514FC8-5C84-4FDB-B8CE-40D6E13ADFDE}" name="暴击倍率"/>
     <tableColumn id="6" xr3:uid="{3AA310F7-56DF-4FAC-AA8E-B454006FB704}" name="暴击几率"/>
@@ -3413,54 +3605,6 @@
 </file>
 
 <file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{2379A92D-1113-45ED-A8A4-AAAB3DC71906}" name="攻击表" displayName="攻击表" ref="D26:E33" totalsRowCount="1">
-  <autoFilter ref="D26:E32" xr:uid="{453710CF-D8F7-433B-9269-A34A821A80FA}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{88DB5370-85B9-418C-B5BC-4FC62F8273A1}" name="攻击来源" totalsRowLabel="SUM"/>
-    <tableColumn id="2" xr3:uid="{587A3648-69A8-4EE4-A281-82858A9FE285}" name="值" totalsRowFunction="custom">
-      <totalsRowFormula>SUM(攻击表[值])</totalsRowFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{BE2FFAE1-2AEB-45EB-B34C-6FFADA37B88A}" name="伤害计算" displayName="伤害计算" ref="D39:E47" totalsRowShown="0">
-  <autoFilter ref="D39:E47" xr:uid="{0542DBDB-921E-4262-A38E-4EE365BD29C8}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{E2E0C8B1-B062-4BE6-BDDF-89282880F2E3}" name="项目"/>
-    <tableColumn id="2" xr3:uid="{884975BD-5290-4348-ABDD-6B0B62491C0C}" name="值" dataDxfId="13"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{5F2BF330-2B0E-4D48-8687-6D194DAC9919}" name="属性表" displayName="属性表" ref="D17:G18" totalsRowShown="0">
-  <autoFilter ref="D17:G18" xr:uid="{4C105FA4-751A-4DE8-9570-1487FDDDB05E}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{8ED8BBA6-73D0-44F1-82FB-9A987F263546}" name="力量"/>
-    <tableColumn id="2" xr3:uid="{4DE31C77-65D3-4281-A0F3-34FCC7BDD158}" name="敏捷"/>
-    <tableColumn id="3" xr3:uid="{7CA5AEB7-5F2A-4B73-B4E9-B8E26E1E2989}" name="智力"/>
-    <tableColumn id="4" xr3:uid="{423E5BD8-5358-4D98-8A5F-58F7FE129015}" name="运气"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="14" xr:uid="{39B4E772-DEE9-473A-837C-3DDDEE94F3D3}" name="怪物参数" displayName="怪物参数" ref="D12:G13" totalsRowShown="0">
   <autoFilter ref="D12:G13" xr:uid="{39B4E772-DEE9-473A-837C-3DDDEE94F3D3}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3474,13 +3618,13 @@
     <tableColumn id="2" xr3:uid="{A169B056-87C0-45D6-9CC1-FC2838D90DAC}" name="min系数"/>
     <tableColumn id="3" xr3:uid="{5A4AA7BB-03D1-4996-8D1C-EE991C9496CB}" name="max系数"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}" name="表15" displayName="表15" ref="K32:W41" totalsRowShown="0">
-  <autoFilter ref="K32:W41" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}">
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}" name="表15" displayName="表15" ref="D25:U37" totalsRowShown="0">
+  <autoFilter ref="D25:U37" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3494,51 +3638,65 @@
     <filterColumn colId="10" hiddenButton="1"/>
     <filterColumn colId="11" hiddenButton="1"/>
     <filterColumn colId="12" hiddenButton="1"/>
+    <filterColumn colId="13" hiddenButton="1"/>
+    <filterColumn colId="14" hiddenButton="1"/>
+    <filterColumn colId="15" hiddenButton="1"/>
+    <filterColumn colId="16" hiddenButton="1"/>
+    <filterColumn colId="17" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="13">
-    <tableColumn id="12" xr3:uid="{E28116B0-6337-4365-A0F6-32D60BC978B6}" name="备注" dataDxfId="12"/>
-    <tableColumn id="13" xr3:uid="{B41CD52A-A98D-4045-A6E3-121E0D0AEF7D}" name="额外攻击" dataDxfId="11"/>
-    <tableColumn id="1" xr3:uid="{5D631460-1878-4992-B4F1-C11DD2022B97}" name="攻击" dataDxfId="10">
-      <calculatedColumnFormula>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="1"/>
-    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="0"/>
-    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="9">
-      <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
+  <tableColumns count="18">
+    <tableColumn id="12" xr3:uid="{E28116B0-6337-4365-A0F6-32D60BC978B6}" name="备注" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{B41CD52A-A98D-4045-A6E3-121E0D0AEF7D}" name="额外攻击" dataDxfId="19"/>
+    <tableColumn id="19" xr3:uid="{7A53DEB6-2117-436A-BF1B-D301DAF6BCEE}" name="武器攻击" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{20152D2D-C68D-446B-8E46-96A7870A92B3}" name="飞镖攻击" dataDxfId="14"/>
+    <tableColumn id="17" xr3:uid="{A88072CD-F8EB-44C3-9C7B-02B153E89A1A}" name="手套攻击" dataDxfId="13"/>
+    <tableColumn id="16" xr3:uid="{D1098DDD-BCA5-4948-A22C-8762851A9BB4}" name="Link攻击" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{1D59A3FA-F5A2-4BF3-8DFD-364A71CE22EE}" name="力量" dataDxfId="8"/>
+    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{85C70B3A-5D87-4857-BD02-D3B80CC6C80E}" name="智力" dataDxfId="6"/>
+    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="4"/>
+    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="5">
+      <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="8">
-      <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
+    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="2">
+      <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="攻击max" dataDxfId="7">
-      <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="双飞斩max" dataDxfId="12">
+      <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="攻击min" dataDxfId="6">
-      <calculatedColumnFormula array="1">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</calculatedColumnFormula>
+    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="双飞斩min" dataDxfId="11">
+      <calculatedColumnFormula array="1">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="5">
-      <calculatedColumnFormula array="1">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
+    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="10">
+      <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="4">
-      <calculatedColumnFormula array="1">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
+    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="9">
+      <calculatedColumnFormula array="1">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{CDE151F5-6122-4088-B163-44E497C31795}" name="实际伤害max" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{CDE151F5-6122-4088-B163-44E497C31795}" name="实际伤害max" dataDxfId="1">
       <calculatedColumnFormula array="1">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{16FD9281-FFFB-49BE-B43A-61A44174EE38}" name="实际伤害min" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{16FD9281-FFFB-49BE-B43A-61A44174EE38}" name="实际伤害min" dataDxfId="0">
       <calculatedColumnFormula array="1">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3546,7 +3704,7 @@
 </table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{C6BEB876-D98A-44E6-96E6-52E2DABA23E5}" name="表17" displayName="表17" ref="B4:D9" totalsRowShown="0">
   <autoFilter ref="B4:D9" xr:uid="{C6BEB876-D98A-44E6-96E6-52E2DABA23E5}">
     <filterColumn colId="0" hiddenButton="1"/>
@@ -3563,7 +3721,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}" name="金价表" displayName="金价表" ref="B5:E6" totalsRowShown="0" headerRowDxfId="50">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}" name="金价表" displayName="金价表" ref="B5:E6" totalsRowShown="0" headerRowDxfId="55">
   <autoFilter ref="B5:E6" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3571,11 +3729,11 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{63ED9EB8-73DB-4AD9-B2A4-1D5B7478467C}" name="当前金价1w" dataDxfId="49"/>
+    <tableColumn id="1" xr3:uid="{63ED9EB8-73DB-4AD9-B2A4-1D5B7478467C}" name="当前金价1w" dataDxfId="54"/>
     <tableColumn id="2" xr3:uid="{D33CA45C-8193-4B2C-8B27-FBAD392BC340}" name="税后金价">
       <calculatedColumnFormula>金价表[[#This Row],[当前金价1w]]/0.95</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{29531BBF-B529-4F64-A29C-03F62C776778}" name="出售商品价格" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{29531BBF-B529-4F64-A29C-03F62C776778}" name="出售商品价格" dataDxfId="53"/>
     <tableColumn id="4" xr3:uid="{35F8F87C-3C60-4850-9D79-EF218F013BD7}" name="等价rmb">
       <calculatedColumnFormula>金价表[[#This Row],[出售商品价格]]*金价表[[#This Row],[当前金价1w]]*0.95</calculatedColumnFormula>
     </tableColumn>
@@ -3585,7 +3743,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}" name="表16" displayName="表16" ref="H12:N34" totalsRowShown="0" headerRowDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}" name="表16" displayName="表16" ref="H12:N34" totalsRowShown="0" headerRowDxfId="52">
   <autoFilter ref="H12:N34" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3596,13 +3754,13 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67FFE6FF-4DC3-4141-9556-C34751EE7C54}" name="商品名称" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{AA234072-647C-4A37-BA00-45785241169C}" name="购买价格w" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{B69C23F2-12E4-49E4-B956-F35FECF6EED2}" name="制作价格" dataDxfId="44"/>
-    <tableColumn id="7" xr3:uid="{1F179FDF-DB5D-4D9E-9382-252E36157465}" name="差价（含税）" dataDxfId="43">
+    <tableColumn id="1" xr3:uid="{67FFE6FF-4DC3-4141-9556-C34751EE7C54}" name="商品名称" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{AA234072-647C-4A37-BA00-45785241169C}" name="购买价格w" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{B69C23F2-12E4-49E4-B956-F35FECF6EED2}" name="制作价格" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{1F179FDF-DB5D-4D9E-9382-252E36157465}" name="差价（含税）" dataDxfId="48">
       <calculatedColumnFormula>IF(表16[[#This Row],[制作价格]]&gt;0,表16[[#This Row],[购买价格w]]*0.95-表16[[#This Row],[制作价格]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8A5E4DE9-C2B5-4A40-BB32-99BB0FFB6D5C}" name="等价rmb" dataDxfId="42">
+    <tableColumn id="3" xr3:uid="{8A5E4DE9-C2B5-4A40-BB32-99BB0FFB6D5C}" name="等价rmb" dataDxfId="47">
       <calculatedColumnFormula array="1">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{DFF8FCC2-0D9D-4B90-A22F-E3039B1304EA}" name="提升"/>
@@ -3626,11 +3784,11 @@
   </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{1845B151-23D6-4795-B6F2-CF21BBF78274}" name="源"/>
-    <tableColumn id="6" xr3:uid="{6745D84B-176D-410B-A732-E68A39D776C3}" name="开始lv" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{EB49316D-EA89-440F-8BED-529A7B30C022}" name="开始" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{D165A06A-4105-4A22-9828-A4BEF84DACDC}" name="结束lv" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{7BC03053-038D-41AD-84CE-B60879A78C44}" name="结束" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{18F6AB19-F5E3-4464-85E9-7510B0FF4FBB}" name="总经验(万)" dataDxfId="53">
+    <tableColumn id="6" xr3:uid="{6745D84B-176D-410B-A732-E68A39D776C3}" name="开始lv" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{EB49316D-EA89-440F-8BED-529A7B30C022}" name="开始" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{D165A06A-4105-4A22-9828-A4BEF84DACDC}" name="结束lv" dataDxfId="60"/>
+    <tableColumn id="3" xr3:uid="{7BC03053-038D-41AD-84CE-B60879A78C44}" name="结束" dataDxfId="59"/>
+    <tableColumn id="8" xr3:uid="{18F6AB19-F5E3-4464-85E9-7510B0FF4FBB}" name="总经验(万)" dataDxfId="58">
       <calculatedColumnFormula>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -3640,7 +3798,7 @@
 /10000</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{14E25966-66F6-42F8-8B80-A23CD832D12D}" name="时间min"/>
-    <tableColumn id="5" xr3:uid="{96A93011-DA20-46D8-8102-FAFE34B717F8}" name="exp/h（万）" dataDxfId="52">
+    <tableColumn id="5" xr3:uid="{96A93011-DA20-46D8-8102-FAFE34B717F8}" name="exp/h（万）" dataDxfId="57">
       <calculatedColumnFormula>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -3665,7 +3823,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C593048-19E0-4739-89F7-550D3BCA4024}" name="等级"/>
     <tableColumn id="2" xr3:uid="{7BF93B33-4DA7-41C2-A05A-738673B7622F}" name="升级所需"/>
-    <tableColumn id="3" xr3:uid="{D469DC4A-2E68-429C-9A30-B15320947E61}" name="升级所需(万)" dataDxfId="51">
+    <tableColumn id="3" xr3:uid="{D469DC4A-2E68-429C-9A30-B15320947E61}" name="升级所需(万)" dataDxfId="56">
       <calculatedColumnFormula>经验表[[#This Row],[升级所需]]/10000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3690,19 +3848,23 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB8998DA-BBB2-46CF-8111-B43AA0A92522}" name="表1" displayName="表1" ref="B6:D16" totalsRowShown="0">
-  <autoFilter ref="B6:D16" xr:uid="{FB8998DA-BBB2-46CF-8111-B43AA0A92522}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{FB8998DA-BBB2-46CF-8111-B43AA0A92522}" name="表1" displayName="表1" ref="B6:E16" totalsRowShown="0">
+  <autoFilter ref="B6:E16" xr:uid="{FB8998DA-BBB2-46CF-8111-B43AA0A92522}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
+    <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="3">
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{698E820D-23C3-4BF8-BEED-4FE313E53471}" name="次数"/>
-    <tableColumn id="2" xr3:uid="{84879E6A-8423-4B05-81FF-8B66F1BA776F}" name="几率" dataDxfId="41">
-      <calculatedColumnFormula array="1">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</calculatedColumnFormula>
+    <tableColumn id="2" xr3:uid="{84879E6A-8423-4B05-81FF-8B66F1BA776F}" name="几率" dataDxfId="18">
+      <calculatedColumnFormula array="1">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7C2768F8-9055-4D23-BE1E-FE8B90B3316B}" name="价值" dataDxfId="40">
-      <calculatedColumnFormula array="1">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</calculatedColumnFormula>
+    <tableColumn id="4" xr3:uid="{E3DE3ED5-E666-48A5-A699-F069DF88052E}" name="成本价" dataDxfId="17">
+      <calculatedColumnFormula array="1">表1[[#This Row],[次数]]*卷轴参数[卷价值]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{7C2768F8-9055-4D23-BE1E-FE8B90B3316B}" name="价值" dataDxfId="16">
+      <calculatedColumnFormula array="1">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -3710,7 +3872,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}" name="卷轴参数" displayName="卷轴参数" ref="B3:E4" totalsRowShown="0" headerRowDxfId="39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}" name="卷轴参数" displayName="卷轴参数" ref="B3:E4" totalsRowShown="0" headerRowDxfId="46">
   <autoFilter ref="B3:E4" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3718,9 +3880,9 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DC107BBC-406B-498C-BD39-B974C0439AFE}" name="卷概率" dataDxfId="38"/>
-    <tableColumn id="2" xr3:uid="{C61182DF-822A-4A58-AE24-69A976436107}" name="预期成功" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{0F00CCD6-E594-41C1-8347-E43384BB99BE}" name="卷拍卖行价w" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{DC107BBC-406B-498C-BD39-B974C0439AFE}" name="卷概率" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{C61182DF-822A-4A58-AE24-69A976436107}" name="预期成功" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{0F00CCD6-E594-41C1-8347-E43384BB99BE}" name="卷拍卖行价w" dataDxfId="43"/>
     <tableColumn id="3" xr3:uid="{C4E5C7A1-FB81-480E-9C73-32F750E3D67C}" name="卷价值">
       <calculatedColumnFormula array="1">卷轴参数[[#This Row],[卷拍卖行价w]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
@@ -3730,8 +3892,8 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1EFEF9C6-D779-41E5-9730-769F54BFE206}" name="表7" displayName="表7" ref="Q15:AC19" totalsRowCount="1">
-  <autoFilter ref="Q15:AC18" xr:uid="{1EFEF9C6-D779-41E5-9730-769F54BFE206}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{1EFEF9C6-D779-41E5-9730-769F54BFE206}" name="表7" displayName="表7" ref="C28:O32" totalsRowCount="1">
+  <autoFilter ref="C28:O31" xr:uid="{1EFEF9C6-D779-41E5-9730-769F54BFE206}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3748,34 +3910,34 @@
   </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{8F08A040-BDE1-42FF-BDBE-7E0E087A8819}" name="卷概率"/>
-    <tableColumn id="8" xr3:uid="{680FF308-0932-4EB2-8486-CA5FEE3FE305}" name="敏捷" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{680FF308-0932-4EB2-8486-CA5FEE3FE305}" name="敏捷" dataDxfId="42"/>
     <tableColumn id="9" xr3:uid="{A70A1698-D188-45CC-BD1C-5EB46D8790A5}" name="命中"/>
     <tableColumn id="10" xr3:uid="{DF40AD0D-56B3-4A4D-8D8F-BCBF9EC1301D}" name="移速"/>
-    <tableColumn id="3" xr3:uid="{A7118FBF-F08B-458A-BB56-4552824BA5FC}" name="单价" dataDxfId="34" totalsRowDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{CA577DD0-7258-45B9-A695-C4171373AE3D}" name="rmb" dataDxfId="32">
+    <tableColumn id="3" xr3:uid="{A7118FBF-F08B-458A-BB56-4552824BA5FC}" name="单价" dataDxfId="41" totalsRowDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{CA577DD0-7258-45B9-A695-C4171373AE3D}" name="rmb" dataDxfId="39">
       <calculatedColumnFormula array="1">表7[[#This Row],[单价]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3BF04BD0-3887-4D5A-9323-13DA842E9180}" name="每点敏捷价格" dataDxfId="31">
+    <tableColumn id="7" xr3:uid="{3BF04BD0-3887-4D5A-9323-13DA842E9180}" name="每点敏捷价格" dataDxfId="38">
       <calculatedColumnFormula>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7B62E845-07A3-42E2-92B2-C00C85BAD066}" name="模拟数量" totalsRowFunction="custom" dataDxfId="30">
+    <tableColumn id="11" xr3:uid="{7B62E845-07A3-42E2-92B2-C00C85BAD066}" name="模拟数量" totalsRowFunction="custom" dataDxfId="37">
       <totalsRowFormula>SUM(表7[模拟数量])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{94F47A8A-0CD2-46BA-BB08-9B69181B3598}" name="成功数量" dataDxfId="29"/>
-    <tableColumn id="13" xr3:uid="{D8FA6D3D-13C9-413D-AA5C-EE25CEB6741F}" name="总敏捷" totalsRowFunction="custom" dataDxfId="28">
+    <tableColumn id="12" xr3:uid="{94F47A8A-0CD2-46BA-BB08-9B69181B3598}" name="成功数量" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{D8FA6D3D-13C9-413D-AA5C-EE25CEB6741F}" name="总敏捷" totalsRowFunction="custom" dataDxfId="35">
       <calculatedColumnFormula>表7[[#This Row],[成功数量]]*表7[[#This Row],[敏捷]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[总敏捷])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{55A7AE7C-6813-49F7-BF22-A6D1331D0893}" name="成本造价" totalsRowFunction="custom" dataDxfId="27">
+    <tableColumn id="14" xr3:uid="{55A7AE7C-6813-49F7-BF22-A6D1331D0893}" name="成本造价" totalsRowFunction="custom" dataDxfId="34">
       <calculatedColumnFormula>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[成本造价])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EE726C5-0F2C-402A-94A6-793B6B1029B8}" name="总价格" totalsRowFunction="custom" dataDxfId="26">
+    <tableColumn id="2" xr3:uid="{7EE726C5-0F2C-402A-94A6-793B6B1029B8}" name="总价格" totalsRowFunction="custom" dataDxfId="33">
       <calculatedColumnFormula>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[总价格])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7DFA1C56-A8FE-42B5-B6C1-2058B28542ED}" name="风险造价" totalsRowFunction="custom" dataDxfId="25">
+    <tableColumn id="15" xr3:uid="{7DFA1C56-A8FE-42B5-B6C1-2058B28542ED}" name="风险造价" totalsRowFunction="custom" dataDxfId="32">
       <calculatedColumnFormula>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[风险造价])</totalsRowFormula>
@@ -4153,10 +4315,10 @@
         <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
@@ -4191,30 +4353,30 @@
     </row>
     <row r="12" spans="2:14" ht="28.5" x14ac:dyDescent="0.2">
       <c r="H12" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
       <c r="H13" s="2" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
       <c r="I13" s="9">
         <v>234</v>
@@ -4238,7 +4400,7 @@
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
       <c r="H14" s="2" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="I14" s="9">
         <v>555.55499999999995</v>
@@ -4262,7 +4424,7 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
       <c r="H15" s="2" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="I15" s="9">
         <v>988.88879999999995</v>
@@ -4286,7 +4448,7 @@
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
       <c r="H16" s="2" t="s">
-        <v>121</v>
+        <v>92</v>
       </c>
       <c r="I16" s="9">
         <v>1488.8887999999999</v>
@@ -4310,7 +4472,7 @@
     </row>
     <row r="17" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="I17" s="2">
         <v>1700</v>
@@ -4334,7 +4496,7 @@
     </row>
     <row r="18" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H18" s="2" t="s">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="I18" s="2">
         <v>3000</v>
@@ -4366,7 +4528,7 @@
     </row>
     <row r="19" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H19" s="2" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="I19" s="2">
         <v>2988.8888000000002</v>
@@ -4390,7 +4552,7 @@
     </row>
     <row r="20" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H20" s="2" t="s">
-        <v>140</v>
+        <v>105</v>
       </c>
       <c r="I20" s="2">
         <v>8000</v>
@@ -4414,7 +4576,7 @@
     </row>
     <row r="21" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H21" s="2" t="s">
-        <v>152</v>
+        <v>117</v>
       </c>
       <c r="I21" s="2">
         <v>2666</v>
@@ -4441,7 +4603,7 @@
     </row>
     <row r="22" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H22" s="2" t="s">
-        <v>153</v>
+        <v>118</v>
       </c>
       <c r="I22" s="2">
         <v>2888</v>
@@ -4468,7 +4630,7 @@
     </row>
     <row r="23" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H23" s="2" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
       <c r="I23" s="2">
         <v>7777</v>
@@ -4489,7 +4651,7 @@
     </row>
     <row r="24" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H24" s="2" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2">
@@ -4514,7 +4676,7 @@
     </row>
     <row r="25" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H25" s="2" t="s">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -4534,18 +4696,18 @@
         <v>-208.13508771929824</v>
       </c>
       <c r="Q25" t="s">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="R25" t="s">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="S25" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H26" s="2" t="s">
-        <v>180</v>
+        <v>145</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -4577,7 +4739,7 @@
     </row>
     <row r="27" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H27" s="2" t="s">
-        <v>181</v>
+        <v>146</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -4607,7 +4769,7 @@
     </row>
     <row r="28" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H28" s="2" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -4629,7 +4791,7 @@
     </row>
     <row r="29" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H29" s="2" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -4649,19 +4811,19 @@
         <v>-78.050657894736844</v>
       </c>
       <c r="Q29" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="R29">
         <f>4*140</f>
         <v>560</v>
       </c>
       <c r="S29" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H30" s="2" t="s">
-        <v>184</v>
+        <v>149</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -4681,7 +4843,7 @@
         <v>-69.378362573099423</v>
       </c>
       <c r="Q30" t="s">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="R30" s="1">
         <f>L28-R29</f>
@@ -4690,7 +4852,7 @@
     </row>
     <row r="31" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H31" s="8" t="s">
-        <v>127</v>
+        <v>98</v>
       </c>
       <c r="I31" s="2">
         <v>236</v>
@@ -4707,7 +4869,7 @@
     </row>
     <row r="32" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H32" s="8" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="I32" s="2">
         <v>386</v>
@@ -4728,7 +4890,7 @@
     </row>
     <row r="33" spans="8:17" x14ac:dyDescent="0.2">
       <c r="H33" s="8" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="I33" s="2">
         <v>114</v>
@@ -4745,7 +4907,7 @@
     </row>
     <row r="34" spans="8:17" x14ac:dyDescent="0.2">
       <c r="H34" s="8" t="s">
-        <v>132</v>
+        <v>103</v>
       </c>
       <c r="I34" s="2">
         <v>326</v>
@@ -4835,7 +4997,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>159</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
@@ -5277,7 +5439,7 @@
         <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>157</v>
+        <v>122</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>
@@ -6015,7 +6177,7 @@
         <v>46.844999999999999</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>141</v>
+        <v>106</v>
       </c>
       <c r="F47" s="2">
         <v>53</v>
@@ -6067,7 +6229,7 @@
         <v>51.042000000000002</v>
       </c>
       <c r="E48" t="s">
-        <v>142</v>
+        <v>107</v>
       </c>
       <c r="F48" s="2">
         <v>55</v>
@@ -6118,7 +6280,7 @@
         <v>55.567999999999998</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="F49" s="2">
         <v>56</v>
@@ -6170,7 +6332,7 @@
         <v>60.441600000000001</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="F50" s="2">
         <v>59</v>
@@ -6222,7 +6384,7 @@
         <v>65.52</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>158</v>
+        <v>123</v>
       </c>
       <c r="F51" s="2">
         <v>61</v>
@@ -6274,7 +6436,7 @@
         <v>70.971599999999995</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>177</v>
+        <v>142</v>
       </c>
       <c r="F52" s="2">
         <v>70</v>
@@ -6326,7 +6488,7 @@
         <v>74.860799999999998</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>185</v>
+        <v>150</v>
       </c>
       <c r="F53" s="2">
         <v>70</v>
@@ -6378,7 +6540,7 @@
         <v>78.963099999999997</v>
       </c>
       <c r="E54" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="F54" s="2">
         <v>71</v>
@@ -6429,7 +6591,7 @@
         <v>83.290199999999999</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="F55" s="2">
         <v>71</v>
@@ -6469,7 +6631,7 @@
         <v>28.725629999999999</v>
       </c>
       <c r="S55" t="s">
-        <v>194</v>
+        <v>158</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
@@ -6484,7 +6646,7 @@
         <v>87.854500000000002</v>
       </c>
       <c r="E56" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="F56" s="2">
         <v>73</v>
@@ -6535,7 +6697,7 @@
         <v>92.668899999999994</v>
       </c>
       <c r="E57" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="F57" s="2">
         <v>21</v>
@@ -6586,7 +6748,7 @@
         <v>97.747100000000003</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>189</v>
+        <v>154</v>
       </c>
       <c r="F58" s="2">
         <v>73</v>
@@ -6637,7 +6799,7 @@
         <v>103.1036</v>
       </c>
       <c r="E59" t="s">
-        <v>190</v>
+        <v>155</v>
       </c>
       <c r="F59" s="2">
         <v>73</v>
@@ -6688,7 +6850,7 @@
         <v>108.75360000000001</v>
       </c>
       <c r="E60" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="F60" s="2">
         <v>74</v>
@@ -6739,7 +6901,7 @@
         <v>114.7132</v>
       </c>
       <c r="E61" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="F61" s="2">
         <v>74</v>
@@ -6790,7 +6952,7 @@
         <v>120.99939999999999</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="F62" s="2">
         <v>74</v>
@@ -6842,7 +7004,7 @@
         <v>127.6301</v>
       </c>
       <c r="E63" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="F63" s="2">
         <v>75</v>
@@ -6893,7 +7055,7 @@
         <v>134.6242</v>
       </c>
       <c r="E64" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="F64" s="2">
         <v>75</v>
@@ -6945,7 +7107,7 @@
         <v>142.0016</v>
       </c>
       <c r="E65" t="s">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="F65" s="2">
         <v>77</v>
@@ -6959,7 +7121,7 @@
       <c r="I65" s="2">
         <v>1584954</v>
       </c>
-      <c r="J65" s="10">
+      <c r="J65" s="2">
         <f>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -6972,7 +7134,7 @@
       <c r="K65">
         <v>30.5</v>
       </c>
-      <c r="L65" s="11">
+      <c r="L65">
         <f>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -6996,7 +7158,7 @@
         <v>149.78319999999999</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>195</v>
+        <v>159</v>
       </c>
       <c r="F66" s="2">
         <v>77</v>
@@ -7010,7 +7172,7 @@
       <c r="I66" s="2">
         <v>0</v>
       </c>
-      <c r="J66" s="10">
+      <c r="J66" s="2">
         <f>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -7024,7 +7186,7 @@
         <f>24*60</f>
         <v>1440</v>
       </c>
-      <c r="L66" s="11">
+      <c r="L66">
         <f>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -7483,18 +7645,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4783B8A4-3AA8-4110-B925-89EB0CBA6491}">
-  <dimension ref="B2:AC30"/>
+  <dimension ref="B2:O43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="2:29" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:5" ht="28.5" x14ac:dyDescent="0.2">
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
@@ -7508,7 +7670,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
         <v>0.6</v>
       </c>
@@ -7516,14 +7678,14 @@
         <v>5</v>
       </c>
       <c r="D4" s="2">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="E4" cm="1">
         <f t="array" ref="E4">卷轴参数[[#This Row],[卷拍卖行价w]]*金价表[税后金价]</f>
-        <v>25.763157894736842</v>
-      </c>
-    </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.2">
+        <v>16.394736842105264</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
         <v>1</v>
       </c>
@@ -7531,525 +7693,572 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E6" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>1</v>
       </c>
-      <c r="C7" t="e" cm="1">
-        <f t="array" ref="C7">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="D7" t="e" cm="1">
-        <f t="array" ref="D7">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="C7" cm="1">
+        <f t="array" ref="C7">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" cm="1">
+        <f t="array" ref="D7">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>16.394736842105264</v>
+      </c>
+      <c r="E7" t="str" cm="1">
+        <f t="array" ref="E7">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>2</v>
       </c>
-      <c r="C8" t="e" cm="1">
-        <f t="array" ref="C8">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="D8" t="e" cm="1">
-        <f t="array" ref="D8">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="C8" cm="1">
+        <f t="array" ref="C8">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D8" cm="1">
+        <f t="array" ref="D8">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>32.789473684210527</v>
+      </c>
+      <c r="E8" t="str" cm="1">
+        <f t="array" ref="E8">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>3</v>
       </c>
-      <c r="C9" t="e" cm="1">
-        <f t="array" ref="C9">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="D9" t="e" cm="1">
-        <f t="array" ref="D9">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>#NUM!</v>
-      </c>
-    </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="C9" cm="1">
+        <f t="array" ref="C9">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D9" cm="1">
+        <f t="array" ref="D9">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>49.184210526315795</v>
+      </c>
+      <c r="E9" t="str" cm="1">
+        <f t="array" ref="E9">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>4</v>
       </c>
       <c r="C10" cm="1">
-        <f t="array" ref="C10">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
+        <f t="array" ref="C10">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
         <v>0</v>
       </c>
-      <c r="D10" t="e" cm="1">
-        <f t="array" ref="D10">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="D10" cm="1">
+        <f t="array" ref="D10">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>65.578947368421055</v>
+      </c>
+      <c r="E10" t="str" cm="1">
+        <f t="array" ref="E10">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>-</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>5</v>
       </c>
       <c r="C11" cm="1">
-        <f t="array" ref="C11">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
+        <f t="array" ref="C11">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
         <v>7.7760000000000051E-2</v>
       </c>
       <c r="D11" cm="1">
-        <f t="array" ref="D11">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>331.31633095083367</v>
-      </c>
-    </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.2">
+        <f t="array" ref="D11">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>81.973684210526315</v>
+      </c>
+      <c r="E11" cm="1">
+        <f t="array" ref="E11">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>1054.1883257526526</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12" cm="1">
-        <f t="array" ref="C12">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
+        <f t="array" ref="C12">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
         <v>0.23327999999999993</v>
       </c>
       <c r="D12" cm="1">
-        <f t="array" ref="D12">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>110.43877698361132</v>
-      </c>
-    </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.2">
+        <f t="array" ref="D12">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>98.368421052631589</v>
+      </c>
+      <c r="E12" cm="1">
+        <f t="array" ref="E12">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>421.67533030106142</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13" cm="1">
-        <f t="array" ref="C13">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
+        <f t="array" ref="C13">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
         <v>0.41990399999999983</v>
       </c>
       <c r="D13" cm="1">
-        <f t="array" ref="D13">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>61.354876102006294</v>
-      </c>
-    </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.2">
+        <f t="array" ref="D13">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>114.76315789473685</v>
+      </c>
+      <c r="E13" cm="1">
+        <f t="array" ref="E13">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>273.30808445439169</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" cm="1">
-        <f t="array" ref="C14">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
+        <f t="array" ref="C14">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
         <v>0.5940863999999999</v>
       </c>
       <c r="D14" cm="1">
-        <f t="array" ref="D14">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>43.366011904559414</v>
-      </c>
-    </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.2">
+        <f t="array" ref="D14">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>131.15789473684211</v>
+      </c>
+      <c r="E14" cm="1">
+        <f t="array" ref="E14">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>220.77242424139337</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>9</v>
       </c>
       <c r="C15" cm="1">
-        <f t="array" ref="C15">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
+        <f t="array" ref="C15">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
         <v>0.73343231999999992</v>
       </c>
       <c r="D15" cm="1">
-        <f t="array" ref="D15">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>35.126837462980696</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>0</v>
-      </c>
-      <c r="R15" t="s">
-        <v>38</v>
-      </c>
-      <c r="S15" t="s">
-        <v>36</v>
-      </c>
-      <c r="T15" t="s">
-        <v>37</v>
-      </c>
-      <c r="U15" t="s">
-        <v>27</v>
-      </c>
-      <c r="V15" t="s">
-        <v>28</v>
-      </c>
-      <c r="W15" t="s">
-        <v>53</v>
-      </c>
-      <c r="X15" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>41</v>
-      </c>
-      <c r="Z15" t="s">
-        <v>40</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="2:29" x14ac:dyDescent="0.2">
+        <f t="array" ref="D15">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>147.55263157894737</v>
+      </c>
+      <c r="E15" cm="1">
+        <f t="array" ref="E15">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>201.18097819707123</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B16">
         <v>10</v>
       </c>
       <c r="C16" cm="1">
-        <f t="array" ref="C16">1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE)</f>
+        <f t="array" ref="C16">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</f>
         <v>0.83376138239999997</v>
       </c>
       <c r="D16" cm="1">
-        <f t="array" ref="D16">1/表1[[#This Row],[几率]]*卷轴参数[卷价值]</f>
-        <v>30.899917456691316</v>
-      </c>
-      <c r="Q16" s="6">
+        <f t="array" ref="D16">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
+        <v>163.94736842105263</v>
+      </c>
+      <c r="E16" cm="1">
+        <f t="array" ref="E16">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
+        <v>196.63583836076293</v>
+      </c>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" t="s">
+        <v>37</v>
+      </c>
+      <c r="G28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H28" t="s">
+        <v>28</v>
+      </c>
+      <c r="I28" t="s">
+        <v>53</v>
+      </c>
+      <c r="J28" t="s">
+        <v>39</v>
+      </c>
+      <c r="K28" t="s">
+        <v>41</v>
+      </c>
+      <c r="L28" t="s">
+        <v>40</v>
+      </c>
+      <c r="M28" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" t="s">
+        <v>54</v>
+      </c>
+      <c r="O28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C29" s="6">
         <v>0.1</v>
       </c>
-      <c r="R16" s="2">
+      <c r="D29" s="2">
         <v>5</v>
       </c>
-      <c r="S16" s="2">
+      <c r="E29" s="2">
         <v>3</v>
       </c>
-      <c r="T16" s="2">
+      <c r="F29" s="2">
         <v>1</v>
       </c>
-      <c r="U16" s="2">
+      <c r="G29" s="2">
         <v>19</v>
       </c>
-      <c r="V16" cm="1">
-        <f t="array" ref="V16">表7[[#This Row],[单价]]*金价表[税后金价]</f>
+      <c r="H29" cm="1">
+        <f t="array" ref="H29">表7[[#This Row],[单价]]*金价表[税后金价]</f>
         <v>4.45</v>
       </c>
-      <c r="W16">
+      <c r="I29">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
         <v>8.9</v>
       </c>
-      <c r="X16" s="2">
+      <c r="J29" s="2">
         <v>6</v>
       </c>
-      <c r="Y16" s="2">
+      <c r="K29" s="2">
         <v>3</v>
       </c>
-      <c r="Z16">
+      <c r="L29">
         <f>表7[[#This Row],[成功数量]]*表7[[#This Row],[敏捷]]</f>
         <v>15</v>
       </c>
-      <c r="AA16">
+      <c r="M29">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
         <v>26.700000000000003</v>
       </c>
-      <c r="AB16">
+      <c r="N29">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
         <v>133.5</v>
       </c>
-      <c r="AC16">
+      <c r="O29">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
         <v>1684.5425867507856</v>
       </c>
     </row>
-    <row r="17" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="Q17" s="6">
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C30" s="6">
         <v>0.6</v>
       </c>
-      <c r="R17" s="2">
+      <c r="D30" s="2">
         <v>2</v>
       </c>
-      <c r="S17" s="2">
+      <c r="E30" s="2">
         <v>1</v>
       </c>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2">
+      <c r="F30" s="2"/>
+      <c r="G30" s="2">
         <v>137</v>
       </c>
-      <c r="V17" cm="1">
-        <f t="array" ref="V17">表7[[#This Row],[单价]]*金价表[税后金价]</f>
+      <c r="H30" cm="1">
+        <f t="array" ref="H30">表7[[#This Row],[单价]]*金价表[税后金价]</f>
         <v>32.086842105263159</v>
       </c>
-      <c r="W17">
+      <c r="I30">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
         <v>26.739035087719301</v>
       </c>
-      <c r="X17" s="2">
+      <c r="J30" s="2">
         <v>0</v>
       </c>
-      <c r="Y17" s="2">
+      <c r="K30" s="2">
         <f>表7[[#This Row],[模拟数量]]</f>
         <v>0</v>
       </c>
-      <c r="Z17">
+      <c r="L30">
         <f>表7[[#This Row],[成功数量]]*表7[[#This Row],[敏捷]]</f>
         <v>0</v>
       </c>
-      <c r="AA17">
+      <c r="M30">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
         <v>0</v>
       </c>
-      <c r="AB17">
+      <c r="N30">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
         <v>0</v>
       </c>
-      <c r="AC17" t="e">
+      <c r="O30" t="e">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="18" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="Q18" s="6">
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="C31" s="6">
         <v>1</v>
       </c>
-      <c r="R18" s="2">
+      <c r="D31" s="2">
         <v>1</v>
       </c>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18">
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31">
         <v>3.5</v>
       </c>
-      <c r="V18" cm="1">
-        <f t="array" ref="V18">表7[[#This Row],[单价]]*金价表[税后金价]</f>
+      <c r="H31" cm="1">
+        <f t="array" ref="H31">表7[[#This Row],[单价]]*金价表[税后金价]</f>
         <v>0.81973684210526321</v>
       </c>
-      <c r="W18">
+      <c r="I31">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
         <v>0.81973684210526321</v>
       </c>
-      <c r="X18" s="2">
+      <c r="J31" s="2">
         <v>4</v>
       </c>
-      <c r="Y18">
+      <c r="K31">
         <f>表7[[#This Row],[模拟数量]]</f>
         <v>4</v>
       </c>
-      <c r="Z18">
+      <c r="L31">
         <f>表7[[#This Row],[成功数量]]*表7[[#This Row],[敏捷]]</f>
         <v>4</v>
       </c>
-      <c r="AA18">
+      <c r="M31">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
         <v>3.2789473684210528</v>
       </c>
-      <c r="AB18">
+      <c r="N31">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
         <v>3.2789473684210528</v>
       </c>
-      <c r="AC18">
+      <c r="O31">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
         <v>3.2789473684210528</v>
       </c>
     </row>
-    <row r="19" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="U19" s="2"/>
-      <c r="X19">
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="G32" s="2"/>
+      <c r="J32">
         <f>SUM(表7[模拟数量])</f>
         <v>10</v>
       </c>
-      <c r="Z19">
+      <c r="L32">
         <f>SUM(表7[总敏捷])</f>
         <v>19</v>
       </c>
-      <c r="AA19">
+      <c r="M32">
         <f>SUM(表7[成本造价])</f>
         <v>29.978947368421057</v>
       </c>
-      <c r="AB19">
+      <c r="N32">
         <f>SUM(表7[总价格])</f>
         <v>136.77894736842106</v>
       </c>
-      <c r="AC19" t="e">
+      <c r="O32" t="e">
         <f>SUM(表7[风险造价])</f>
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="26" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="Q26" t="s">
+    <row r="39" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
         <v>0</v>
       </c>
-      <c r="R26" t="s">
+      <c r="D39" t="s">
         <v>38</v>
       </c>
-      <c r="S26" t="s">
+      <c r="E39" t="s">
         <v>36</v>
       </c>
-      <c r="T26" t="s">
+      <c r="F39" t="s">
         <v>37</v>
       </c>
-      <c r="U26" t="s">
+      <c r="G39" t="s">
         <v>27</v>
       </c>
-      <c r="V26" t="s">
+      <c r="H39" t="s">
         <v>28</v>
       </c>
-      <c r="W26" t="s">
+      <c r="I39" t="s">
         <v>35</v>
       </c>
-      <c r="X26" t="s">
+      <c r="J39" t="s">
         <v>39</v>
       </c>
-      <c r="Y26" t="s">
+      <c r="K39" t="s">
         <v>41</v>
       </c>
-      <c r="Z26" t="s">
+      <c r="L39" t="s">
         <v>40</v>
       </c>
-      <c r="AA26" t="s">
+      <c r="M39" t="s">
         <v>42</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="N39" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="Q27" s="6">
+    <row r="40" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C40" s="6">
         <v>0.1</v>
       </c>
-      <c r="R27" s="2">
+      <c r="D40" s="2">
         <v>5</v>
       </c>
-      <c r="S27" s="2">
+      <c r="E40" s="2">
         <v>3</v>
       </c>
-      <c r="T27" s="2">
+      <c r="F40" s="2">
         <v>1</v>
       </c>
-      <c r="U27" s="2">
+      <c r="G40" s="2">
         <v>19</v>
       </c>
-      <c r="V27" cm="1">
-        <f t="array" ref="V27">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
+      <c r="H40" cm="1">
+        <f t="array" ref="H40">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
         <v>4.45</v>
       </c>
-      <c r="W27">
+      <c r="I40">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
         <v>8.9</v>
       </c>
-      <c r="X27" s="2">
+      <c r="J40" s="2">
         <v>7</v>
       </c>
-      <c r="Y27" s="2">
+      <c r="K40" s="2">
         <v>3</v>
       </c>
-      <c r="Z27">
+      <c r="L40">
         <f>表7_9[[#This Row],[成功数量]]*表7_9[[#This Row],[敏捷]]</f>
         <v>15</v>
       </c>
-      <c r="AA27">
+      <c r="M40">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
         <v>31.150000000000002</v>
       </c>
-      <c r="AB27">
+      <c r="N40">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
         <v>346.41807601736014</v>
       </c>
     </row>
-    <row r="28" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="Q28" s="6">
+    <row r="41" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C41" s="6">
         <v>0.6</v>
       </c>
-      <c r="R28" s="2">
+      <c r="D41" s="2">
         <v>2</v>
       </c>
-      <c r="S28" s="2">
+      <c r="E41" s="2">
         <v>1</v>
       </c>
-      <c r="T28" s="2"/>
-      <c r="U28" s="2">
+      <c r="F41" s="2"/>
+      <c r="G41" s="2">
         <v>137</v>
       </c>
-      <c r="V28" cm="1">
-        <f t="array" ref="V28">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
+      <c r="H41" cm="1">
+        <f t="array" ref="H41">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
         <v>32.086842105263159</v>
       </c>
-      <c r="W28">
+      <c r="I41">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
         <v>26.739035087719301</v>
       </c>
-      <c r="X28" s="2">
+      <c r="J41" s="2">
         <v>3</v>
       </c>
-      <c r="Y28" s="2">
+      <c r="K41" s="2">
         <v>3</v>
       </c>
-      <c r="Z28">
+      <c r="L41">
         <f>表7_9[[#This Row],[成功数量]]*表7_9[[#This Row],[敏捷]]</f>
         <v>6</v>
       </c>
-      <c r="AA28">
+      <c r="M41">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
         <v>96.260526315789477</v>
       </c>
-      <c r="AB28">
+      <c r="N41">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
         <v>123.7918291098116</v>
       </c>
     </row>
-    <row r="29" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="Q29" s="6">
+    <row r="42" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="C42" s="6">
         <v>1</v>
       </c>
-      <c r="R29" s="2">
+      <c r="D42" s="2">
         <v>1</v>
       </c>
-      <c r="S29" s="2"/>
-      <c r="T29" s="2"/>
-      <c r="U29">
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42">
         <v>3.5</v>
       </c>
-      <c r="V29" cm="1">
-        <f t="array" ref="V29">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
+      <c r="H42" cm="1">
+        <f t="array" ref="H42">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
         <v>0.81973684210526321</v>
       </c>
-      <c r="W29">
+      <c r="I42">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
         <v>0.81973684210526321</v>
       </c>
-      <c r="X29" s="2">
+      <c r="J42" s="2">
         <v>0</v>
       </c>
-      <c r="Y29">
+      <c r="K42">
         <f>表7_9[[#This Row],[模拟数量]]</f>
         <v>0</v>
       </c>
-      <c r="Z29">
+      <c r="L42">
         <f>表7_9[[#This Row],[成功数量]]*表7_9[[#This Row],[敏捷]]</f>
         <v>0</v>
       </c>
-      <c r="AA29">
+      <c r="M42">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
         <v>0</v>
       </c>
-      <c r="AB29">
+      <c r="N42">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="17:29" x14ac:dyDescent="0.2">
-      <c r="U30" s="2"/>
-      <c r="X30">
+    <row r="43" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="G43" s="2"/>
+      <c r="J43">
         <f>SUM(表7_9[模拟数量])</f>
         <v>10</v>
       </c>
-      <c r="Z30">
+      <c r="L43">
         <f>SUM(表7_9[总敏捷])</f>
         <v>21</v>
       </c>
-      <c r="AA30">
+      <c r="M43">
         <f>SUM(表7_9[造价])</f>
         <v>127.41052631578948</v>
       </c>
-      <c r="AB30">
+      <c r="N43">
         <f>SUM(表7_9[风险造价])</f>
         <v>470.20990512717174</v>
       </c>
@@ -8069,7 +8278,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C898E4F5-1983-43C5-86AB-660F992C424E}">
-  <dimension ref="B2:W47"/>
+  <dimension ref="B2:U37"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="17.25" customWidth="1"/>
@@ -8077,15 +8286,16 @@
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="13" width="10.25" customWidth="1"/>
     <col min="14" max="14" width="13.875" customWidth="1"/>
-    <col min="15" max="17" width="13.5" customWidth="1"/>
-    <col min="18" max="18" width="13.875" customWidth="1"/>
-    <col min="19" max="19" width="13.5" customWidth="1"/>
-    <col min="20" max="21" width="12.5" customWidth="1"/>
-    <col min="22" max="22" width="16.625" customWidth="1"/>
-    <col min="23" max="23" width="14.875" customWidth="1"/>
+    <col min="15" max="18" width="13.5" customWidth="1"/>
+    <col min="19" max="19" width="13.875" customWidth="1"/>
+    <col min="20" max="20" width="13.5" customWidth="1"/>
+    <col min="21" max="22" width="12.5" customWidth="1"/>
+    <col min="23" max="23" width="16.625" customWidth="1"/>
+    <col min="24" max="24" width="14.875" customWidth="1"/>
+    <col min="25" max="28" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>59</v>
       </c>
@@ -8093,7 +8303,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B3" t="s">
         <v>61</v>
       </c>
@@ -8101,53 +8311,56 @@
         <v>62</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J5" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="J6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="D8" s="3" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>165</v>
+        <v>130</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>166</v>
+        <v>131</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>68</v>
+        <v>169</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>89</v>
+        <v>168</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D9">
         <v>0.6</v>
       </c>
@@ -8158,41 +8371,44 @@
         <v>1</v>
       </c>
       <c r="G9">
+        <v>0.54</v>
+      </c>
+      <c r="H9">
         <v>5</v>
       </c>
-      <c r="H9">
-        <v>0.54</v>
-      </c>
       <c r="I9">
+        <v>2.5</v>
+      </c>
+      <c r="J9">
         <v>1.5</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>1</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.5</v>
       </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D11" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D12" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="F12" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="D13">
         <v>-10</v>
       </c>
@@ -8206,812 +8422,1083 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="D16" t="s">
+    <row r="20" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="L20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D17" t="s">
+    <row r="22" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="L22" t="s">
         <v>70</v>
       </c>
-      <c r="E17" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="18" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D18">
+    </row>
+    <row r="25" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D25" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" t="s">
+        <v>162</v>
+      </c>
+      <c r="G25" t="s">
+        <v>163</v>
+      </c>
+      <c r="H25" t="s">
+        <v>164</v>
+      </c>
+      <c r="I25" t="s">
+        <v>165</v>
+      </c>
+      <c r="J25" t="s">
+        <v>68</v>
+      </c>
+      <c r="K25" t="s">
+        <v>38</v>
+      </c>
+      <c r="L25" t="s">
+        <v>161</v>
+      </c>
+      <c r="M25" t="s">
+        <v>84</v>
+      </c>
+      <c r="N25" t="s">
+        <v>128</v>
+      </c>
+      <c r="O25" t="s">
+        <v>129</v>
+      </c>
+      <c r="P25" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>167</v>
+      </c>
+      <c r="R25" t="s">
+        <v>75</v>
+      </c>
+      <c r="S25" t="s">
+        <v>74</v>
+      </c>
+      <c r="T25" t="s">
+        <v>80</v>
+      </c>
+      <c r="U25" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D26" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26" s="8">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2">
+        <v>44</v>
+      </c>
+      <c r="G26" s="2">
+        <v>23</v>
+      </c>
+      <c r="H26" s="2">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2</v>
+      </c>
+      <c r="J26" s="10">
         <v>6</v>
       </c>
-      <c r="E18">
-        <v>83</v>
-      </c>
-      <c r="F18">
+      <c r="K26" s="10">
+        <v>110</v>
+      </c>
+      <c r="L26" s="10">
         <v>6</v>
       </c>
-      <c r="G18">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="20" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="L20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="L22" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="25" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D25" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="26" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D26" t="s">
-        <v>77</v>
-      </c>
-      <c r="E26" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="27" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D27" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D28" t="s">
-        <v>80</v>
-      </c>
-      <c r="E28">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D29" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="30" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D30" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="31" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D31" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="32" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D32" t="s">
-        <v>193</v>
-      </c>
-      <c r="E32">
-        <v>2</v>
-      </c>
-      <c r="K32" t="s">
-        <v>111</v>
-      </c>
-      <c r="L32" t="s">
-        <v>139</v>
-      </c>
-      <c r="M32" t="s">
-        <v>138</v>
-      </c>
-      <c r="N32" t="s">
-        <v>110</v>
-      </c>
-      <c r="O32" t="s">
-        <v>38</v>
-      </c>
-      <c r="P32" t="s">
-        <v>163</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>164</v>
-      </c>
-      <c r="R32" t="s">
-        <v>108</v>
-      </c>
-      <c r="S32" t="s">
-        <v>109</v>
-      </c>
-      <c r="T32" t="s">
-        <v>96</v>
-      </c>
-      <c r="U32" t="s">
-        <v>94</v>
-      </c>
-      <c r="V32" t="s">
-        <v>102</v>
-      </c>
-      <c r="W32" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="33" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D33" t="s">
-        <v>84</v>
-      </c>
-      <c r="E33">
-        <f>SUM(攻击表[值])</f>
-        <v>69</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="L33" s="8">
-        <v>0</v>
-      </c>
-      <c r="M33" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>69</v>
-      </c>
-      <c r="N33" s="2">
+      <c r="M26" s="10">
         <v>338</v>
       </c>
-      <c r="O33" s="2">
-        <v>110</v>
-      </c>
-      <c r="P33" cm="1">
-        <f t="array" ref="P33">表15[[#This Row],[攻击]]
+      <c r="N26" cm="1">
+        <f t="array" ref="N26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>919.63199999999995</v>
       </c>
-      <c r="Q33" cm="1">
-        <f t="array" ref="Q33">表15[[#This Row],[攻击]]
+      <c r="O26" cm="1">
+        <f t="array" ref="O26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>533.41967999999997</v>
       </c>
-      <c r="R33" cm="1">
-        <f t="array" ref="R33">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1166.0999999999999</v>
-      </c>
-      <c r="S33" cm="1">
-        <f t="array" ref="S33">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>351.9</v>
-      </c>
-      <c r="T33" cm="1">
-        <f t="array" ref="T33">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P26" cm="1">
+        <f t="array" ref="P26">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1749.1499999999999</v>
+      </c>
+      <c r="Q26" cm="1">
+        <f t="array" ref="Q26">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>874.57499999999993</v>
+      </c>
+      <c r="R26" cm="1">
+        <f t="array" ref="R26">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>2915.25</v>
       </c>
-      <c r="U33" cm="1">
-        <f t="array" ref="U33">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>879.75</v>
-      </c>
-      <c r="V33" s="1" cm="1">
-        <f t="array" ref="V33">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S26" cm="1">
+        <f t="array" ref="S26">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1457.625</v>
+      </c>
+      <c r="T26" s="1" cm="1">
+        <f t="array" ref="T26">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2413.7249999999999</v>
       </c>
-      <c r="W33" s="1" cm="1">
-        <f t="array" ref="W33">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>539.77499999999998</v>
-      </c>
-    </row>
-    <row r="34" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="K34" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="L34" s="8">
+      <c r="U26" s="1" cm="1">
+        <f t="array" ref="U26">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1059.8625</v>
+      </c>
+    </row>
+    <row r="27" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D27" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" s="8">
         <v>1</v>
       </c>
-      <c r="M34" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>70</v>
-      </c>
-      <c r="N34" s="2">
+      <c r="F27" s="2">
+        <v>44</v>
+      </c>
+      <c r="G27" s="2">
+        <v>23</v>
+      </c>
+      <c r="H27" s="2">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2">
+        <v>2</v>
+      </c>
+      <c r="J27" s="10">
+        <v>6</v>
+      </c>
+      <c r="K27" s="10">
+        <v>110</v>
+      </c>
+      <c r="L27" s="10">
+        <v>6</v>
+      </c>
+      <c r="M27" s="10">
         <v>338</v>
       </c>
-      <c r="O34" s="2">
-        <v>110</v>
-      </c>
-      <c r="P34" cm="1">
-        <f t="array" ref="P34">表15[[#This Row],[攻击]]
+      <c r="N27" cm="1">
+        <f t="array" ref="N27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>932.96</v>
       </c>
-      <c r="Q34" cm="1">
-        <f t="array" ref="Q34">表15[[#This Row],[攻击]]
+      <c r="O27" cm="1">
+        <f t="array" ref="O27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>541.15039999999999</v>
       </c>
-      <c r="R34" cm="1">
-        <f t="array" ref="R34">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1183</v>
-      </c>
-      <c r="S34" cm="1">
-        <f t="array" ref="S34">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>357</v>
-      </c>
-      <c r="T34" cm="1">
-        <f t="array" ref="T34">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P27" cm="1">
+        <f t="array" ref="P27">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1774.5</v>
+      </c>
+      <c r="Q27" cm="1">
+        <f t="array" ref="Q27">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>887.25</v>
+      </c>
+      <c r="R27" cm="1">
+        <f t="array" ref="R27">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>2957.5</v>
       </c>
-      <c r="U34" cm="1">
-        <f t="array" ref="U34">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>892.5</v>
-      </c>
-      <c r="V34" s="1" cm="1">
-        <f t="array" ref="V34">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S27" cm="1">
+        <f t="array" ref="S27">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1478.75</v>
+      </c>
+      <c r="T27" s="1" cm="1">
+        <f t="array" ref="T27">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2451.75</v>
       </c>
-      <c r="W34" s="1" cm="1">
-        <f t="array" ref="W34">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>551.25</v>
-      </c>
-    </row>
-    <row r="35" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="K35" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="L35" s="8">
+      <c r="U27" s="1" cm="1">
+        <f t="array" ref="U27">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1078.875</v>
+      </c>
+    </row>
+    <row r="28" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D28" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E28" s="8">
         <v>2</v>
       </c>
-      <c r="M35" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>71</v>
-      </c>
-      <c r="N35" s="2">
+      <c r="F28" s="2">
+        <v>44</v>
+      </c>
+      <c r="G28" s="2">
+        <v>23</v>
+      </c>
+      <c r="H28" s="2">
+        <v>2</v>
+      </c>
+      <c r="I28" s="2">
+        <v>2</v>
+      </c>
+      <c r="J28" s="10">
+        <v>6</v>
+      </c>
+      <c r="K28" s="10">
+        <v>110</v>
+      </c>
+      <c r="L28" s="10">
+        <v>6</v>
+      </c>
+      <c r="M28" s="10">
         <v>338</v>
       </c>
-      <c r="O35" s="2">
-        <v>110</v>
-      </c>
-      <c r="P35" cm="1">
-        <f t="array" ref="P35">表15[[#This Row],[攻击]]
+      <c r="N28" cm="1">
+        <f t="array" ref="N28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>946.28800000000001</v>
       </c>
-      <c r="Q35" cm="1">
-        <f t="array" ref="Q35">表15[[#This Row],[攻击]]
+      <c r="O28" cm="1">
+        <f t="array" ref="O28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>548.88112000000001</v>
       </c>
-      <c r="R35" cm="1">
-        <f t="array" ref="R35">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1199.9000000000001</v>
-      </c>
-      <c r="S35" cm="1">
-        <f t="array" ref="S35">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>362.1</v>
-      </c>
-      <c r="T35" cm="1">
-        <f t="array" ref="T35">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P28" cm="1">
+        <f t="array" ref="P28">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1799.8500000000001</v>
+      </c>
+      <c r="Q28" cm="1">
+        <f t="array" ref="Q28">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>899.92500000000007</v>
+      </c>
+      <c r="R28" cm="1">
+        <f t="array" ref="R28">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>2999.75</v>
       </c>
-      <c r="U35" cm="1">
-        <f t="array" ref="U35">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>905.25</v>
-      </c>
-      <c r="V35" s="1" cm="1">
-        <f t="array" ref="V35">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S28" cm="1">
+        <f t="array" ref="S28">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1499.875</v>
+      </c>
+      <c r="T28" s="1" cm="1">
+        <f t="array" ref="T28">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2489.7750000000001</v>
       </c>
-      <c r="W35" s="1" cm="1">
-        <f t="array" ref="W35">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>562.72500000000002</v>
-      </c>
-    </row>
-    <row r="36" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="K36" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="L36" s="8">
+      <c r="U28" s="1" cm="1">
+        <f t="array" ref="U28">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1097.8875</v>
+      </c>
+    </row>
+    <row r="29" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D29" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E29" s="8">
         <v>3</v>
       </c>
-      <c r="M36" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>72</v>
-      </c>
-      <c r="N36" s="2">
+      <c r="F29" s="2">
+        <v>44</v>
+      </c>
+      <c r="G29" s="2">
+        <v>23</v>
+      </c>
+      <c r="H29" s="2">
+        <v>3</v>
+      </c>
+      <c r="I29" s="2">
+        <v>2</v>
+      </c>
+      <c r="J29" s="10">
+        <v>6</v>
+      </c>
+      <c r="K29" s="10">
+        <v>110</v>
+      </c>
+      <c r="L29" s="10">
+        <v>6</v>
+      </c>
+      <c r="M29" s="10">
         <v>338</v>
       </c>
-      <c r="O36" s="2">
-        <v>110</v>
-      </c>
-      <c r="P36" cm="1">
-        <f t="array" ref="P36">表15[[#This Row],[攻击]]
+      <c r="N29" cm="1">
+        <f t="array" ref="N29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>959.61599999999987</v>
       </c>
-      <c r="Q36" cm="1">
-        <f t="array" ref="Q36">表15[[#This Row],[攻击]]
+      <c r="O29" cm="1">
+        <f t="array" ref="O29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>556.61184000000003</v>
       </c>
-      <c r="R36" cm="1">
-        <f t="array" ref="R36">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1216.8</v>
-      </c>
-      <c r="S36" cm="1">
-        <f t="array" ref="S36">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>367.2</v>
-      </c>
-      <c r="T36" cm="1">
-        <f t="array" ref="T36">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P29" cm="1">
+        <f t="array" ref="P29">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1825.1999999999998</v>
+      </c>
+      <c r="Q29" cm="1">
+        <f t="array" ref="Q29">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>912.59999999999991</v>
+      </c>
+      <c r="R29" cm="1">
+        <f t="array" ref="R29">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3042</v>
       </c>
-      <c r="U36" cm="1">
-        <f t="array" ref="U36">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>918</v>
-      </c>
-      <c r="V36" s="1" cm="1">
-        <f t="array" ref="V36">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S29" cm="1">
+        <f t="array" ref="S29">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1521</v>
+      </c>
+      <c r="T29" s="1" cm="1">
+        <f t="array" ref="T29">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2527.8000000000002</v>
       </c>
-      <c r="W36" s="1" cm="1">
-        <f t="array" ref="W36">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>574.20000000000005</v>
-      </c>
-    </row>
-    <row r="37" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="K37" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="L37" s="8">
+      <c r="U29" s="1" cm="1">
+        <f t="array" ref="U29">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1116.9000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D30" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="E30" s="8">
         <v>4</v>
       </c>
-      <c r="M37" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>73</v>
-      </c>
-      <c r="N37" s="2">
+      <c r="F30" s="2">
+        <v>44</v>
+      </c>
+      <c r="G30" s="2">
+        <v>23</v>
+      </c>
+      <c r="H30" s="2">
+        <v>4</v>
+      </c>
+      <c r="I30" s="2">
+        <v>2</v>
+      </c>
+      <c r="J30" s="10">
+        <v>6</v>
+      </c>
+      <c r="K30" s="10">
+        <v>110</v>
+      </c>
+      <c r="L30" s="10">
+        <v>6</v>
+      </c>
+      <c r="M30" s="10">
         <v>338</v>
       </c>
-      <c r="O37" s="2">
-        <v>110</v>
-      </c>
-      <c r="P37" cm="1">
-        <f t="array" ref="P37">表15[[#This Row],[攻击]]
+      <c r="N30" cm="1">
+        <f t="array" ref="N30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>972.94399999999996</v>
       </c>
-      <c r="Q37" cm="1">
-        <f t="array" ref="Q37">表15[[#This Row],[攻击]]
+      <c r="O30" cm="1">
+        <f t="array" ref="O30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>564.34256000000005</v>
       </c>
-      <c r="R37" cm="1">
-        <f t="array" ref="R37">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1233.7</v>
-      </c>
-      <c r="S37" cm="1">
-        <f t="array" ref="S37">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>372.3</v>
-      </c>
-      <c r="T37" cm="1">
-        <f t="array" ref="T37">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P30" cm="1">
+        <f t="array" ref="P30">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1850.5500000000002</v>
+      </c>
+      <c r="Q30" cm="1">
+        <f t="array" ref="Q30">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>925.27500000000009</v>
+      </c>
+      <c r="R30" cm="1">
+        <f t="array" ref="R30">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3084.25</v>
       </c>
-      <c r="U37" cm="1">
-        <f t="array" ref="U37">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>930.75</v>
-      </c>
-      <c r="V37" s="1" cm="1">
-        <f t="array" ref="V37">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S30" cm="1">
+        <f t="array" ref="S30">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1542.125</v>
+      </c>
+      <c r="T30" s="1" cm="1">
+        <f t="array" ref="T30">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2565.8250000000003</v>
       </c>
-      <c r="W37" s="1" cm="1">
-        <f t="array" ref="W37">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>585.67500000000007</v>
-      </c>
-    </row>
-    <row r="38" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D38" t="s">
-        <v>85</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="L38" s="8">
+      <c r="U30" s="1" cm="1">
+        <f t="array" ref="U30">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1135.9125000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D31" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E31" s="8">
         <v>5</v>
       </c>
-      <c r="M38" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>74</v>
-      </c>
-      <c r="N38" s="2">
+      <c r="F31" s="2">
+        <v>44</v>
+      </c>
+      <c r="G31" s="2">
+        <v>23</v>
+      </c>
+      <c r="H31" s="2">
+        <v>5</v>
+      </c>
+      <c r="I31" s="2">
+        <v>2</v>
+      </c>
+      <c r="J31" s="10">
+        <v>6</v>
+      </c>
+      <c r="K31" s="10">
+        <v>110</v>
+      </c>
+      <c r="L31" s="10">
+        <v>6</v>
+      </c>
+      <c r="M31" s="10">
         <v>338</v>
       </c>
-      <c r="O38" s="2">
-        <v>110</v>
-      </c>
-      <c r="P38" cm="1">
-        <f t="array" ref="P38">表15[[#This Row],[攻击]]
+      <c r="N31" cm="1">
+        <f t="array" ref="N31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>986.27199999999993</v>
       </c>
-      <c r="Q38" cm="1">
-        <f t="array" ref="Q38">表15[[#This Row],[攻击]]
+      <c r="O31" cm="1">
+        <f t="array" ref="O31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>572.07328000000007</v>
       </c>
-      <c r="R38" cm="1">
-        <f t="array" ref="R38">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1250.5999999999999</v>
-      </c>
-      <c r="S38" cm="1">
-        <f t="array" ref="S38">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>377.4</v>
-      </c>
-      <c r="T38" cm="1">
-        <f t="array" ref="T38">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P31" cm="1">
+        <f t="array" ref="P31">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1875.8999999999999</v>
+      </c>
+      <c r="Q31" cm="1">
+        <f t="array" ref="Q31">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>937.94999999999993</v>
+      </c>
+      <c r="R31" cm="1">
+        <f t="array" ref="R31">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3126.5</v>
       </c>
-      <c r="U38" cm="1">
-        <f t="array" ref="U38">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>943.5</v>
-      </c>
-      <c r="V38" s="1" cm="1">
-        <f t="array" ref="V38">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S31" cm="1">
+        <f t="array" ref="S31">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1563.25</v>
+      </c>
+      <c r="T31" s="1" cm="1">
+        <f t="array" ref="T31">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2603.85</v>
       </c>
-      <c r="W38" s="1" cm="1">
-        <f t="array" ref="W38">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>597.15</v>
-      </c>
-    </row>
-    <row r="39" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D39" t="s">
-        <v>86</v>
-      </c>
-      <c r="E39" t="s">
-        <v>78</v>
-      </c>
-      <c r="K39" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="L39" s="8">
+      <c r="U31" s="1" cm="1">
+        <f t="array" ref="U31">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1154.925</v>
+      </c>
+    </row>
+    <row r="32" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D32" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="E32" s="8">
         <v>6</v>
       </c>
-      <c r="M39" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>75</v>
-      </c>
-      <c r="N39" s="2">
+      <c r="F32" s="2">
+        <v>44</v>
+      </c>
+      <c r="G32" s="2">
+        <v>23</v>
+      </c>
+      <c r="H32" s="2">
+        <v>6</v>
+      </c>
+      <c r="I32" s="2">
+        <v>2</v>
+      </c>
+      <c r="J32" s="10">
+        <v>6</v>
+      </c>
+      <c r="K32" s="10">
+        <v>110</v>
+      </c>
+      <c r="L32" s="10">
+        <v>6</v>
+      </c>
+      <c r="M32" s="10">
         <v>338</v>
       </c>
-      <c r="O39" s="2">
-        <v>110</v>
-      </c>
-      <c r="P39" cm="1">
-        <f t="array" ref="P39">表15[[#This Row],[攻击]]
+      <c r="N32" cm="1">
+        <f t="array" ref="N32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>999.6</v>
       </c>
-      <c r="Q39" cm="1">
-        <f t="array" ref="Q39">表15[[#This Row],[攻击]]
+      <c r="O32" cm="1">
+        <f t="array" ref="O32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>579.80399999999997</v>
       </c>
-      <c r="R39" cm="1">
-        <f t="array" ref="R39">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1267.5</v>
-      </c>
-      <c r="S39" cm="1">
-        <f t="array" ref="S39">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>382.5</v>
-      </c>
-      <c r="T39" cm="1">
-        <f t="array" ref="T39">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P32" cm="1">
+        <f t="array" ref="P32">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1901.25</v>
+      </c>
+      <c r="Q32" cm="1">
+        <f t="array" ref="Q32">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>950.625</v>
+      </c>
+      <c r="R32" cm="1">
+        <f t="array" ref="R32">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3168.75</v>
       </c>
-      <c r="U39" cm="1">
-        <f t="array" ref="U39">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>956.25</v>
-      </c>
-      <c r="V39" s="1" cm="1">
-        <f t="array" ref="V39">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S32" cm="1">
+        <f t="array" ref="S32">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1584.375</v>
+      </c>
+      <c r="T32" s="1" cm="1">
+        <f t="array" ref="T32">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2641.875</v>
       </c>
-      <c r="W39" s="1" cm="1">
-        <f t="array" ref="W39">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>608.625</v>
-      </c>
-    </row>
-    <row r="40" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D40" t="s">
-        <v>87</v>
-      </c>
-      <c r="E40" cm="1">
-        <f t="array" ref="E40">攻击表[[#Totals],[值]]
-*(1+(属性表[运气]*常量表[主属性系数]+SUM(属性表[力量],属性表[敏捷])*常量表[面板副属性系数])/100)</f>
-        <v>834.21</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="L40" s="8">
+      <c r="U32" s="1" cm="1">
+        <f t="array" ref="U32">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1173.9375</v>
+      </c>
+    </row>
+    <row r="33" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D33" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E33" s="8">
+        <v>6</v>
+      </c>
+      <c r="F33" s="2">
+        <v>43</v>
+      </c>
+      <c r="G33" s="2">
+        <v>23</v>
+      </c>
+      <c r="H33" s="2">
         <v>7</v>
       </c>
-      <c r="M40" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>76</v>
-      </c>
-      <c r="N40" s="2">
-        <v>338</v>
-      </c>
-      <c r="O40" s="2">
-        <v>110</v>
-      </c>
-      <c r="P40" s="1" cm="1">
-        <f t="array" ref="P40">表15[[#This Row],[攻击]]
+      <c r="I33" s="2">
+        <v>2</v>
+      </c>
+      <c r="J33" s="10">
+        <v>6</v>
+      </c>
+      <c r="K33" s="10">
+        <v>104</v>
+      </c>
+      <c r="L33" s="10">
+        <v>6</v>
+      </c>
+      <c r="M33" s="10">
+        <v>343</v>
+      </c>
+      <c r="N33" cm="1">
+        <f t="array" ref="N33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100</f>
+        <v>1008.6</v>
+      </c>
+      <c r="O33" cm="1">
+        <f t="array" ref="O33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100</f>
+        <v>582.59400000000005</v>
+      </c>
+      <c r="P33" cm="1">
+        <f t="array" ref="P33">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1929.375</v>
+      </c>
+      <c r="Q33" cm="1">
+        <f t="array" ref="Q33">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>964.6875</v>
+      </c>
+      <c r="R33" cm="1">
+        <f t="array" ref="R33">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>3215.625</v>
+      </c>
+      <c r="S33" cm="1">
+        <f t="array" ref="S33">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1607.8125</v>
+      </c>
+      <c r="T33" s="1" cm="1">
+        <f t="array" ref="T33">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2684.0625</v>
+      </c>
+      <c r="U33" s="1" cm="1">
+        <f t="array" ref="U33">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1195.03125</v>
+      </c>
+    </row>
+    <row r="34" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D34" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E34" s="8">
+        <v>7</v>
+      </c>
+      <c r="F34" s="2">
+        <v>44</v>
+      </c>
+      <c r="G34" s="2">
+        <v>23</v>
+      </c>
+      <c r="H34" s="2">
+        <v>7</v>
+      </c>
+      <c r="I34" s="2">
+        <v>2</v>
+      </c>
+      <c r="J34" s="10">
+        <v>6</v>
+      </c>
+      <c r="K34" s="10">
+        <v>110</v>
+      </c>
+      <c r="L34" s="10">
+        <v>6</v>
+      </c>
+      <c r="M34" s="10">
+        <v>338</v>
+      </c>
+      <c r="N34" cm="1">
+        <f t="array" ref="N34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>1012.928</v>
       </c>
-      <c r="Q40" s="1" cm="1">
-        <f t="array" ref="Q40">表15[[#This Row],[攻击]]
+      <c r="O34" cm="1">
+        <f t="array" ref="O34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>587.53471999999999</v>
       </c>
-      <c r="R40" s="1" cm="1">
-        <f t="array" ref="R40">表15[[#This Row],[攻击]]
-*(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
-)/100</f>
-        <v>1284.4000000000001</v>
-      </c>
-      <c r="S40" s="1" cm="1">
-        <f t="array" ref="S40">表15[[#This Row],[攻击]]
-*(
- 0.5*常量表[主属性系数]*属性表[运气]
-)/100</f>
-        <v>387.6</v>
-      </c>
-      <c r="T40" s="1" cm="1">
-        <f t="array" ref="T40">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
+      <c r="P34" cm="1">
+        <f t="array" ref="P34">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1926.6000000000001</v>
+      </c>
+      <c r="Q34" cm="1">
+        <f t="array" ref="Q34">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>963.30000000000007</v>
+      </c>
+      <c r="R34" cm="1">
+        <f t="array" ref="R34">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3211</v>
       </c>
-      <c r="U40" s="1" cm="1">
-        <f t="array" ref="U40">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>969</v>
-      </c>
-      <c r="V40" s="1" cm="1">
-        <f t="array" ref="V40">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="S34" cm="1">
+        <f t="array" ref="S34">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1605.5</v>
+      </c>
+      <c r="T34" s="1" cm="1">
+        <f t="array" ref="T34">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2679.9</v>
       </c>
-      <c r="W40" s="1" cm="1">
-        <f t="array" ref="W40">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>620.1</v>
-      </c>
-    </row>
-    <row r="41" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D41" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" cm="1">
-        <f t="array" ref="E41">攻击表[[#Totals],[值]]
-*(常量表[伤害下限系数]+(属性表[运气]*常量表[主属性系数]*常量表[熟练度系数]+SUM(属性表[力量],属性表[敏捷])*常量表[面板副属性系数])/100)</f>
-        <v>482.86200000000002</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="L41" s="8">
+      <c r="U34" s="1" cm="1">
+        <f t="array" ref="U34">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1192.95</v>
+      </c>
+    </row>
+    <row r="35" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D35" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E35" s="8">
+        <v>7</v>
+      </c>
+      <c r="F35" s="2">
+        <v>70</v>
+      </c>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2">
+        <v>7</v>
+      </c>
+      <c r="I35" s="2">
+        <v>2</v>
+      </c>
+      <c r="J35" s="10">
         <v>6</v>
       </c>
-      <c r="M41" s="2">
-        <f>攻击表[[#Totals],[值]]+表15[[#This Row],[额外攻击]]</f>
-        <v>75</v>
-      </c>
-      <c r="N41" s="2">
-        <v>343</v>
-      </c>
-      <c r="O41" s="2">
-        <v>104</v>
-      </c>
-      <c r="P41" s="1" cm="1">
-        <f t="array" ref="P41">表15[[#This Row],[攻击]]
+      <c r="K35" s="10">
+        <v>94</v>
+      </c>
+      <c r="L35" s="10">
+        <v>6</v>
+      </c>
+      <c r="M35" s="10">
+        <v>353</v>
+      </c>
+      <c r="N35" cm="1">
+        <f t="array" ref="N35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1008.6</v>
-      </c>
-      <c r="Q41" s="1" cm="1">
-        <f t="array" ref="Q41">表15[[#This Row],[攻击]]
+        <v>1082.932</v>
+      </c>
+      <c r="O35" cm="1">
+        <f t="array" ref="O35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
- +常量表[面板副属性系数]*SUM(属性表[力量],表15[[#This Row],[敏捷]])
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>582.59400000000005</v>
-      </c>
-      <c r="R41" s="1" cm="1">
-        <f t="array" ref="R41">表15[[#This Row],[攻击]]
+        <v>621.12327999999991</v>
+      </c>
+      <c r="P35" cm="1">
+        <f t="array" ref="P35">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>2091.5249999999996</v>
+      </c>
+      <c r="Q35" cm="1">
+        <f t="array" ref="Q35">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1045.7624999999998</v>
+      </c>
+      <c r="R35" cm="1">
+        <f t="array" ref="R35">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>3485.875</v>
+      </c>
+      <c r="S35" cm="1">
+        <f t="array" ref="S35">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1742.9375</v>
+      </c>
+      <c r="T35" s="1" cm="1">
+        <f t="array" ref="T35">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2927.2874999999999</v>
+      </c>
+      <c r="U35" s="1" cm="1">
+        <f t="array" ref="U35">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1316.64375</v>
+      </c>
+    </row>
+    <row r="36" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D36" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E36" s="8">
+        <v>7</v>
+      </c>
+      <c r="F36" s="2">
+        <v>83</v>
+      </c>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2">
+        <v>7</v>
+      </c>
+      <c r="I36" s="2">
+        <v>2</v>
+      </c>
+      <c r="J36" s="10">
+        <v>50</v>
+      </c>
+      <c r="K36" s="10">
+        <v>104</v>
+      </c>
+      <c r="L36" s="10">
+        <v>6</v>
+      </c>
+      <c r="M36" s="10">
+        <f>343-44</f>
+        <v>299</v>
+      </c>
+      <c r="N36" cm="1">
+        <f t="array" ref="N36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
- 常量表[主属性系数]*表15[[#This Row],[运气]]
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1286.25</v>
-      </c>
-      <c r="S41" s="1" cm="1">
-        <f t="array" ref="S41">表15[[#This Row],[攻击]]
+        <v>1131.9680000000001</v>
+      </c>
+      <c r="O36" cm="1">
+        <f t="array" ref="O36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
- 0.5*常量表[主属性系数]*属性表[运气]
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>382.5</v>
-      </c>
-      <c r="T41" s="1" cm="1">
-        <f t="array" ref="T41">表15[[#This Row],[攻击max]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3215.625</v>
-      </c>
-      <c r="U41" s="1" cm="1">
-        <f t="array" ref="U41">表15[[#This Row],[攻击min]]*(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>956.25</v>
-      </c>
-      <c r="V41" s="1" cm="1">
-        <f t="array" ref="V41">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2684.0625</v>
-      </c>
-      <c r="W41" s="1" cm="1">
-        <f t="array" ref="W41">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>608.625</v>
-      </c>
-    </row>
-    <row r="42" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D42" t="s">
-        <v>91</v>
-      </c>
-      <c r="E42" cm="1">
-        <f t="array" ref="E42">E40*常量表[技能倍率]</f>
-        <v>1251.3150000000001</v>
-      </c>
-    </row>
-    <row r="43" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D43" t="s">
-        <v>90</v>
-      </c>
-      <c r="E43" cm="1">
-        <f t="array" ref="E43">E41*常量表[技能倍率]</f>
-        <v>724.29300000000001</v>
-      </c>
-    </row>
-    <row r="44" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D44" t="s">
-        <v>97</v>
-      </c>
-      <c r="E44" cm="1">
-        <f t="array" ref="E44">E42*常量表[暴击倍率]</f>
-        <v>1251.3150000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D45" t="s">
-        <v>95</v>
-      </c>
-      <c r="E45" cm="1">
-        <f t="array" ref="E45">E43*常量表[暴击倍率]</f>
-        <v>724.29300000000001</v>
-      </c>
-    </row>
-    <row r="46" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D46" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" cm="1">
-        <f t="array" ref="E46">E44*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>916.18350000000009</v>
-      </c>
-    </row>
-    <row r="47" spans="4:23" x14ac:dyDescent="0.2">
-      <c r="D47" t="s">
-        <v>105</v>
-      </c>
-      <c r="E47" cm="1">
-        <f t="array" ref="E47">E45*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>399.86369999999999</v>
+        <v>676.43552000000011</v>
+      </c>
+      <c r="P36" cm="1">
+        <f t="array" ref="P36">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>2063.1000000000004</v>
+      </c>
+      <c r="Q36" cm="1">
+        <f t="array" ref="Q36">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1031.5500000000002</v>
+      </c>
+      <c r="R36" cm="1">
+        <f t="array" ref="R36">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>3438.5</v>
+      </c>
+      <c r="S36" cm="1">
+        <f t="array" ref="S36">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1719.25</v>
+      </c>
+      <c r="T36" s="1" cm="1">
+        <f t="array" ref="T36">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2884.65</v>
+      </c>
+      <c r="U36" s="1" cm="1">
+        <f t="array" ref="U36">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1295.325</v>
+      </c>
+    </row>
+    <row r="37" spans="4:21" x14ac:dyDescent="0.2">
+      <c r="D37" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="E37" s="8">
+        <v>7</v>
+      </c>
+      <c r="F37" s="2">
+        <v>88</v>
+      </c>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2">
+        <v>7</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2</v>
+      </c>
+      <c r="J37" s="10">
+        <v>55</v>
+      </c>
+      <c r="K37" s="10">
+        <v>110</v>
+      </c>
+      <c r="L37" s="10">
+        <v>6</v>
+      </c>
+      <c r="M37" s="10">
+        <v>288</v>
+      </c>
+      <c r="N37" cm="1">
+        <f t="array" ref="N37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100</f>
+        <v>1165.7459999999999</v>
+      </c>
+      <c r="O37" cm="1">
+        <f t="array" ref="O37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100</f>
+        <v>703.12584000000004</v>
+      </c>
+      <c r="P37" cm="1">
+        <f t="array" ref="P37">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>2095.1999999999998</v>
+      </c>
+      <c r="Q37" cm="1">
+        <f t="array" ref="Q37">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1047.5999999999999</v>
+      </c>
+      <c r="R37" cm="1">
+        <f t="array" ref="R37">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>3492</v>
+      </c>
+      <c r="S37" cm="1">
+        <f t="array" ref="S37">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1746</v>
+      </c>
+      <c r="T37" s="1" cm="1">
+        <f t="array" ref="T37">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2932.8</v>
+      </c>
+      <c r="U37" s="1" cm="1">
+        <f t="array" ref="U37">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1319.4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="6">
-    <tablePart r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <tableParts count="3">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
-    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
@@ -9028,62 +9515,62 @@
   <sheetData>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>132</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>135</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="C6" t="s">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="D6" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="C7" t="s">
-        <v>172</v>
+        <v>137</v>
       </c>
       <c r="D7" t="s">
-        <v>174</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>173</v>
+        <v>138</v>
       </c>
       <c r="C8" t="s">
-        <v>176</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="C9" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -9105,7 +9592,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="105" spans="7:15" x14ac:dyDescent="0.2">
@@ -9113,7 +9600,7 @@
         <v>2</v>
       </c>
       <c r="H105" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="7:15" x14ac:dyDescent="0.2">
@@ -9121,7 +9608,7 @@
         <v>3</v>
       </c>
       <c r="H106" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="107" spans="7:15" x14ac:dyDescent="0.2">
@@ -9129,7 +9616,7 @@
         <v>31</v>
       </c>
       <c r="O107" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="108" spans="7:15" x14ac:dyDescent="0.2">
@@ -9137,7 +9624,7 @@
         <v>32</v>
       </c>
       <c r="O108" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="109" spans="7:15" x14ac:dyDescent="0.2">
@@ -9145,13 +9632,13 @@
         <v>19</v>
       </c>
       <c r="H109" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="N109">
         <v>33</v>
       </c>
       <c r="O109" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="110" spans="7:15" x14ac:dyDescent="0.2">
@@ -9159,13 +9646,13 @@
         <v>23</v>
       </c>
       <c r="H110" t="s">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="N110">
         <v>36</v>
       </c>
       <c r="O110" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" spans="7:15" x14ac:dyDescent="0.2">
@@ -9173,7 +9660,7 @@
         <v>39</v>
       </c>
       <c r="O111" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="112" spans="7:15" x14ac:dyDescent="0.2">
@@ -9181,7 +9668,7 @@
         <v>41</v>
       </c>
       <c r="O112" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
     </row>
     <row r="113" spans="14:15" x14ac:dyDescent="0.2">
@@ -9189,7 +9676,7 @@
         <v>54</v>
       </c>
       <c r="O113" t="s">
-        <v>161</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/冒险岛.xlsx
+++ b/冒险岛.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\BossTimer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyPrograms\BossTimer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBCDECB5-6CCE-4202-85F6-B49101714D25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0F4509-D5DF-447B-B4EC-4023A6E214AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33660" yWindow="2970" windowWidth="30090" windowHeight="17475" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32055" yWindow="690" windowWidth="28995" windowHeight="20115" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="盈利比" sheetId="4" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="188">
   <si>
     <t>卷概率</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -500,10 +500,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>额外攻击</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>工地手套+9</t>
   </si>
   <si>
@@ -794,6 +790,38 @@
   </si>
   <si>
     <t>力刀70</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运气+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+1提升面板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运气+5提升面板</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击+1提升伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>运气+5提升伤害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到90预估</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗迹4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -801,7 +829,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -876,13 +904,43 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -897,7 +955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -913,11 +971,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="63">
+  <dxfs count="67">
     <dxf>
       <font>
         <b/>
@@ -931,6 +997,76 @@
         <family val="3"/>
         <charset val="134"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="9" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
       <font>
@@ -970,6 +1106,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -986,26 +1123,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1065,16 +1182,23 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -1134,34 +1258,6 @@
       </font>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B0F0"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <strike val="0"/>
@@ -1175,6 +1271,9 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1427,6 +1526,105 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1532,96 +1730,6 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3156,22 +3264,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>494987</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>47568</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>161733</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>38024</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="图片 6">
+        <xdr:cNvPr id="2" name="图片 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D3106FA-550D-16E0-2EA4-3E1747D47909}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1220CCAD-2072-4799-9742-75E6A286F44D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3187,8 +3295,96 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11620500" y="10629900"/>
-          <a:ext cx="2504762" cy="457143"/>
+          <a:off x="11572875" y="8477250"/>
+          <a:ext cx="1533333" cy="609524"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>476052</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>9456</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="图片 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{291FF4BE-B94A-4B61-AADE-DACFACA722CD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13211175" y="8324850"/>
+          <a:ext cx="1580952" cy="552381"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>541481</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>133105</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="图片 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B2E73C0-C9FC-6FDD-EE05-47B1E3F88954}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7419975" y="9210675"/>
+          <a:ext cx="11552381" cy="1961905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3255,13 +3451,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>599773</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>142519</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3299,13 +3495,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>40</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>466421</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>113943</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3343,13 +3539,13 @@
     <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>113988</xdr:colOff>
-      <xdr:row>56</xdr:row>
+      <xdr:row>57</xdr:row>
       <xdr:rowOff>171098</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3543,30 +3739,30 @@
   <autoFilter ref="C39:N42" xr:uid="{D2F5DA31-758D-4974-A8DB-D862E9E685DC}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{C9A11298-FA96-49C6-A3A1-A77A91972722}" name="卷概率"/>
-    <tableColumn id="8" xr3:uid="{BEDD0CAD-6AB0-4C30-A86C-19070711828D}" name="敏捷" dataDxfId="31"/>
+    <tableColumn id="8" xr3:uid="{BEDD0CAD-6AB0-4C30-A86C-19070711828D}" name="敏捷" dataDxfId="32"/>
     <tableColumn id="9" xr3:uid="{DB11AE09-BC1F-400F-8121-26D0BBD40CE3}" name="命中"/>
     <tableColumn id="10" xr3:uid="{419A6181-B2C8-4E1A-BD6F-47425EDBEDC1}" name="移速"/>
-    <tableColumn id="3" xr3:uid="{06987FE9-FC9A-467C-8516-1C8A6991EFD3}" name="单价" dataDxfId="30" totalsRowDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{EC81E847-7526-4094-88CA-6860A893C3B1}" name="rmb" dataDxfId="28">
+    <tableColumn id="3" xr3:uid="{06987FE9-FC9A-467C-8516-1C8A6991EFD3}" name="单价" dataDxfId="31" totalsRowDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{EC81E847-7526-4094-88CA-6860A893C3B1}" name="rmb" dataDxfId="29">
       <calculatedColumnFormula array="1">表7_9[[#This Row],[单价]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{C26F07DB-AA65-4261-A542-9FF829521DAC}" name="敏捷价格" dataDxfId="27">
+    <tableColumn id="7" xr3:uid="{C26F07DB-AA65-4261-A542-9FF829521DAC}" name="敏捷价格" dataDxfId="28">
       <calculatedColumnFormula>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{247B50C8-19A4-4B64-A6C4-FEFA5C146E13}" name="模拟数量" totalsRowFunction="custom" dataDxfId="26">
+    <tableColumn id="11" xr3:uid="{247B50C8-19A4-4B64-A6C4-FEFA5C146E13}" name="模拟数量" totalsRowFunction="custom" dataDxfId="27">
       <totalsRowFormula>SUM(表7_9[模拟数量])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E46A5CC0-4EA5-480B-A804-F448C4FD1200}" name="成功数量" dataDxfId="25"/>
-    <tableColumn id="13" xr3:uid="{4297568D-CFCF-46D6-99EB-6BE373700BA1}" name="总敏捷" totalsRowFunction="custom" dataDxfId="24">
+    <tableColumn id="12" xr3:uid="{E46A5CC0-4EA5-480B-A804-F448C4FD1200}" name="成功数量" dataDxfId="26"/>
+    <tableColumn id="13" xr3:uid="{4297568D-CFCF-46D6-99EB-6BE373700BA1}" name="总敏捷" totalsRowFunction="custom" dataDxfId="25">
       <calculatedColumnFormula>表7_9[[#This Row],[成功数量]]*表7_9[[#This Row],[敏捷]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[总敏捷])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{DF214F81-3AC6-44F7-A044-188A8853DA6B}" name="造价" totalsRowFunction="custom" dataDxfId="23">
+    <tableColumn id="14" xr3:uid="{DF214F81-3AC6-44F7-A044-188A8853DA6B}" name="造价" totalsRowFunction="custom" dataDxfId="24">
       <calculatedColumnFormula>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[造价])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2749CEFB-FAB2-4688-B950-EB889079A869}" name="风险造价" totalsRowFunction="custom" dataDxfId="22">
+    <tableColumn id="15" xr3:uid="{2749CEFB-FAB2-4688-B950-EB889079A869}" name="风险造价" totalsRowFunction="custom" dataDxfId="23">
       <calculatedColumnFormula>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[风险造价])</totalsRowFormula>
@@ -3577,7 +3773,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4EBDEB06-9EAF-4C59-8B85-E07E60337705}" name="常量表" displayName="常量表" ref="D8:L9" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4EBDEB06-9EAF-4C59-8B85-E07E60337705}" name="常量表" displayName="常量表" ref="D8:L9" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="D8:L9" xr:uid="{1EC169C2-1CE1-41D3-B5C2-AF9DACDA284A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3623,8 +3819,8 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}" name="表15" displayName="表15" ref="D25:U37" totalsRowShown="0">
-  <autoFilter ref="D25:U37" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}" name="表15" displayName="表15" ref="D25:X38" totalsRowShown="0" headerRowDxfId="21">
+  <autoFilter ref="D25:X38" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3643,55 +3839,87 @@
     <filterColumn colId="15" hiddenButton="1"/>
     <filterColumn colId="16" hiddenButton="1"/>
     <filterColumn colId="17" hiddenButton="1"/>
+    <filterColumn colId="18" hiddenButton="1"/>
+    <filterColumn colId="19" hiddenButton="1"/>
+    <filterColumn colId="20" hiddenButton="1"/>
   </autoFilter>
-  <tableColumns count="18">
+  <tableColumns count="21">
     <tableColumn id="12" xr3:uid="{E28116B0-6337-4365-A0F6-32D60BC978B6}" name="备注" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{B41CD52A-A98D-4045-A6E3-121E0D0AEF7D}" name="额外攻击" dataDxfId="19"/>
-    <tableColumn id="19" xr3:uid="{7A53DEB6-2117-436A-BF1B-D301DAF6BCEE}" name="武器攻击" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{20152D2D-C68D-446B-8E46-96A7870A92B3}" name="飞镖攻击" dataDxfId="14"/>
-    <tableColumn id="17" xr3:uid="{A88072CD-F8EB-44C3-9C7B-02B153E89A1A}" name="手套攻击" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{D1098DDD-BCA5-4948-A22C-8762851A9BB4}" name="Link攻击" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{1D59A3FA-F5A2-4BF3-8DFD-364A71CE22EE}" name="力量" dataDxfId="8"/>
-    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{85C70B3A-5D87-4857-BD02-D3B80CC6C80E}" name="智力" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="4"/>
-    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="5">
+    <tableColumn id="19" xr3:uid="{7A53DEB6-2117-436A-BF1B-D301DAF6BCEE}" name="武器攻击" dataDxfId="19"/>
+    <tableColumn id="18" xr3:uid="{20152D2D-C68D-446B-8E46-96A7870A92B3}" name="飞镖攻击" dataDxfId="18"/>
+    <tableColumn id="17" xr3:uid="{A88072CD-F8EB-44C3-9C7B-02B153E89A1A}" name="手套攻击" dataDxfId="17"/>
+    <tableColumn id="16" xr3:uid="{D1098DDD-BCA5-4948-A22C-8762851A9BB4}" name="Link攻击" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{1D59A3FA-F5A2-4BF3-8DFD-364A71CE22EE}" name="力量" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{85C70B3A-5D87-4857-BD02-D3B80CC6C80E}" name="智力" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="11">
       <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="2">
+    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="10">
       <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="双飞斩max" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{0600774E-6E25-4B9E-B1EF-DC7A6148D9E7}" name="攻击+1提升面板" dataDxfId="9">
+      <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="13" xr3:uid="{F92D18E3-61E1-4175-A13E-DEEF72D61CB3}" name="运气+5提升面板" dataDxfId="8">
+      <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="双飞斩max" dataDxfId="7">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="双飞斩min" dataDxfId="11">
+    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="双飞斩min" dataDxfId="6">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="10">
+    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="5">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="9">
+    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="4">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="20" xr3:uid="{030A6DFF-61EB-463E-AC11-D16E84D830A0}" name="攻击+1提升伤害" dataDxfId="3">
+      <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="21" xr3:uid="{E30714F7-4C29-45F8-B00B-4FBAD467D571}" name="运气+5提升伤害" dataDxfId="2">
+      <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{CDE151F5-6122-4088-B163-44E497C31795}" name="实际伤害max" dataDxfId="1">
       <calculatedColumnFormula array="1">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</calculatedColumnFormula>
@@ -3721,7 +3949,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}" name="金价表" displayName="金价表" ref="B5:E6" totalsRowShown="0" headerRowDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}" name="金价表" displayName="金价表" ref="B5:E6" totalsRowShown="0" headerRowDxfId="66">
   <autoFilter ref="B5:E6" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3729,11 +3957,11 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{63ED9EB8-73DB-4AD9-B2A4-1D5B7478467C}" name="当前金价1w" dataDxfId="54"/>
+    <tableColumn id="1" xr3:uid="{63ED9EB8-73DB-4AD9-B2A4-1D5B7478467C}" name="当前金价1w" dataDxfId="65"/>
     <tableColumn id="2" xr3:uid="{D33CA45C-8193-4B2C-8B27-FBAD392BC340}" name="税后金价">
       <calculatedColumnFormula>金价表[[#This Row],[当前金价1w]]/0.95</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{29531BBF-B529-4F64-A29C-03F62C776778}" name="出售商品价格" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{29531BBF-B529-4F64-A29C-03F62C776778}" name="出售商品价格" dataDxfId="64"/>
     <tableColumn id="4" xr3:uid="{35F8F87C-3C60-4850-9D79-EF218F013BD7}" name="等价rmb">
       <calculatedColumnFormula>金价表[[#This Row],[出售商品价格]]*金价表[[#This Row],[当前金价1w]]*0.95</calculatedColumnFormula>
     </tableColumn>
@@ -3743,7 +3971,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}" name="表16" displayName="表16" ref="H12:N34" totalsRowShown="0" headerRowDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}" name="表16" displayName="表16" ref="H12:N34" totalsRowShown="0" headerRowDxfId="63">
   <autoFilter ref="H12:N34" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3754,13 +3982,13 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67FFE6FF-4DC3-4141-9556-C34751EE7C54}" name="商品名称" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{AA234072-647C-4A37-BA00-45785241169C}" name="购买价格w" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{B69C23F2-12E4-49E4-B956-F35FECF6EED2}" name="制作价格" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{1F179FDF-DB5D-4D9E-9382-252E36157465}" name="差价（含税）" dataDxfId="48">
+    <tableColumn id="1" xr3:uid="{67FFE6FF-4DC3-4141-9556-C34751EE7C54}" name="商品名称" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{AA234072-647C-4A37-BA00-45785241169C}" name="购买价格w" dataDxfId="61"/>
+    <tableColumn id="6" xr3:uid="{B69C23F2-12E4-49E4-B956-F35FECF6EED2}" name="制作价格" dataDxfId="60"/>
+    <tableColumn id="7" xr3:uid="{1F179FDF-DB5D-4D9E-9382-252E36157465}" name="差价（含税）" dataDxfId="59">
       <calculatedColumnFormula>IF(表16[[#This Row],[制作价格]]&gt;0,表16[[#This Row],[购买价格w]]*0.95-表16[[#This Row],[制作价格]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8A5E4DE9-C2B5-4A40-BB32-99BB0FFB6D5C}" name="等价rmb" dataDxfId="47">
+    <tableColumn id="3" xr3:uid="{8A5E4DE9-C2B5-4A40-BB32-99BB0FFB6D5C}" name="等价rmb" dataDxfId="58">
       <calculatedColumnFormula array="1">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{DFF8FCC2-0D9D-4B90-A22F-E3039B1304EA}" name="提升"/>
@@ -3771,8 +3999,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}" name="表5" displayName="表5" ref="E32:L66" totalsRowShown="0">
-  <autoFilter ref="E32:L66" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}" name="表5" displayName="表5" ref="E32:L69" totalsRowShown="0">
+  <autoFilter ref="E32:L69" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -3784,11 +4012,11 @@
   </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{1845B151-23D6-4795-B6F2-CF21BBF78274}" name="源"/>
-    <tableColumn id="6" xr3:uid="{6745D84B-176D-410B-A732-E68A39D776C3}" name="开始lv" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{EB49316D-EA89-440F-8BED-529A7B30C022}" name="开始" dataDxfId="61"/>
-    <tableColumn id="7" xr3:uid="{D165A06A-4105-4A22-9828-A4BEF84DACDC}" name="结束lv" dataDxfId="60"/>
-    <tableColumn id="3" xr3:uid="{7BC03053-038D-41AD-84CE-B60879A78C44}" name="结束" dataDxfId="59"/>
-    <tableColumn id="8" xr3:uid="{18F6AB19-F5E3-4464-85E9-7510B0FF4FBB}" name="总经验(万)" dataDxfId="58">
+    <tableColumn id="6" xr3:uid="{6745D84B-176D-410B-A732-E68A39D776C3}" name="开始lv" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{EB49316D-EA89-440F-8BED-529A7B30C022}" name="开始" dataDxfId="56"/>
+    <tableColumn id="7" xr3:uid="{D165A06A-4105-4A22-9828-A4BEF84DACDC}" name="结束lv" dataDxfId="55"/>
+    <tableColumn id="3" xr3:uid="{7BC03053-038D-41AD-84CE-B60879A78C44}" name="结束" dataDxfId="54"/>
+    <tableColumn id="8" xr3:uid="{18F6AB19-F5E3-4464-85E9-7510B0FF4FBB}" name="总经验(万)" dataDxfId="53">
       <calculatedColumnFormula>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -3798,7 +4026,7 @@
 /10000</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{14E25966-66F6-42F8-8B80-A23CD832D12D}" name="时间min"/>
-    <tableColumn id="5" xr3:uid="{96A93011-DA20-46D8-8102-FAFE34B717F8}" name="exp/h（万）" dataDxfId="57">
+    <tableColumn id="5" xr3:uid="{96A93011-DA20-46D8-8102-FAFE34B717F8}" name="exp/h（万）" dataDxfId="52">
       <calculatedColumnFormula>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -3823,7 +4051,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C593048-19E0-4739-89F7-550D3BCA4024}" name="等级"/>
     <tableColumn id="2" xr3:uid="{7BF93B33-4DA7-41C2-A05A-738673B7622F}" name="升级所需"/>
-    <tableColumn id="3" xr3:uid="{D469DC4A-2E68-429C-9A30-B15320947E61}" name="升级所需(万)" dataDxfId="56">
+    <tableColumn id="3" xr3:uid="{D469DC4A-2E68-429C-9A30-B15320947E61}" name="升级所需(万)" dataDxfId="51">
       <calculatedColumnFormula>经验表[[#This Row],[升级所需]]/10000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3857,13 +4085,13 @@
   </autoFilter>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{698E820D-23C3-4BF8-BEED-4FE313E53471}" name="次数"/>
-    <tableColumn id="2" xr3:uid="{84879E6A-8423-4B05-81FF-8B66F1BA776F}" name="几率" dataDxfId="18">
+    <tableColumn id="2" xr3:uid="{84879E6A-8423-4B05-81FF-8B66F1BA776F}" name="几率" dataDxfId="50">
       <calculatedColumnFormula array="1">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E3DE3ED5-E666-48A5-A699-F069DF88052E}" name="成本价" dataDxfId="17">
+    <tableColumn id="4" xr3:uid="{E3DE3ED5-E666-48A5-A699-F069DF88052E}" name="成本价" dataDxfId="49">
       <calculatedColumnFormula array="1">表1[[#This Row],[次数]]*卷轴参数[卷价值]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7C2768F8-9055-4D23-BE1E-FE8B90B3316B}" name="价值" dataDxfId="16">
+    <tableColumn id="3" xr3:uid="{7C2768F8-9055-4D23-BE1E-FE8B90B3316B}" name="价值" dataDxfId="48">
       <calculatedColumnFormula array="1">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3872,7 +4100,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}" name="卷轴参数" displayName="卷轴参数" ref="B3:E4" totalsRowShown="0" headerRowDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}" name="卷轴参数" displayName="卷轴参数" ref="B3:E4" totalsRowShown="0" headerRowDxfId="47">
   <autoFilter ref="B3:E4" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3880,9 +4108,9 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DC107BBC-406B-498C-BD39-B974C0439AFE}" name="卷概率" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{C61182DF-822A-4A58-AE24-69A976436107}" name="预期成功" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{0F00CCD6-E594-41C1-8347-E43384BB99BE}" name="卷拍卖行价w" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{DC107BBC-406B-498C-BD39-B974C0439AFE}" name="卷概率" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{C61182DF-822A-4A58-AE24-69A976436107}" name="预期成功" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{0F00CCD6-E594-41C1-8347-E43384BB99BE}" name="卷拍卖行价w" dataDxfId="44"/>
     <tableColumn id="3" xr3:uid="{C4E5C7A1-FB81-480E-9C73-32F750E3D67C}" name="卷价值">
       <calculatedColumnFormula array="1">卷轴参数[[#This Row],[卷拍卖行价w]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
@@ -3910,34 +4138,34 @@
   </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{8F08A040-BDE1-42FF-BDBE-7E0E087A8819}" name="卷概率"/>
-    <tableColumn id="8" xr3:uid="{680FF308-0932-4EB2-8486-CA5FEE3FE305}" name="敏捷" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{680FF308-0932-4EB2-8486-CA5FEE3FE305}" name="敏捷" dataDxfId="43"/>
     <tableColumn id="9" xr3:uid="{A70A1698-D188-45CC-BD1C-5EB46D8790A5}" name="命中"/>
     <tableColumn id="10" xr3:uid="{DF40AD0D-56B3-4A4D-8D8F-BCBF9EC1301D}" name="移速"/>
-    <tableColumn id="3" xr3:uid="{A7118FBF-F08B-458A-BB56-4552824BA5FC}" name="单价" dataDxfId="41" totalsRowDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{CA577DD0-7258-45B9-A695-C4171373AE3D}" name="rmb" dataDxfId="39">
+    <tableColumn id="3" xr3:uid="{A7118FBF-F08B-458A-BB56-4552824BA5FC}" name="单价" dataDxfId="42" totalsRowDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{CA577DD0-7258-45B9-A695-C4171373AE3D}" name="rmb" dataDxfId="40">
       <calculatedColumnFormula array="1">表7[[#This Row],[单价]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3BF04BD0-3887-4D5A-9323-13DA842E9180}" name="每点敏捷价格" dataDxfId="38">
+    <tableColumn id="7" xr3:uid="{3BF04BD0-3887-4D5A-9323-13DA842E9180}" name="每点敏捷价格" dataDxfId="39">
       <calculatedColumnFormula>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7B62E845-07A3-42E2-92B2-C00C85BAD066}" name="模拟数量" totalsRowFunction="custom" dataDxfId="37">
+    <tableColumn id="11" xr3:uid="{7B62E845-07A3-42E2-92B2-C00C85BAD066}" name="模拟数量" totalsRowFunction="custom" dataDxfId="38">
       <totalsRowFormula>SUM(表7[模拟数量])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{94F47A8A-0CD2-46BA-BB08-9B69181B3598}" name="成功数量" dataDxfId="36"/>
-    <tableColumn id="13" xr3:uid="{D8FA6D3D-13C9-413D-AA5C-EE25CEB6741F}" name="总敏捷" totalsRowFunction="custom" dataDxfId="35">
+    <tableColumn id="12" xr3:uid="{94F47A8A-0CD2-46BA-BB08-9B69181B3598}" name="成功数量" dataDxfId="37"/>
+    <tableColumn id="13" xr3:uid="{D8FA6D3D-13C9-413D-AA5C-EE25CEB6741F}" name="总敏捷" totalsRowFunction="custom" dataDxfId="36">
       <calculatedColumnFormula>表7[[#This Row],[成功数量]]*表7[[#This Row],[敏捷]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[总敏捷])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{55A7AE7C-6813-49F7-BF22-A6D1331D0893}" name="成本造价" totalsRowFunction="custom" dataDxfId="34">
+    <tableColumn id="14" xr3:uid="{55A7AE7C-6813-49F7-BF22-A6D1331D0893}" name="成本造价" totalsRowFunction="custom" dataDxfId="35">
       <calculatedColumnFormula>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[成本造价])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EE726C5-0F2C-402A-94A6-793B6B1029B8}" name="总价格" totalsRowFunction="custom" dataDxfId="33">
+    <tableColumn id="2" xr3:uid="{7EE726C5-0F2C-402A-94A6-793B6B1029B8}" name="总价格" totalsRowFunction="custom" dataDxfId="34">
       <calculatedColumnFormula>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[总价格])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7DFA1C56-A8FE-42B5-B6C1-2058B28542ED}" name="风险造价" totalsRowFunction="custom" dataDxfId="32">
+    <tableColumn id="15" xr3:uid="{7DFA1C56-A8FE-42B5-B6C1-2058B28542ED}" name="风险造价" totalsRowFunction="custom" dataDxfId="33">
       <calculatedColumnFormula>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[风险造价])</totalsRowFormula>
@@ -4315,7 +4543,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>87</v>
@@ -4323,32 +4551,32 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
-        <v>0.2225</v>
+        <v>0.21560000000000001</v>
       </c>
       <c r="C6">
         <f>金价表[[#This Row],[当前金价1w]]/0.95</f>
-        <v>0.23421052631578948</v>
+        <v>0.22694736842105265</v>
       </c>
       <c r="D6" s="5">
-        <v>3088</v>
+        <v>2400</v>
       </c>
       <c r="E6">
         <f>金价表[[#This Row],[出售商品价格]]*金价表[[#This Row],[当前金价1w]]*0.95</f>
-        <v>652.726</v>
+        <v>491.56800000000004</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I8" cm="1">
         <f t="array" ref="I8">555*金价表[税后金价]</f>
-        <v>129.98684210526315</v>
+        <v>125.95578947368422</v>
       </c>
       <c r="J8" cm="1">
         <f t="array" ref="J8">2888.8888*金价表[当前金价1w]</f>
-        <v>642.77775800000006</v>
+        <v>622.84442528000011</v>
       </c>
       <c r="K8" cm="1">
         <f t="array" ref="K8">2888.8888*金价表[当前金价1w]</f>
-        <v>642.77775800000006</v>
+        <v>622.84442528000011</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -4388,7 +4616,7 @@
       </c>
       <c r="L13" s="3" cm="1">
         <f t="array" ref="L13">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>54.805263157894736</v>
+        <v>53.10568421052632</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -4412,14 +4640,14 @@
       </c>
       <c r="L14" s="3" cm="1">
         <f t="array" ref="L14">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>130.11682894736842</v>
+        <v>126.0817452631579</v>
       </c>
       <c r="M14" s="3">
         <v>1</v>
       </c>
       <c r="N14" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>75.31156578947369</v>
+        <v>72.976061052631579</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
@@ -4436,14 +4664,14 @@
       </c>
       <c r="L15" s="3" cm="1">
         <f t="array" ref="L15">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>231.60816631578948</v>
+        <v>224.42571082105263</v>
       </c>
       <c r="M15" s="3">
         <v>2</v>
       </c>
       <c r="N15" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>88.401451578947373</v>
+        <v>85.660013305263163</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
@@ -4460,14 +4688,14 @@
       </c>
       <c r="L16" s="3" cm="1">
         <f t="array" ref="L16">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>348.71342947368419</v>
+        <v>337.89939503157893</v>
       </c>
       <c r="M16" s="3">
         <v>3</v>
       </c>
       <c r="N16" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>97.969388771929815</v>
+        <v>94.931236940350871</v>
       </c>
     </row>
     <row r="17" spans="8:20" x14ac:dyDescent="0.2">
@@ -4484,14 +4712,14 @@
       </c>
       <c r="L17" cm="1">
         <f t="array" ref="L17">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>398.15789473684214</v>
+        <v>385.8105263157895</v>
       </c>
       <c r="M17">
         <v>4</v>
       </c>
       <c r="N17" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>85.838157894736852</v>
+        <v>83.176210526315799</v>
       </c>
     </row>
     <row r="18" spans="8:20" x14ac:dyDescent="0.2">
@@ -4508,14 +4736,14 @@
       </c>
       <c r="L18" cm="1">
         <f t="array" ref="L18">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>702.63157894736844</v>
+        <v>680.84210526315792</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>129.56526315789475</v>
+        <v>125.54728421052633</v>
       </c>
       <c r="Q18">
         <f>555.555+98</f>
@@ -4523,7 +4751,7 @@
       </c>
       <c r="R18" s="1" cm="1">
         <f t="array" ref="R18">Q18*金价表[当前金价1w]</f>
-        <v>145.4159875</v>
+        <v>140.90645799999999</v>
       </c>
     </row>
     <row r="19" spans="8:20" x14ac:dyDescent="0.2">
@@ -4540,19 +4768,19 @@
       </c>
       <c r="L19" cm="1">
         <f t="array" ref="L19">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>700.02921894736846</v>
+        <v>678.32044766315801</v>
       </c>
       <c r="M19">
         <v>6</v>
       </c>
       <c r="N19" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>107.53732596491228</v>
+        <v>104.20246057543862</v>
       </c>
     </row>
     <row r="20" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H20" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I20" s="2">
         <v>8000</v>
@@ -4564,19 +4792,19 @@
       </c>
       <c r="L20" cm="1">
         <f t="array" ref="L20">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1873.6842105263158</v>
+        <v>1815.5789473684213</v>
       </c>
       <c r="M20">
         <v>7</v>
       </c>
       <c r="N20" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>259.83984962406015</v>
+        <v>251.78189473684213</v>
       </c>
     </row>
     <row r="21" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I21" s="2">
         <v>2666</v>
@@ -4591,7 +4819,7 @@
       </c>
       <c r="L21" cm="1">
         <f t="array" ref="L21">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>624.40526315789475</v>
+        <v>605.04168421052634</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -4603,7 +4831,7 @@
     </row>
     <row r="22" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H22" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I22" s="2">
         <v>2888</v>
@@ -4618,19 +4846,19 @@
       </c>
       <c r="L22" cm="1">
         <f t="array" ref="L22">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>676.4</v>
+        <v>655.42400000000009</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>51.994736842105226</v>
+        <v>50.382315789473751</v>
       </c>
     </row>
     <row r="23" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H23" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I23" s="2">
         <v>7777</v>
@@ -4645,13 +4873,13 @@
       </c>
       <c r="L23" cm="1">
         <f t="array" ref="L23">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1821.4552631578947</v>
+        <v>1764.9696842105263</v>
       </c>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H24" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2">
@@ -4664,19 +4892,19 @@
       </c>
       <c r="L24" cm="1">
         <f t="array" ref="L24">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1179.926587368421</v>
+        <v>1143.3356055578947</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
       <c r="N24" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>277.76066210526312</v>
+        <v>269.14696067368419</v>
       </c>
     </row>
     <row r="25" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -4693,21 +4921,21 @@
       </c>
       <c r="N25" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-208.13508771929824</v>
+        <v>-201.68056140350879</v>
       </c>
       <c r="Q25" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="R25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="26" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H26" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -4724,7 +4952,7 @@
       </c>
       <c r="N26" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-156.10131578947369</v>
+        <v>-151.26042105263159</v>
       </c>
       <c r="Q26">
         <v>200</v>
@@ -4739,7 +4967,7 @@
     </row>
     <row r="27" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H27" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -4756,7 +4984,7 @@
       </c>
       <c r="N27" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-124.88105263157895</v>
+        <v>-121.00833684210527</v>
       </c>
       <c r="R27" s="1">
         <f>SUM(Q26:S26)</f>
@@ -4764,12 +4992,12 @@
       </c>
       <c r="T27" cm="1">
         <f t="array" ref="T27">R27/金价表[税后金价]</f>
-        <v>1370.5617977528088</v>
+        <v>1414.4248608534322</v>
       </c>
     </row>
     <row r="28" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H28" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -4786,12 +5014,12 @@
       </c>
       <c r="N28" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-89.200751879699254</v>
+        <v>-86.434526315789483</v>
       </c>
     </row>
     <row r="29" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -4808,22 +5036,22 @@
       </c>
       <c r="N29" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-78.050657894736844</v>
+        <v>-75.630210526315793</v>
       </c>
       <c r="Q29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R29">
         <f>4*140</f>
         <v>560</v>
       </c>
       <c r="S29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H30" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -4840,10 +5068,10 @@
       </c>
       <c r="N30" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-69.378362573099423</v>
+        <v>-67.226853801169597</v>
       </c>
       <c r="Q30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R30" s="1">
         <f>L28-R29</f>
@@ -4864,7 +5092,7 @@
       </c>
       <c r="L31" cm="1">
         <f t="array" ref="L31">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>55.273684210526319</v>
+        <v>53.559578947368422</v>
       </c>
     </row>
     <row r="32" spans="8:20" x14ac:dyDescent="0.2">
@@ -4881,7 +5109,7 @@
       </c>
       <c r="L32" cm="1">
         <f t="array" ref="L32">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>90.405263157894737</v>
+        <v>87.601684210526315</v>
       </c>
       <c r="R32">
         <f>2200/0.35</f>
@@ -4902,7 +5130,7 @@
       </c>
       <c r="L33" cm="1">
         <f t="array" ref="L33">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>26.7</v>
+        <v>25.872000000000003</v>
       </c>
     </row>
     <row r="34" spans="8:17" x14ac:dyDescent="0.2">
@@ -4919,7 +5147,7 @@
       </c>
       <c r="L34" cm="1">
         <f t="array" ref="L34">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>76.352631578947367</v>
+        <v>73.984842105263169</v>
       </c>
     </row>
     <row r="41" spans="8:17" x14ac:dyDescent="0.2">
@@ -4997,7 +5225,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
@@ -5439,7 +5667,7 @@
         <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>
@@ -6177,7 +6405,7 @@
         <v>46.844999999999999</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F47" s="2">
         <v>53</v>
@@ -6229,7 +6457,7 @@
         <v>51.042000000000002</v>
       </c>
       <c r="E48" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F48" s="2">
         <v>55</v>
@@ -6280,7 +6508,7 @@
         <v>55.567999999999998</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F49" s="2">
         <v>56</v>
@@ -6332,7 +6560,7 @@
         <v>60.441600000000001</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F50" s="2">
         <v>59</v>
@@ -6384,7 +6612,7 @@
         <v>65.52</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F51" s="2">
         <v>61</v>
@@ -6436,7 +6664,7 @@
         <v>70.971599999999995</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F52" s="2">
         <v>70</v>
@@ -6488,7 +6716,7 @@
         <v>74.860799999999998</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F53" s="2">
         <v>70</v>
@@ -6540,7 +6768,7 @@
         <v>78.963099999999997</v>
       </c>
       <c r="E54" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F54" s="2">
         <v>71</v>
@@ -6591,7 +6819,7 @@
         <v>83.290199999999999</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F55" s="2">
         <v>71</v>
@@ -6631,7 +6859,7 @@
         <v>28.725629999999999</v>
       </c>
       <c r="S55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
@@ -6646,7 +6874,7 @@
         <v>87.854500000000002</v>
       </c>
       <c r="E56" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F56" s="2">
         <v>73</v>
@@ -6697,7 +6925,7 @@
         <v>92.668899999999994</v>
       </c>
       <c r="E57" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F57" s="2">
         <v>21</v>
@@ -6748,7 +6976,7 @@
         <v>97.747100000000003</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F58" s="2">
         <v>73</v>
@@ -6799,7 +7027,7 @@
         <v>103.1036</v>
       </c>
       <c r="E59" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F59" s="2">
         <v>73</v>
@@ -6850,7 +7078,7 @@
         <v>108.75360000000001</v>
       </c>
       <c r="E60" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F60" s="2">
         <v>74</v>
@@ -6901,7 +7129,7 @@
         <v>114.7132</v>
       </c>
       <c r="E61" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F61" s="2">
         <v>74</v>
@@ -6952,7 +7180,7 @@
         <v>120.99939999999999</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F62" s="2">
         <v>74</v>
@@ -7004,7 +7232,7 @@
         <v>127.6301</v>
       </c>
       <c r="E63" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F63" s="2">
         <v>75</v>
@@ -7055,7 +7283,7 @@
         <v>134.6242</v>
       </c>
       <c r="E64" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F64" s="2">
         <v>75</v>
@@ -7107,7 +7335,7 @@
         <v>142.0016</v>
       </c>
       <c r="E65" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F65" s="2">
         <v>77</v>
@@ -7158,7 +7386,7 @@
         <v>149.78319999999999</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F66" s="2">
         <v>77</v>
@@ -7209,6 +7437,45 @@
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>157.9913</v>
       </c>
+      <c r="E67" t="s">
+        <v>142</v>
+      </c>
+      <c r="F67" s="2">
+        <v>80</v>
+      </c>
+      <c r="G67" s="2">
+        <v>2622632</v>
+      </c>
+      <c r="H67" s="2">
+        <v>80</v>
+      </c>
+      <c r="I67" s="2">
+        <v>2708984</v>
+      </c>
+      <c r="J67" s="15">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>8.6351999999999993</v>
+      </c>
+      <c r="K67">
+        <v>17.5</v>
+      </c>
+      <c r="L67" s="16">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>29.606400000000001</v>
+      </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68">
@@ -7221,6 +7488,44 @@
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>166.64920000000001</v>
       </c>
+      <c r="E68" t="s">
+        <v>186</v>
+      </c>
+      <c r="F68" s="2">
+        <v>81</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2">
+        <v>90</v>
+      </c>
+      <c r="I68" s="2">
+        <v>0</v>
+      </c>
+      <c r="J68" s="15">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>4172.4310999999998</v>
+      </c>
+      <c r="K68">
+        <f>60*40*4</f>
+        <v>9600</v>
+      </c>
+      <c r="L68" s="16">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>26.077694375</v>
+      </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69">
@@ -7232,6 +7537,38 @@
       <c r="C69">
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>175.78149999999999</v>
+      </c>
+      <c r="E69" t="s">
+        <v>187</v>
+      </c>
+      <c r="F69" s="2">
+        <v>81</v>
+      </c>
+      <c r="G69" s="2">
+        <v>2042534</v>
+      </c>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="15">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>12703.7359</v>
+      </c>
+      <c r="L69" s="16" t="e">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -7682,7 +8019,7 @@
       </c>
       <c r="E4" cm="1">
         <f t="array" ref="E4">卷轴参数[[#This Row],[卷拍卖行价w]]*金价表[税后金价]</f>
-        <v>16.394736842105264</v>
+        <v>15.886315789473686</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -7693,7 +8030,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -7709,7 +8046,7 @@
       </c>
       <c r="D7" cm="1">
         <f t="array" ref="D7">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>16.394736842105264</v>
+        <v>15.886315789473686</v>
       </c>
       <c r="E7" t="str" cm="1">
         <f t="array" ref="E7">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -7726,7 +8063,7 @@
       </c>
       <c r="D8" cm="1">
         <f t="array" ref="D8">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>32.789473684210527</v>
+        <v>31.772631578947372</v>
       </c>
       <c r="E8" t="str" cm="1">
         <f t="array" ref="E8">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -7743,7 +8080,7 @@
       </c>
       <c r="D9" cm="1">
         <f t="array" ref="D9">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>49.184210526315795</v>
+        <v>47.65894736842106</v>
       </c>
       <c r="E9" t="str" cm="1">
         <f t="array" ref="E9">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -7760,7 +8097,7 @@
       </c>
       <c r="D10" cm="1">
         <f t="array" ref="D10">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>65.578947368421055</v>
+        <v>63.545263157894745</v>
       </c>
       <c r="E10" t="str" cm="1">
         <f t="array" ref="E10">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -7777,11 +8114,11 @@
       </c>
       <c r="D11" cm="1">
         <f t="array" ref="D11">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>81.973684210526315</v>
+        <v>79.431578947368436</v>
       </c>
       <c r="E11" cm="1">
         <f t="array" ref="E11">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>1054.1883257526526</v>
+        <v>1021.4966428416715</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -7794,11 +8131,11 @@
       </c>
       <c r="D12" cm="1">
         <f t="array" ref="D12">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>98.368421052631589</v>
+        <v>95.317894736842121</v>
       </c>
       <c r="E12" cm="1">
         <f t="array" ref="E12">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>421.67533030106142</v>
+        <v>408.59865713666903</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -7811,11 +8148,11 @@
       </c>
       <c r="D13" cm="1">
         <f t="array" ref="D13">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>114.76315789473685</v>
+        <v>111.2042105263158</v>
       </c>
       <c r="E13" cm="1">
         <f t="array" ref="E13">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>273.30808445439169</v>
+        <v>264.83246295895214</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -7828,11 +8165,11 @@
       </c>
       <c r="D14" cm="1">
         <f t="array" ref="D14">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>131.15789473684211</v>
+        <v>127.09052631578949</v>
       </c>
       <c r="E14" cm="1">
         <f t="array" ref="E14">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>220.77242424139337</v>
+        <v>213.92599850087379</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -7845,11 +8182,11 @@
       </c>
       <c r="D15" cm="1">
         <f t="array" ref="D15">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>147.55263157894737</v>
+        <v>142.97684210526319</v>
       </c>
       <c r="E15" cm="1">
         <f t="array" ref="E15">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>201.18097819707123</v>
+        <v>194.94210741253286</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -7862,11 +8199,11 @@
       </c>
       <c r="D16" cm="1">
         <f t="array" ref="D16">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>163.94736842105263</v>
+        <v>158.86315789473687</v>
       </c>
       <c r="E16" cm="1">
         <f t="array" ref="E16">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>196.63583836076293</v>
+        <v>190.53791798013705</v>
       </c>
     </row>
     <row r="28" spans="3:15" x14ac:dyDescent="0.2">
@@ -7928,12 +8265,12 @@
       </c>
       <c r="H29" cm="1">
         <f t="array" ref="H29">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>4.45</v>
+        <v>4.3120000000000003</v>
       </c>
       <c r="I29">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>8.9</v>
+        <v>8.6240000000000006</v>
       </c>
       <c r="J29" s="2">
         <v>6</v>
@@ -7947,16 +8284,16 @@
       </c>
       <c r="M29">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
-        <v>26.700000000000003</v>
+        <v>25.872</v>
       </c>
       <c r="N29">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
-        <v>133.5</v>
+        <v>129.36000000000001</v>
       </c>
       <c r="O29">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
-        <v>1684.5425867507856</v>
+        <v>1632.3028391167161</v>
       </c>
     </row>
     <row r="30" spans="3:15" x14ac:dyDescent="0.2">
@@ -7975,12 +8312,12 @@
       </c>
       <c r="H30" cm="1">
         <f t="array" ref="H30">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>32.086842105263159</v>
+        <v>31.091789473684212</v>
       </c>
       <c r="I30">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>26.739035087719301</v>
+        <v>25.909824561403511</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -8021,12 +8358,12 @@
       </c>
       <c r="H31" cm="1">
         <f t="array" ref="H31">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>0.81973684210526321</v>
+        <v>0.79431578947368431</v>
       </c>
       <c r="I31">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>0.81973684210526321</v>
+        <v>0.79431578947368431</v>
       </c>
       <c r="J31" s="2">
         <v>4</v>
@@ -8041,16 +8378,16 @@
       </c>
       <c r="M31">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
-        <v>3.2789473684210528</v>
+        <v>3.1772631578947372</v>
       </c>
       <c r="N31">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
-        <v>3.2789473684210528</v>
+        <v>3.1772631578947372</v>
       </c>
       <c r="O31">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
-        <v>3.2789473684210528</v>
+        <v>3.1772631578947372</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.2">
@@ -8065,11 +8402,11 @@
       </c>
       <c r="M32">
         <f>SUM(表7[成本造价])</f>
-        <v>29.978947368421057</v>
+        <v>29.049263157894735</v>
       </c>
       <c r="N32">
         <f>SUM(表7[总价格])</f>
-        <v>136.77894736842106</v>
+        <v>132.53726315789476</v>
       </c>
       <c r="O32" t="e">
         <f>SUM(表7[风险造价])</f>
@@ -8132,12 +8469,12 @@
       </c>
       <c r="H40" cm="1">
         <f t="array" ref="H40">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>4.45</v>
+        <v>4.3120000000000003</v>
       </c>
       <c r="I40">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>8.9</v>
+        <v>8.6240000000000006</v>
       </c>
       <c r="J40" s="2">
         <v>7</v>
@@ -8151,12 +8488,12 @@
       </c>
       <c r="M40">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
-        <v>31.150000000000002</v>
+        <v>30.184000000000001</v>
       </c>
       <c r="N40">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
-        <v>346.41807601736014</v>
+        <v>335.67522332288917</v>
       </c>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.2">
@@ -8175,12 +8512,12 @@
       </c>
       <c r="H41" cm="1">
         <f t="array" ref="H41">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>32.086842105263159</v>
+        <v>31.091789473684212</v>
       </c>
       <c r="I41">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>26.739035087719301</v>
+        <v>25.909824561403511</v>
       </c>
       <c r="J41" s="2">
         <v>3</v>
@@ -8194,12 +8531,12 @@
       </c>
       <c r="M41">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
-        <v>96.260526315789477</v>
+        <v>93.275368421052633</v>
       </c>
       <c r="N41">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
-        <v>123.7918291098116</v>
+        <v>119.95289148797924</v>
       </c>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.2">
@@ -8216,12 +8553,12 @@
       </c>
       <c r="H42" cm="1">
         <f t="array" ref="H42">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>0.81973684210526321</v>
+        <v>0.79431578947368431</v>
       </c>
       <c r="I42">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>0.81973684210526321</v>
+        <v>0.79431578947368431</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
@@ -8256,11 +8593,11 @@
       </c>
       <c r="M43">
         <f>SUM(表7_9[造价])</f>
-        <v>127.41052631578948</v>
+        <v>123.45936842105263</v>
       </c>
       <c r="N43">
         <f>SUM(表7_9[风险造价])</f>
-        <v>470.20990512717174</v>
+        <v>455.6281148108684</v>
       </c>
     </row>
   </sheetData>
@@ -8278,7 +8615,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C898E4F5-1983-43C5-86AB-660F992C424E}">
-  <dimension ref="B2:U37"/>
+  <dimension ref="B2:X38"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="17.25" customWidth="1"/>
@@ -8286,13 +8623,13 @@
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="13" width="10.25" customWidth="1"/>
     <col min="14" max="14" width="13.875" customWidth="1"/>
-    <col min="15" max="18" width="13.5" customWidth="1"/>
-    <col min="19" max="19" width="13.875" customWidth="1"/>
-    <col min="20" max="20" width="13.5" customWidth="1"/>
-    <col min="21" max="22" width="12.5" customWidth="1"/>
-    <col min="23" max="23" width="16.625" customWidth="1"/>
-    <col min="24" max="24" width="14.875" customWidth="1"/>
-    <col min="25" max="28" width="19" customWidth="1"/>
+    <col min="15" max="20" width="13.5" customWidth="1"/>
+    <col min="21" max="21" width="13.875" customWidth="1"/>
+    <col min="22" max="22" width="13.5" customWidth="1"/>
+    <col min="23" max="24" width="12.5" customWidth="1"/>
+    <col min="25" max="25" width="16.625" customWidth="1"/>
+    <col min="26" max="26" width="14.875" customWidth="1"/>
+    <col min="27" max="30" width="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.2">
@@ -8336,19 +8673,19 @@
         <v>83</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>71</v>
@@ -8422,1072 +8759,1568 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="20" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:24" x14ac:dyDescent="0.2">
       <c r="L20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="22" spans="4:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="4:24" x14ac:dyDescent="0.2">
       <c r="L22" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="4:21" x14ac:dyDescent="0.2">
-      <c r="D25" t="s">
+    <row r="25" spans="4:24" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="D25" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="P25" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T25" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="U25" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="V25" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="W25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="4:24" x14ac:dyDescent="0.2">
+      <c r="D26" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" s="2">
+        <v>43</v>
+      </c>
+      <c r="F26" s="2">
+        <v>23</v>
+      </c>
+      <c r="G26" s="2">
+        <v>0</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2</v>
+      </c>
+      <c r="I26" s="10">
+        <v>5</v>
+      </c>
+      <c r="J26" s="10">
         <v>104</v>
       </c>
-      <c r="F25" t="s">
-        <v>162</v>
-      </c>
-      <c r="G25" t="s">
-        <v>163</v>
-      </c>
-      <c r="H25" t="s">
-        <v>164</v>
-      </c>
-      <c r="I25" t="s">
-        <v>165</v>
-      </c>
-      <c r="J25" t="s">
-        <v>68</v>
-      </c>
-      <c r="K25" t="s">
-        <v>38</v>
-      </c>
-      <c r="L25" t="s">
-        <v>161</v>
-      </c>
-      <c r="M25" t="s">
-        <v>84</v>
-      </c>
-      <c r="N25" t="s">
-        <v>128</v>
-      </c>
-      <c r="O25" t="s">
-        <v>129</v>
-      </c>
-      <c r="P25" t="s">
-        <v>166</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>167</v>
-      </c>
-      <c r="R25" t="s">
-        <v>75</v>
-      </c>
-      <c r="S25" t="s">
-        <v>74</v>
-      </c>
-      <c r="T25" t="s">
-        <v>80</v>
-      </c>
-      <c r="U25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="26" spans="4:21" x14ac:dyDescent="0.2">
-      <c r="D26" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E26" s="8">
-        <v>0</v>
-      </c>
-      <c r="F26" s="2">
-        <v>44</v>
-      </c>
-      <c r="G26" s="2">
-        <v>23</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>2</v>
-      </c>
-      <c r="J26" s="10">
+      <c r="K26" s="10">
         <v>6</v>
       </c>
-      <c r="K26" s="10">
-        <v>110</v>
-      </c>
       <c r="L26" s="10">
-        <v>6</v>
-      </c>
-      <c r="M26" s="10">
-        <v>338</v>
-      </c>
-      <c r="N26" cm="1">
-        <f t="array" ref="N26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M26" cm="1">
+        <f t="array" ref="M26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>919.63199999999995</v>
-      </c>
-      <c r="O26" cm="1">
-        <f t="array" ref="O26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>943.16</v>
+      </c>
+      <c r="N26" cm="1">
+        <f t="array" ref="N26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>533.41967999999997</v>
-      </c>
-      <c r="P26" cm="1">
-        <f t="array" ref="P26">常量表[双飞斩运气系数max]
+        <v>543.40160000000003</v>
+      </c>
+      <c r="O26" s="12" cm="1">
+        <f t="array" ref="O26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.4705882352941124E-2</v>
+      </c>
+      <c r="P26" s="12" cm="1">
+        <f t="array" ref="P26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460817E-2</v>
+      </c>
+      <c r="Q26" cm="1">
+        <f t="array" ref="Q26">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1749.1499999999999</v>
-      </c>
-      <c r="Q26" cm="1">
-        <f t="array" ref="Q26">常量表[双飞斩运气系数min]
+        <v>1810.5</v>
+      </c>
+      <c r="R26" cm="1">
+        <f t="array" ref="R26">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>874.57499999999993</v>
-      </c>
-      <c r="R26" cm="1">
-        <f t="array" ref="R26">常量表[双飞斩运气系数max]
+        <v>905.25</v>
+      </c>
+      <c r="S26" cm="1">
+        <f t="array" ref="S26">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2915.25</v>
-      </c>
-      <c r="S26" cm="1">
-        <f t="array" ref="S26">常量表[双飞斩运气系数min]
+        <v>3017.5</v>
+      </c>
+      <c r="T26" cm="1">
+        <f t="array" ref="T26">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1457.625</v>
-      </c>
-      <c r="T26" s="1" cm="1">
-        <f t="array" ref="T26">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2413.7249999999999</v>
-      </c>
-      <c r="U26" s="1" cm="1">
-        <f t="array" ref="U26">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1059.8625</v>
-      </c>
-    </row>
-    <row r="27" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1508.75</v>
+      </c>
+      <c r="U26" s="14" cm="1">
+        <f t="array" ref="U26">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4705882352941124E-2</v>
+      </c>
+      <c r="V26" s="14" cm="1">
+        <f t="array" ref="V26">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W26" s="1" cm="1">
+        <f t="array" ref="W26">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2505.75</v>
+      </c>
+      <c r="X26" s="1" cm="1">
+        <f t="array" ref="X26">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1105.875</v>
+      </c>
+    </row>
+    <row r="27" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D27" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="E27" s="8">
+        <v>169</v>
+      </c>
+      <c r="E27" s="2">
+        <v>43</v>
+      </c>
+      <c r="F27" s="2">
+        <v>23</v>
+      </c>
+      <c r="G27" s="2">
         <v>1</v>
       </c>
-      <c r="F27" s="2">
-        <v>44</v>
-      </c>
-      <c r="G27" s="2">
-        <v>23</v>
-      </c>
       <c r="H27" s="2">
-        <v>1</v>
-      </c>
-      <c r="I27" s="2">
         <v>2</v>
       </c>
+      <c r="I27" s="10">
+        <v>5</v>
+      </c>
       <c r="J27" s="10">
+        <v>104</v>
+      </c>
+      <c r="K27" s="10">
         <v>6</v>
       </c>
-      <c r="K27" s="10">
-        <v>110</v>
-      </c>
       <c r="L27" s="10">
-        <v>6</v>
-      </c>
-      <c r="M27" s="10">
-        <v>338</v>
-      </c>
-      <c r="N27" cm="1">
-        <f t="array" ref="N27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M27" cm="1">
+        <f t="array" ref="M27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>932.96</v>
-      </c>
-      <c r="O27" cm="1">
-        <f t="array" ref="O27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>957.03</v>
+      </c>
+      <c r="N27" cm="1">
+        <f t="array" ref="N27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>541.15039999999999</v>
-      </c>
-      <c r="P27" cm="1">
-        <f t="array" ref="P27">常量表[双飞斩运气系数max]
+        <v>551.39279999999997</v>
+      </c>
+      <c r="O27" s="12" cm="1">
+        <f t="array" ref="O27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.449275362318847E-2</v>
+      </c>
+      <c r="P27" s="12" cm="1">
+        <f t="array" ref="P27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460817E-2</v>
+      </c>
+      <c r="Q27" cm="1">
+        <f t="array" ref="Q27">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1774.5</v>
-      </c>
-      <c r="Q27" cm="1">
-        <f t="array" ref="Q27">常量表[双飞斩运气系数min]
+        <v>1837.125</v>
+      </c>
+      <c r="R27" cm="1">
+        <f t="array" ref="R27">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>887.25</v>
-      </c>
-      <c r="R27" cm="1">
-        <f t="array" ref="R27">常量表[双飞斩运气系数max]
+        <v>918.5625</v>
+      </c>
+      <c r="S27" cm="1">
+        <f t="array" ref="S27">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2957.5</v>
-      </c>
-      <c r="S27" cm="1">
-        <f t="array" ref="S27">常量表[双飞斩运气系数min]
+        <v>3061.875</v>
+      </c>
+      <c r="T27" cm="1">
+        <f t="array" ref="T27">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1478.75</v>
-      </c>
-      <c r="T27" s="1" cm="1">
-        <f t="array" ref="T27">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2451.75</v>
-      </c>
-      <c r="U27" s="1" cm="1">
-        <f t="array" ref="U27">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1078.875</v>
-      </c>
-    </row>
-    <row r="28" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1530.9375</v>
+      </c>
+      <c r="U27" s="14" cm="1">
+        <f t="array" ref="U27">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.449275362318847E-2</v>
+      </c>
+      <c r="V27" s="14" cm="1">
+        <f t="array" ref="V27">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W27" s="1" cm="1">
+        <f t="array" ref="W27">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2545.6875</v>
+      </c>
+      <c r="X27" s="1" cm="1">
+        <f t="array" ref="X27">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1125.84375</v>
+      </c>
+    </row>
+    <row r="28" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D28" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E28" s="8">
+        <v>170</v>
+      </c>
+      <c r="E28" s="2">
+        <v>43</v>
+      </c>
+      <c r="F28" s="2">
+        <v>23</v>
+      </c>
+      <c r="G28" s="2">
         <v>2</v>
-      </c>
-      <c r="F28" s="2">
-        <v>44</v>
-      </c>
-      <c r="G28" s="2">
-        <v>23</v>
       </c>
       <c r="H28" s="2">
         <v>2</v>
       </c>
-      <c r="I28" s="2">
-        <v>2</v>
+      <c r="I28" s="10">
+        <v>5</v>
       </c>
       <c r="J28" s="10">
+        <v>104</v>
+      </c>
+      <c r="K28" s="10">
         <v>6</v>
       </c>
-      <c r="K28" s="10">
-        <v>110</v>
-      </c>
       <c r="L28" s="10">
-        <v>6</v>
-      </c>
-      <c r="M28" s="10">
-        <v>338</v>
-      </c>
-      <c r="N28" cm="1">
-        <f t="array" ref="N28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M28" cm="1">
+        <f t="array" ref="M28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>946.28800000000001</v>
-      </c>
-      <c r="O28" cm="1">
-        <f t="array" ref="O28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>970.9</v>
+      </c>
+      <c r="N28" cm="1">
+        <f t="array" ref="N28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>548.88112000000001</v>
-      </c>
-      <c r="P28" cm="1">
-        <f t="array" ref="P28">常量表[双飞斩运气系数max]
+        <v>559.38400000000001</v>
+      </c>
+      <c r="O28" s="12" cm="1">
+        <f t="array" ref="O28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.4285714285714235E-2</v>
+      </c>
+      <c r="P28" s="12" cm="1">
+        <f t="array" ref="P28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460817E-2</v>
+      </c>
+      <c r="Q28" cm="1">
+        <f t="array" ref="Q28">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1799.8500000000001</v>
-      </c>
-      <c r="Q28" cm="1">
-        <f t="array" ref="Q28">常量表[双飞斩运气系数min]
+        <v>1863.75</v>
+      </c>
+      <c r="R28" cm="1">
+        <f t="array" ref="R28">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>899.92500000000007</v>
-      </c>
-      <c r="R28" cm="1">
-        <f t="array" ref="R28">常量表[双飞斩运气系数max]
+        <v>931.875</v>
+      </c>
+      <c r="S28" cm="1">
+        <f t="array" ref="S28">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>2999.75</v>
-      </c>
-      <c r="S28" cm="1">
-        <f t="array" ref="S28">常量表[双飞斩运气系数min]
+        <v>3106.25</v>
+      </c>
+      <c r="T28" cm="1">
+        <f t="array" ref="T28">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1499.875</v>
-      </c>
-      <c r="T28" s="1" cm="1">
-        <f t="array" ref="T28">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2489.7750000000001</v>
-      </c>
-      <c r="U28" s="1" cm="1">
-        <f t="array" ref="U28">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1097.8875</v>
-      </c>
-    </row>
-    <row r="29" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1553.125</v>
+      </c>
+      <c r="U28" s="14" cm="1">
+        <f t="array" ref="U28">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4285714285714235E-2</v>
+      </c>
+      <c r="V28" s="14" cm="1">
+        <f t="array" ref="V28">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W28" s="1" cm="1">
+        <f t="array" ref="W28">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2585.625</v>
+      </c>
+      <c r="X28" s="1" cm="1">
+        <f t="array" ref="X28">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1145.8125</v>
+      </c>
+    </row>
+    <row r="29" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D29" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="E29" s="8">
+        <v>171</v>
+      </c>
+      <c r="E29" s="2">
+        <v>43</v>
+      </c>
+      <c r="F29" s="2">
+        <v>23</v>
+      </c>
+      <c r="G29" s="2">
         <v>3</v>
       </c>
-      <c r="F29" s="2">
-        <v>44</v>
-      </c>
-      <c r="G29" s="2">
-        <v>23</v>
-      </c>
       <c r="H29" s="2">
-        <v>3</v>
-      </c>
-      <c r="I29" s="2">
         <v>2</v>
       </c>
+      <c r="I29" s="10">
+        <v>5</v>
+      </c>
       <c r="J29" s="10">
+        <v>104</v>
+      </c>
+      <c r="K29" s="10">
         <v>6</v>
       </c>
-      <c r="K29" s="10">
-        <v>110</v>
-      </c>
       <c r="L29" s="10">
-        <v>6</v>
-      </c>
-      <c r="M29" s="10">
-        <v>338</v>
-      </c>
-      <c r="N29" cm="1">
-        <f t="array" ref="N29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M29" cm="1">
+        <f t="array" ref="M29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>959.61599999999987</v>
-      </c>
-      <c r="O29" cm="1">
-        <f t="array" ref="O29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>984.77</v>
+      </c>
+      <c r="N29" cm="1">
+        <f t="array" ref="N29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>556.61184000000003</v>
-      </c>
-      <c r="P29" cm="1">
-        <f t="array" ref="P29">常量表[双飞斩运气系数max]
+        <v>567.37519999999995</v>
+      </c>
+      <c r="O29" s="12" cm="1">
+        <f t="array" ref="O29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="P29" s="12" cm="1">
+        <f t="array" ref="P29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460595E-2</v>
+      </c>
+      <c r="Q29" cm="1">
+        <f t="array" ref="Q29">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1825.1999999999998</v>
-      </c>
-      <c r="Q29" cm="1">
-        <f t="array" ref="Q29">常量表[双飞斩运气系数min]
+        <v>1890.375</v>
+      </c>
+      <c r="R29" cm="1">
+        <f t="array" ref="R29">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>912.59999999999991</v>
-      </c>
-      <c r="R29" cm="1">
-        <f t="array" ref="R29">常量表[双飞斩运气系数max]
+        <v>945.1875</v>
+      </c>
+      <c r="S29" cm="1">
+        <f t="array" ref="S29">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3042</v>
-      </c>
-      <c r="S29" cm="1">
-        <f t="array" ref="S29">常量表[双飞斩运气系数min]
+        <v>3150.625</v>
+      </c>
+      <c r="T29" cm="1">
+        <f t="array" ref="T29">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1521</v>
-      </c>
-      <c r="T29" s="1" cm="1">
-        <f t="array" ref="T29">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2527.8000000000002</v>
-      </c>
-      <c r="U29" s="1" cm="1">
-        <f t="array" ref="U29">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1116.9000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1575.3125</v>
+      </c>
+      <c r="U29" s="14" cm="1">
+        <f t="array" ref="U29">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="V29" s="14" cm="1">
+        <f t="array" ref="V29">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W29" s="1" cm="1">
+        <f t="array" ref="W29">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2625.5625</v>
+      </c>
+      <c r="X29" s="1" cm="1">
+        <f t="array" ref="X29">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1165.78125</v>
+      </c>
+    </row>
+    <row r="30" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D30" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="E30" s="8">
+        <v>173</v>
+      </c>
+      <c r="E30" s="2">
+        <v>43</v>
+      </c>
+      <c r="F30" s="2">
+        <v>23</v>
+      </c>
+      <c r="G30" s="2">
         <v>4</v>
       </c>
-      <c r="F30" s="2">
-        <v>44</v>
-      </c>
-      <c r="G30" s="2">
-        <v>23</v>
-      </c>
       <c r="H30" s="2">
-        <v>4</v>
-      </c>
-      <c r="I30" s="2">
         <v>2</v>
       </c>
+      <c r="I30" s="10">
+        <v>5</v>
+      </c>
       <c r="J30" s="10">
+        <v>104</v>
+      </c>
+      <c r="K30" s="10">
         <v>6</v>
       </c>
-      <c r="K30" s="10">
-        <v>110</v>
-      </c>
       <c r="L30" s="10">
-        <v>6</v>
-      </c>
-      <c r="M30" s="10">
-        <v>338</v>
-      </c>
-      <c r="N30" cm="1">
-        <f t="array" ref="N30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M30" cm="1">
+        <f t="array" ref="M30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>972.94399999999996</v>
-      </c>
-      <c r="O30" cm="1">
-        <f t="array" ref="O30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>998.64</v>
+      </c>
+      <c r="N30" cm="1">
+        <f t="array" ref="N30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>564.34256000000005</v>
-      </c>
-      <c r="P30" cm="1">
-        <f t="array" ref="P30">常量表[双飞斩运气系数max]
+        <v>575.3664</v>
+      </c>
+      <c r="O30" s="12" cm="1">
+        <f t="array" ref="O30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.388888888888884E-2</v>
+      </c>
+      <c r="P30" s="12" cm="1">
+        <f t="array" ref="P30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460817E-2</v>
+      </c>
+      <c r="Q30" cm="1">
+        <f t="array" ref="Q30">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1850.5500000000002</v>
-      </c>
-      <c r="Q30" cm="1">
-        <f t="array" ref="Q30">常量表[双飞斩运气系数min]
+        <v>1917</v>
+      </c>
+      <c r="R30" cm="1">
+        <f t="array" ref="R30">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>925.27500000000009</v>
-      </c>
-      <c r="R30" cm="1">
-        <f t="array" ref="R30">常量表[双飞斩运气系数max]
+        <v>958.5</v>
+      </c>
+      <c r="S30" cm="1">
+        <f t="array" ref="S30">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3084.25</v>
-      </c>
-      <c r="S30" cm="1">
-        <f t="array" ref="S30">常量表[双飞斩运气系数min]
+        <v>3195</v>
+      </c>
+      <c r="T30" cm="1">
+        <f t="array" ref="T30">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1542.125</v>
-      </c>
-      <c r="T30" s="1" cm="1">
-        <f t="array" ref="T30">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2565.8250000000003</v>
-      </c>
-      <c r="U30" s="1" cm="1">
-        <f t="array" ref="U30">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1135.9125000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1597.5</v>
+      </c>
+      <c r="U30" s="14" cm="1">
+        <f t="array" ref="U30">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.388888888888884E-2</v>
+      </c>
+      <c r="V30" s="14" cm="1">
+        <f t="array" ref="V30">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W30" s="1" cm="1">
+        <f t="array" ref="W30">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2665.5</v>
+      </c>
+      <c r="X30" s="1" cm="1">
+        <f t="array" ref="X30">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1185.75</v>
+      </c>
+    </row>
+    <row r="31" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D31" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E31" s="8">
+        <v>174</v>
+      </c>
+      <c r="E31" s="2">
+        <v>43</v>
+      </c>
+      <c r="F31" s="2">
+        <v>23</v>
+      </c>
+      <c r="G31" s="2">
         <v>5</v>
       </c>
-      <c r="F31" s="2">
-        <v>44</v>
-      </c>
-      <c r="G31" s="2">
-        <v>23</v>
-      </c>
       <c r="H31" s="2">
+        <v>2</v>
+      </c>
+      <c r="I31" s="10">
         <v>5</v>
       </c>
-      <c r="I31" s="2">
-        <v>2</v>
-      </c>
       <c r="J31" s="10">
+        <v>104</v>
+      </c>
+      <c r="K31" s="10">
         <v>6</v>
       </c>
-      <c r="K31" s="10">
-        <v>110</v>
-      </c>
       <c r="L31" s="10">
-        <v>6</v>
-      </c>
-      <c r="M31" s="10">
-        <v>338</v>
-      </c>
-      <c r="N31" cm="1">
-        <f t="array" ref="N31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M31" cm="1">
+        <f t="array" ref="M31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>986.27199999999993</v>
-      </c>
-      <c r="O31" cm="1">
-        <f t="array" ref="O31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>1012.51</v>
+      </c>
+      <c r="N31" cm="1">
+        <f t="array" ref="N31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>572.07328000000007</v>
-      </c>
-      <c r="P31" cm="1">
-        <f t="array" ref="P31">常量表[双飞斩运气系数max]
+        <v>583.35760000000005</v>
+      </c>
+      <c r="O31" s="12" cm="1">
+        <f t="array" ref="O31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.3698630136986356E-2</v>
+      </c>
+      <c r="P31" s="12" cm="1">
+        <f t="array" ref="P31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460817E-2</v>
+      </c>
+      <c r="Q31" cm="1">
+        <f t="array" ref="Q31">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1875.8999999999999</v>
-      </c>
-      <c r="Q31" cm="1">
-        <f t="array" ref="Q31">常量表[双飞斩运气系数min]
+        <v>1943.625</v>
+      </c>
+      <c r="R31" cm="1">
+        <f t="array" ref="R31">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>937.94999999999993</v>
-      </c>
-      <c r="R31" cm="1">
-        <f t="array" ref="R31">常量表[双飞斩运气系数max]
+        <v>971.8125</v>
+      </c>
+      <c r="S31" cm="1">
+        <f t="array" ref="S31">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3126.5</v>
-      </c>
-      <c r="S31" cm="1">
-        <f t="array" ref="S31">常量表[双飞斩运气系数min]
+        <v>3239.375</v>
+      </c>
+      <c r="T31" cm="1">
+        <f t="array" ref="T31">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1563.25</v>
-      </c>
-      <c r="T31" s="1" cm="1">
-        <f t="array" ref="T31">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2603.85</v>
-      </c>
-      <c r="U31" s="1" cm="1">
-        <f t="array" ref="U31">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1154.925</v>
-      </c>
-    </row>
-    <row r="32" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1619.6875</v>
+      </c>
+      <c r="U31" s="14" cm="1">
+        <f t="array" ref="U31">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.3698630136986356E-2</v>
+      </c>
+      <c r="V31" s="14" cm="1">
+        <f t="array" ref="V31">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W31" s="1" cm="1">
+        <f t="array" ref="W31">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2705.4375</v>
+      </c>
+      <c r="X31" s="1" cm="1">
+        <f t="array" ref="X31">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1205.71875</v>
+      </c>
+    </row>
+    <row r="32" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D32" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="E32" s="8">
+        <v>175</v>
+      </c>
+      <c r="E32" s="2">
+        <v>43</v>
+      </c>
+      <c r="F32" s="2">
+        <v>23</v>
+      </c>
+      <c r="G32" s="2">
         <v>6</v>
       </c>
-      <c r="F32" s="2">
-        <v>44</v>
-      </c>
-      <c r="G32" s="2">
-        <v>23</v>
-      </c>
       <c r="H32" s="2">
+        <v>2</v>
+      </c>
+      <c r="I32" s="10">
+        <v>5</v>
+      </c>
+      <c r="J32" s="10">
+        <v>104</v>
+      </c>
+      <c r="K32" s="10">
         <v>6</v>
       </c>
-      <c r="I32" s="2">
-        <v>2</v>
-      </c>
-      <c r="J32" s="10">
-        <v>6</v>
-      </c>
-      <c r="K32" s="10">
-        <v>110</v>
-      </c>
       <c r="L32" s="10">
-        <v>6</v>
-      </c>
-      <c r="M32" s="10">
-        <v>338</v>
-      </c>
-      <c r="N32" cm="1">
-        <f t="array" ref="N32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M32" cm="1">
+        <f t="array" ref="M32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>999.6</v>
-      </c>
-      <c r="O32" cm="1">
-        <f t="array" ref="O32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>1026.3800000000001</v>
+      </c>
+      <c r="N32" cm="1">
+        <f t="array" ref="N32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>579.80399999999997</v>
-      </c>
-      <c r="P32" cm="1">
-        <f t="array" ref="P32">常量表[双飞斩运气系数max]
+        <v>591.34879999999998</v>
+      </c>
+      <c r="O32" s="12" cm="1">
+        <f t="array" ref="O32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.3513513513513375E-2</v>
+      </c>
+      <c r="P32" s="12" cm="1">
+        <f t="array" ref="P32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460595E-2</v>
+      </c>
+      <c r="Q32" cm="1">
+        <f t="array" ref="Q32">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1901.25</v>
-      </c>
-      <c r="Q32" cm="1">
-        <f t="array" ref="Q32">常量表[双飞斩运气系数min]
+        <v>1970.25</v>
+      </c>
+      <c r="R32" cm="1">
+        <f t="array" ref="R32">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>950.625</v>
-      </c>
-      <c r="R32" cm="1">
-        <f t="array" ref="R32">常量表[双飞斩运气系数max]
+        <v>985.125</v>
+      </c>
+      <c r="S32" cm="1">
+        <f t="array" ref="S32">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3168.75</v>
-      </c>
-      <c r="S32" cm="1">
-        <f t="array" ref="S32">常量表[双飞斩运气系数min]
+        <v>3283.75</v>
+      </c>
+      <c r="T32" cm="1">
+        <f t="array" ref="T32">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1584.375</v>
-      </c>
-      <c r="T32" s="1" cm="1">
-        <f t="array" ref="T32">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2641.875</v>
-      </c>
-      <c r="U32" s="1" cm="1">
-        <f t="array" ref="U32">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1173.9375</v>
-      </c>
-    </row>
-    <row r="33" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1641.875</v>
+      </c>
+      <c r="U32" s="14" cm="1">
+        <f t="array" ref="U32">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.3513513513513598E-2</v>
+      </c>
+      <c r="V32" s="14" cm="1">
+        <f t="array" ref="V32">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W32" s="1" cm="1">
+        <f t="array" ref="W32">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2745.375</v>
+      </c>
+      <c r="X32" s="1" cm="1">
+        <f t="array" ref="X32">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1225.6875</v>
+      </c>
+    </row>
+    <row r="33" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D33" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E33" s="8">
+        <v>176</v>
+      </c>
+      <c r="E33" s="2">
+        <v>43</v>
+      </c>
+      <c r="F33" s="2">
+        <v>23</v>
+      </c>
+      <c r="G33" s="2">
+        <v>7</v>
+      </c>
+      <c r="H33" s="2">
+        <v>2</v>
+      </c>
+      <c r="I33" s="10">
+        <v>5</v>
+      </c>
+      <c r="J33" s="10">
+        <v>104</v>
+      </c>
+      <c r="K33" s="10">
         <v>6</v>
       </c>
-      <c r="F33" s="2">
-        <v>43</v>
-      </c>
-      <c r="G33" s="2">
-        <v>23</v>
-      </c>
-      <c r="H33" s="2">
-        <v>7</v>
-      </c>
-      <c r="I33" s="2">
-        <v>2</v>
-      </c>
-      <c r="J33" s="10">
-        <v>6</v>
-      </c>
-      <c r="K33" s="10">
-        <v>104</v>
-      </c>
       <c r="L33" s="10">
-        <v>6</v>
-      </c>
-      <c r="M33" s="10">
-        <v>343</v>
-      </c>
-      <c r="N33" cm="1">
-        <f t="array" ref="N33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M33" s="1" cm="1">
+        <f t="array" ref="M33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1008.6</v>
-      </c>
-      <c r="O33" cm="1">
-        <f t="array" ref="O33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>1040.25</v>
+      </c>
+      <c r="N33" s="1" cm="1">
+        <f t="array" ref="N33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>582.59400000000005</v>
-      </c>
-      <c r="P33" cm="1">
-        <f t="array" ref="P33">常量表[双飞斩运气系数max]
+        <v>599.34</v>
+      </c>
+      <c r="O33" s="13" cm="1">
+        <f t="array" ref="O33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.3333333333333197E-2</v>
+      </c>
+      <c r="P33" s="13" cm="1">
+        <f t="array" ref="P33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460817E-2</v>
+      </c>
+      <c r="Q33" s="1" cm="1">
+        <f t="array" ref="Q33">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1929.375</v>
-      </c>
-      <c r="Q33" cm="1">
-        <f t="array" ref="Q33">常量表[双飞斩运气系数min]
+        <v>1996.875</v>
+      </c>
+      <c r="R33" s="1" cm="1">
+        <f t="array" ref="R33">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>964.6875</v>
-      </c>
-      <c r="R33" cm="1">
-        <f t="array" ref="R33">常量表[双飞斩运气系数max]
+        <v>998.4375</v>
+      </c>
+      <c r="S33" s="1" cm="1">
+        <f t="array" ref="S33">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3215.625</v>
-      </c>
-      <c r="S33" cm="1">
-        <f t="array" ref="S33">常量表[双飞斩运气系数min]
+        <v>3328.125</v>
+      </c>
+      <c r="T33" s="1" cm="1">
+        <f t="array" ref="T33">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1607.8125</v>
-      </c>
-      <c r="T33" s="1" cm="1">
-        <f t="array" ref="T33">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2684.0625</v>
-      </c>
-      <c r="U33" s="1" cm="1">
-        <f t="array" ref="U33">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1195.03125</v>
-      </c>
-    </row>
-    <row r="34" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1664.0625</v>
+      </c>
+      <c r="U33" s="14" cm="1">
+        <f t="array" ref="U33">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.3333333333333419E-2</v>
+      </c>
+      <c r="V33" s="14" cm="1">
+        <f t="array" ref="V33">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W33" s="1" cm="1">
+        <f t="array" ref="W33">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2785.3125</v>
+      </c>
+      <c r="X33" s="1" cm="1">
+        <f t="array" ref="X33">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1245.65625</v>
+      </c>
+    </row>
+    <row r="34" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D34" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="E34" s="8">
-        <v>7</v>
+        <v>180</v>
+      </c>
+      <c r="E34" s="2">
+        <v>43</v>
       </c>
       <c r="F34" s="2">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="G34" s="2">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="H34" s="2">
-        <v>7</v>
-      </c>
-      <c r="I34" s="2">
         <v>2</v>
       </c>
+      <c r="I34" s="10">
+        <v>5</v>
+      </c>
       <c r="J34" s="10">
+        <v>104</v>
+      </c>
+      <c r="K34" s="10">
         <v>6</v>
       </c>
-      <c r="K34" s="10">
-        <v>110</v>
-      </c>
       <c r="L34" s="10">
-        <v>6</v>
-      </c>
-      <c r="M34" s="10">
-        <v>338</v>
-      </c>
-      <c r="N34" cm="1">
-        <f t="array" ref="N34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>355</v>
+      </c>
+      <c r="M34" cm="1">
+        <f t="array" ref="M34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1012.928</v>
-      </c>
-      <c r="O34" cm="1">
-        <f t="array" ref="O34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+        <v>1054.1199999999999</v>
+      </c>
+      <c r="N34" cm="1">
+        <f t="array" ref="N34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>587.53471999999999</v>
-      </c>
-      <c r="P34" cm="1">
-        <f t="array" ref="P34">常量表[双飞斩运气系数max]
+        <v>607.33120000000008</v>
+      </c>
+      <c r="O34" s="12" cm="1">
+        <f t="array" ref="O34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.3157894736842257E-2</v>
+      </c>
+      <c r="P34" s="12" cm="1">
+        <f t="array" ref="P34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2977649603460817E-2</v>
+      </c>
+      <c r="Q34" cm="1">
+        <f t="array" ref="Q34">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1926.6000000000001</v>
-      </c>
-      <c r="Q34" cm="1">
-        <f t="array" ref="Q34">常量表[双飞斩运气系数min]
+        <v>2023.5</v>
+      </c>
+      <c r="R34" cm="1">
+        <f t="array" ref="R34">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>963.30000000000007</v>
-      </c>
-      <c r="R34" cm="1">
-        <f t="array" ref="R34">常量表[双飞斩运气系数max]
+        <v>1011.75</v>
+      </c>
+      <c r="S34" s="1" cm="1">
+        <f t="array" ref="S34">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3211</v>
-      </c>
-      <c r="S34" cm="1">
-        <f t="array" ref="S34">常量表[双飞斩运气系数min]
+        <v>3372.5</v>
+      </c>
+      <c r="T34" s="1" cm="1">
+        <f t="array" ref="T34">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1605.5</v>
-      </c>
-      <c r="T34" s="1" cm="1">
-        <f t="array" ref="T34">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2679.9</v>
-      </c>
-      <c r="U34" s="1" cm="1">
-        <f t="array" ref="U34">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1192.95</v>
-      </c>
-    </row>
-    <row r="35" spans="4:21" x14ac:dyDescent="0.2">
+        <v>1686.25</v>
+      </c>
+      <c r="U34" s="14" cm="1">
+        <f t="array" ref="U34">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.3157894736842035E-2</v>
+      </c>
+      <c r="V34" s="14" cm="1">
+        <f t="array" ref="V34">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4084507042253502E-2</v>
+      </c>
+      <c r="W34" s="1" cm="1">
+        <f t="array" ref="W34">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2825.25</v>
+      </c>
+      <c r="X34" s="1" cm="1">
+        <f t="array" ref="X34">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1265.625</v>
+      </c>
+    </row>
+    <row r="35" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D35" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="E35" s="8">
+        <v>181</v>
+      </c>
+      <c r="E35" s="2">
+        <v>43</v>
+      </c>
+      <c r="F35" s="2">
+        <v>23</v>
+      </c>
+      <c r="G35" s="2">
         <v>7</v>
       </c>
-      <c r="F35" s="2">
-        <v>70</v>
-      </c>
-      <c r="G35" s="2"/>
       <c r="H35" s="2">
-        <v>7</v>
-      </c>
-      <c r="I35" s="2">
         <v>2</v>
       </c>
+      <c r="I35" s="10">
+        <v>5</v>
+      </c>
       <c r="J35" s="10">
+        <v>104</v>
+      </c>
+      <c r="K35" s="10">
         <v>6</v>
       </c>
-      <c r="K35" s="10">
-        <v>94</v>
-      </c>
       <c r="L35" s="10">
-        <v>6</v>
-      </c>
-      <c r="M35" s="10">
-        <v>353</v>
+        <v>360</v>
+      </c>
+      <c r="M35" cm="1">
+        <f t="array" ref="M35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100</f>
+        <v>1053.75</v>
       </c>
       <c r="N35" cm="1">
         <f t="array" ref="N35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100</f>
+        <v>606.63</v>
+      </c>
+      <c r="O35" s="12" cm="1">
+        <f t="array" ref="O35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.3333333333333197E-2</v>
+      </c>
+      <c r="P35" s="12" cm="1">
+        <f t="array" ref="P35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2811387900355964E-2</v>
+      </c>
+      <c r="Q35" cm="1">
+        <f t="array" ref="Q35">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>2025</v>
+      </c>
+      <c r="R35" cm="1">
+        <f t="array" ref="R35">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*常量表[技能倍率]</f>
+        <v>1012.5</v>
+      </c>
+      <c r="S35" s="1" cm="1">
+        <f t="array" ref="S35">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>3375</v>
+      </c>
+      <c r="T35" s="1" cm="1">
+        <f t="array" ref="T35">常量表[双飞斩运气系数min]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])</f>
+        <v>1687.5</v>
+      </c>
+      <c r="U35" s="14" cm="1">
+        <f t="array" ref="U35">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.3333333333333419E-2</v>
+      </c>
+      <c r="V35" s="14" cm="1">
+        <f t="array" ref="V35">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.388888888888884E-2</v>
+      </c>
+      <c r="W35" s="1" cm="1">
+        <f t="array" ref="W35">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+        <v>2827.5</v>
+      </c>
+      <c r="X35" s="1" cm="1">
+        <f t="array" ref="X35">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+        <v>1266.75</v>
+      </c>
+    </row>
+    <row r="36" spans="4:24" x14ac:dyDescent="0.2">
+      <c r="D36" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" s="2">
+        <v>70</v>
+      </c>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2">
+        <v>7</v>
+      </c>
+      <c r="H36" s="2">
+        <v>2</v>
+      </c>
+      <c r="I36" s="10">
+        <v>6</v>
+      </c>
+      <c r="J36" s="10">
+        <v>94</v>
+      </c>
+      <c r="K36" s="10">
+        <v>6</v>
+      </c>
+      <c r="L36" s="10">
+        <v>353</v>
+      </c>
+      <c r="M36" cm="1">
+        <f t="array" ref="M36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>1082.932</v>
       </c>
-      <c r="O35" cm="1">
-        <f t="array" ref="O35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+      <c r="N36" cm="1">
+        <f t="array" ref="N36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>621.12327999999991</v>
       </c>
-      <c r="P35" cm="1">
-        <f t="array" ref="P35">常量表[双飞斩运气系数max]
+      <c r="O36" s="12" cm="1">
+        <f t="array" ref="O36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.2658227848101333E-2</v>
+      </c>
+      <c r="P36" s="12" cm="1">
+        <f t="array" ref="P36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.3131018383425674E-2</v>
+      </c>
+      <c r="Q36" cm="1">
+        <f t="array" ref="Q36">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
         <v>2091.5249999999996</v>
       </c>
-      <c r="Q35" cm="1">
-        <f t="array" ref="Q35">常量表[双飞斩运气系数min]
+      <c r="R36" cm="1">
+        <f t="array" ref="R36">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
         <v>1045.7624999999998</v>
       </c>
-      <c r="R35" cm="1">
-        <f t="array" ref="R35">常量表[双飞斩运气系数max]
+      <c r="S36" cm="1">
+        <f t="array" ref="S36">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3485.875</v>
       </c>
-      <c r="S35" cm="1">
-        <f t="array" ref="S35">常量表[双飞斩运气系数min]
+      <c r="T36" cm="1">
+        <f t="array" ref="T36">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>1742.9375</v>
       </c>
-      <c r="T35" s="1" cm="1">
-        <f t="array" ref="T35">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="U36" s="14" cm="1">
+        <f t="array" ref="U36">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.2658227848101333E-2</v>
+      </c>
+      <c r="V36" s="14" cm="1">
+        <f t="array" ref="V36">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.4164305949008416E-2</v>
+      </c>
+      <c r="W36" s="1" cm="1">
+        <f t="array" ref="W36">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2927.2874999999999</v>
       </c>
-      <c r="U35" s="1" cm="1">
-        <f t="array" ref="U35">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+      <c r="X36" s="1" cm="1">
+        <f t="array" ref="X36">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
         <v>1316.64375</v>
       </c>
     </row>
-    <row r="36" spans="4:21" x14ac:dyDescent="0.2">
-      <c r="D36" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="E36" s="8">
+    <row r="37" spans="4:24" x14ac:dyDescent="0.2">
+      <c r="D37" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="E37" s="2">
+        <v>83</v>
+      </c>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2">
         <v>7</v>
       </c>
-      <c r="F36" s="2">
-        <v>83</v>
-      </c>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2">
-        <v>7</v>
-      </c>
-      <c r="I36" s="2">
+      <c r="H37" s="2">
         <v>2</v>
       </c>
-      <c r="J36" s="10">
+      <c r="I37" s="10">
         <v>50</v>
       </c>
-      <c r="K36" s="10">
+      <c r="J37" s="10">
         <v>104</v>
       </c>
-      <c r="L36" s="10">
+      <c r="K37" s="10">
         <v>6</v>
       </c>
-      <c r="M36" s="10">
+      <c r="L37" s="10">
         <f>343-44</f>
         <v>299</v>
       </c>
-      <c r="N36" cm="1">
-        <f t="array" ref="N36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+      <c r="M37" cm="1">
+        <f t="array" ref="M37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>1131.9680000000001</v>
       </c>
-      <c r="O36" cm="1">
-        <f t="array" ref="O36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+      <c r="N37" cm="1">
+        <f t="array" ref="N37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>676.43552000000011</v>
       </c>
-      <c r="P36" cm="1">
-        <f t="array" ref="P36">常量表[双飞斩运气系数max]
+      <c r="O37" s="12" cm="1">
+        <f t="array" ref="O37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.0869565217391353E-2</v>
+      </c>
+      <c r="P37" s="12" cm="1">
+        <f t="array" ref="P37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.4629388816644884E-2</v>
+      </c>
+      <c r="Q37" cm="1">
+        <f t="array" ref="Q37">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
         <v>2063.1000000000004</v>
       </c>
-      <c r="Q36" cm="1">
-        <f t="array" ref="Q36">常量表[双飞斩运气系数min]
+      <c r="R37" cm="1">
+        <f t="array" ref="R37">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
         <v>1031.5500000000002</v>
       </c>
-      <c r="R36" cm="1">
-        <f t="array" ref="R36">常量表[双飞斩运气系数max]
+      <c r="S37" cm="1">
+        <f t="array" ref="S37">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3438.5</v>
       </c>
-      <c r="S36" cm="1">
-        <f t="array" ref="S36">常量表[双飞斩运气系数min]
+      <c r="T37" cm="1">
+        <f t="array" ref="T37">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>1719.25</v>
       </c>
-      <c r="T36" s="1" cm="1">
-        <f t="array" ref="T36">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="U37" s="14" cm="1">
+        <f t="array" ref="U37">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.0869565217391353E-2</v>
+      </c>
+      <c r="V37" s="14" cm="1">
+        <f t="array" ref="V37">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.6722408026755842E-2</v>
+      </c>
+      <c r="W37" s="1" cm="1">
+        <f t="array" ref="W37">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2884.65</v>
       </c>
-      <c r="U36" s="1" cm="1">
-        <f t="array" ref="U36">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+      <c r="X37" s="1" cm="1">
+        <f t="array" ref="X37">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
         <v>1295.325</v>
       </c>
     </row>
-    <row r="37" spans="4:21" x14ac:dyDescent="0.2">
-      <c r="D37" s="8" t="s">
-        <v>180</v>
-      </c>
-      <c r="E37" s="8">
+    <row r="38" spans="4:24" x14ac:dyDescent="0.2">
+      <c r="D38" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E38" s="2">
+        <v>88</v>
+      </c>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2">
         <v>7</v>
       </c>
-      <c r="F37" s="2">
-        <v>88</v>
-      </c>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2">
-        <v>7</v>
-      </c>
-      <c r="I37" s="2">
+      <c r="H38" s="2">
         <v>2</v>
       </c>
-      <c r="J37" s="10">
+      <c r="I38" s="10">
         <v>55</v>
       </c>
-      <c r="K37" s="10">
+      <c r="J38" s="10">
         <v>110</v>
       </c>
-      <c r="L37" s="10">
+      <c r="K38" s="10">
         <v>6</v>
       </c>
-      <c r="M37" s="10">
+      <c r="L38" s="10">
         <v>288</v>
       </c>
-      <c r="N37" cm="1">
-        <f t="array" ref="N37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+      <c r="M38" cm="1">
+        <f t="array" ref="M38">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>1165.7459999999999</v>
       </c>
-      <c r="O37" cm="1">
-        <f t="array" ref="O37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+      <c r="N38" cm="1">
+        <f t="array" ref="N38">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
         <v>703.12584000000004</v>
       </c>
-      <c r="P37" cm="1">
-        <f t="array" ref="P37">常量表[双飞斩运气系数max]
+      <c r="O38" s="12" cm="1">
+        <f t="array" ref="O38">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*(
+ 常量表[面板主属性系数]*表15[[#This Row],[运气]]
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.0309278350515427E-2</v>
+      </c>
+      <c r="P38" s="12" cm="1">
+        <f t="array" ref="P38">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(
+ 常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
+ +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
+)/100
+/表15[[#This Row],[面板max]]-1</f>
+        <v>1.4977533699450873E-2</v>
+      </c>
+      <c r="Q38" cm="1">
+        <f t="array" ref="Q38">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
         <v>2095.1999999999998</v>
       </c>
-      <c r="Q37" cm="1">
-        <f t="array" ref="Q37">常量表[双飞斩运气系数min]
+      <c r="R38" cm="1">
+        <f t="array" ref="R38">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
         <v>1047.5999999999999</v>
       </c>
-      <c r="R37" cm="1">
-        <f t="array" ref="R37">常量表[双飞斩运气系数max]
+      <c r="S38" cm="1">
+        <f t="array" ref="S38">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>3492</v>
       </c>
-      <c r="S37" cm="1">
-        <f t="array" ref="S37">常量表[双飞斩运气系数min]
+      <c r="T38" cm="1">
+        <f t="array" ref="T38">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
         <v>1746</v>
       </c>
-      <c r="T37" s="1" cm="1">
-        <f t="array" ref="T37">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
+      <c r="U38" s="14" cm="1">
+        <f t="array" ref="U38">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
+*表15[[#This Row],[运气]]/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.0309278350515427E-2</v>
+      </c>
+      <c r="V38" s="14" cm="1">
+        <f t="array" ref="V38">常量表[双飞斩运气系数max]
+*SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
+*(表15[[#This Row],[运气]]+5)/100
+*(常量表[技能倍率]+常量表[暴击倍率])
+/表15[[#This Row],[暴击伤害max]]-1</f>
+        <v>1.736111111111116E-2</v>
+      </c>
+      <c r="W38" s="1" cm="1">
+        <f t="array" ref="W38">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
         <v>2932.8</v>
       </c>
-      <c r="U37" s="1" cm="1">
-        <f t="array" ref="U37">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
+      <c r="X38" s="1" cm="1">
+        <f t="array" ref="X38">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
         <v>1319.4</v>
       </c>
     </row>
@@ -9515,62 +10348,62 @@
   <sheetData>
     <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C4" t="s">
+        <v>131</v>
+      </c>
+      <c r="D4" t="s">
         <v>132</v>
-      </c>
-      <c r="D4" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" t="s">
         <v>138</v>
-      </c>
-      <c r="C5" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" t="s">
         <v>138</v>
-      </c>
-      <c r="C6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
+        <v>137</v>
+      </c>
+      <c r="C7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" t="s">
         <v>138</v>
-      </c>
-      <c r="C7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D7" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -9592,7 +10425,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="105" spans="7:15" x14ac:dyDescent="0.2">
@@ -9600,7 +10433,7 @@
         <v>2</v>
       </c>
       <c r="H105" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="7:15" x14ac:dyDescent="0.2">
@@ -9608,7 +10441,7 @@
         <v>3</v>
       </c>
       <c r="H106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="7:15" x14ac:dyDescent="0.2">
@@ -9616,7 +10449,7 @@
         <v>31</v>
       </c>
       <c r="O107" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="108" spans="7:15" x14ac:dyDescent="0.2">
@@ -9624,7 +10457,7 @@
         <v>32</v>
       </c>
       <c r="O108" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="7:15" x14ac:dyDescent="0.2">
@@ -9632,13 +10465,13 @@
         <v>19</v>
       </c>
       <c r="H109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N109">
         <v>33</v>
       </c>
       <c r="O109" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="7:15" x14ac:dyDescent="0.2">
@@ -9646,13 +10479,13 @@
         <v>23</v>
       </c>
       <c r="H110" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N110">
         <v>36</v>
       </c>
       <c r="O110" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="111" spans="7:15" x14ac:dyDescent="0.2">
@@ -9660,7 +10493,7 @@
         <v>39</v>
       </c>
       <c r="O111" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="112" spans="7:15" x14ac:dyDescent="0.2">
@@ -9668,7 +10501,7 @@
         <v>41</v>
       </c>
       <c r="O112" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="14:15" x14ac:dyDescent="0.2">
@@ -9676,7 +10509,7 @@
         <v>54</v>
       </c>
       <c r="O113" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/冒险岛.xlsx
+++ b/冒险岛.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyPrograms\BossTimer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB0F4509-D5DF-447B-B4EC-4023A6E214AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C0B3EF1-068C-4995-BF06-92B2CB69A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32055" yWindow="690" windowWidth="28995" windowHeight="20115" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32055" yWindow="690" windowWidth="28995" windowHeight="20115" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="盈利比" sheetId="4" r:id="rId1"/>
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="241">
   <si>
     <t>卷概率</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -539,10 +539,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无魂蘑菇王</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>代练 2026/8/18</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -603,46 +599,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>名单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 神罗天正</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 三千雷幻身</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 关你吊事</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>蝙蝠怪</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>扫线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 UUUD</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/找人 油炸派大星</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>70_80预估</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -701,10 +657,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>第5天</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -823,6 +775,207 @@
   <si>
     <t>遗迹4</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到100预估</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝙蝠魔克星</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>频道</t>
+  </si>
+  <si>
+    <t>频道</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝙蝠魔克星1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝙蝠魔克星2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝙蝠魔克星3</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星4</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星5</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星6</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星7</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星8</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星9</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星10</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星11</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星12</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星13</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星14</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星15</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星16</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星17</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星18</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星19</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星20</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星21</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星22</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星23</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星24</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星25</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星26</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星27</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星28</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星29</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星30</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星31</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星32</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星33</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星34</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星35</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星36</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星37</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星38</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星39</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星40</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星41</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星42</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星43</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星44</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星45</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星46</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星47</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星48</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星49</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星50</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星51</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星52</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星53</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星54</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星55</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星56</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星57</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星58</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星59</t>
+  </si>
+  <si>
+    <t>蝙蝠魔克星60</t>
   </si>
 </sst>
 </file>
@@ -983,7 +1136,45 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="68">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="7" tint="-0.249977111117893"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -1111,22 +1302,6 @@
     <dxf>
       <font>
         <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="7" tint="-0.249977111117893"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -1175,25 +1350,6 @@
         <vertAlign val="baseline"/>
         <sz val="11"/>
         <color theme="7" tint="-0.249977111117893"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
         <name val="等线"/>
         <family val="3"/>
         <charset val="134"/>
@@ -1535,96 +1691,6 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1730,6 +1796,96 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3265,21 +3421,21 @@
     <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>161733</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>38024</xdr:rowOff>
+      <xdr:colOff>180781</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>133288</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1">
+        <xdr:cNvPr id="14" name="图片 13">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1220CCAD-2072-4799-9742-75E6A286F44D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0309FD7A-FD7A-79E8-128C-C1D80F3E76C7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3295,8 +3451,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11572875" y="8477250"/>
-          <a:ext cx="1533333" cy="609524"/>
+          <a:off x="11572875" y="12125325"/>
+          <a:ext cx="1552381" cy="495238"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3307,23 +3463,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>476052</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>9456</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>18892</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>152345</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="图片 2">
+        <xdr:cNvPr id="15" name="图片 14">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{291FF4BE-B94A-4B61-AADE-DACFACA722CD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{586F209B-0AAE-19AE-EFF6-C3A9F001D1FB}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3339,52 +3495,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13211175" y="8324850"/>
-          <a:ext cx="1580952" cy="552381"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>541481</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>133105</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8B2E73C0-C9FC-6FDD-EE05-47B1E3F88954}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7419975" y="9210675"/>
-          <a:ext cx="11552381" cy="1961905"/>
+          <a:off x="11696700" y="12925425"/>
+          <a:ext cx="1266667" cy="438095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3739,30 +3851,30 @@
   <autoFilter ref="C39:N42" xr:uid="{D2F5DA31-758D-4974-A8DB-D862E9E685DC}"/>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{C9A11298-FA96-49C6-A3A1-A77A91972722}" name="卷概率"/>
-    <tableColumn id="8" xr3:uid="{BEDD0CAD-6AB0-4C30-A86C-19070711828D}" name="敏捷" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{BEDD0CAD-6AB0-4C30-A86C-19070711828D}" name="敏捷" dataDxfId="33"/>
     <tableColumn id="9" xr3:uid="{DB11AE09-BC1F-400F-8121-26D0BBD40CE3}" name="命中"/>
     <tableColumn id="10" xr3:uid="{419A6181-B2C8-4E1A-BD6F-47425EDBEDC1}" name="移速"/>
-    <tableColumn id="3" xr3:uid="{06987FE9-FC9A-467C-8516-1C8A6991EFD3}" name="单价" dataDxfId="31" totalsRowDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{EC81E847-7526-4094-88CA-6860A893C3B1}" name="rmb" dataDxfId="29">
+    <tableColumn id="3" xr3:uid="{06987FE9-FC9A-467C-8516-1C8A6991EFD3}" name="单价" dataDxfId="32" totalsRowDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{EC81E847-7526-4094-88CA-6860A893C3B1}" name="rmb" dataDxfId="30">
       <calculatedColumnFormula array="1">表7_9[[#This Row],[单价]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{C26F07DB-AA65-4261-A542-9FF829521DAC}" name="敏捷价格" dataDxfId="28">
+    <tableColumn id="7" xr3:uid="{C26F07DB-AA65-4261-A542-9FF829521DAC}" name="敏捷价格" dataDxfId="29">
       <calculatedColumnFormula>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{247B50C8-19A4-4B64-A6C4-FEFA5C146E13}" name="模拟数量" totalsRowFunction="custom" dataDxfId="27">
+    <tableColumn id="11" xr3:uid="{247B50C8-19A4-4B64-A6C4-FEFA5C146E13}" name="模拟数量" totalsRowFunction="custom" dataDxfId="28">
       <totalsRowFormula>SUM(表7_9[模拟数量])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{E46A5CC0-4EA5-480B-A804-F448C4FD1200}" name="成功数量" dataDxfId="26"/>
-    <tableColumn id="13" xr3:uid="{4297568D-CFCF-46D6-99EB-6BE373700BA1}" name="总敏捷" totalsRowFunction="custom" dataDxfId="25">
+    <tableColumn id="12" xr3:uid="{E46A5CC0-4EA5-480B-A804-F448C4FD1200}" name="成功数量" dataDxfId="27"/>
+    <tableColumn id="13" xr3:uid="{4297568D-CFCF-46D6-99EB-6BE373700BA1}" name="总敏捷" totalsRowFunction="custom" dataDxfId="26">
       <calculatedColumnFormula>表7_9[[#This Row],[成功数量]]*表7_9[[#This Row],[敏捷]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[总敏捷])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{DF214F81-3AC6-44F7-A044-188A8853DA6B}" name="造价" totalsRowFunction="custom" dataDxfId="24">
+    <tableColumn id="14" xr3:uid="{DF214F81-3AC6-44F7-A044-188A8853DA6B}" name="造价" totalsRowFunction="custom" dataDxfId="25">
       <calculatedColumnFormula>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[造价])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{2749CEFB-FAB2-4688-B950-EB889079A869}" name="风险造价" totalsRowFunction="custom" dataDxfId="23">
+    <tableColumn id="15" xr3:uid="{2749CEFB-FAB2-4688-B950-EB889079A869}" name="风险造价" totalsRowFunction="custom" dataDxfId="24">
       <calculatedColumnFormula>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7_9[风险造价])</totalsRowFormula>
@@ -3773,7 +3885,7 @@
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4EBDEB06-9EAF-4C59-8B85-E07E60337705}" name="常量表" displayName="常量表" ref="D8:L9" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{4EBDEB06-9EAF-4C59-8B85-E07E60337705}" name="常量表" displayName="常量表" ref="D8:L9" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="D8:L9" xr:uid="{1EC169C2-1CE1-41D3-B5C2-AF9DACDA284A}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3819,7 +3931,7 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}" name="表15" displayName="表15" ref="D25:X38" totalsRowShown="0" headerRowDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="15" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}" name="表15" displayName="表15" ref="D25:X38" totalsRowShown="0" headerRowDxfId="22">
   <autoFilter ref="D25:X38" xr:uid="{EA561F5C-EA5E-422A-8BB0-B9095727B3D5}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3844,30 +3956,30 @@
     <filterColumn colId="20" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="21">
-    <tableColumn id="12" xr3:uid="{E28116B0-6337-4365-A0F6-32D60BC978B6}" name="备注" dataDxfId="20"/>
-    <tableColumn id="19" xr3:uid="{7A53DEB6-2117-436A-BF1B-D301DAF6BCEE}" name="武器攻击" dataDxfId="19"/>
-    <tableColumn id="18" xr3:uid="{20152D2D-C68D-446B-8E46-96A7870A92B3}" name="飞镖攻击" dataDxfId="18"/>
-    <tableColumn id="17" xr3:uid="{A88072CD-F8EB-44C3-9C7B-02B153E89A1A}" name="手套攻击" dataDxfId="17"/>
-    <tableColumn id="16" xr3:uid="{D1098DDD-BCA5-4948-A22C-8762851A9BB4}" name="Link攻击" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{1D59A3FA-F5A2-4BF3-8DFD-364A71CE22EE}" name="力量" dataDxfId="15"/>
-    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{85C70B3A-5D87-4857-BD02-D3B80CC6C80E}" name="智力" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="12"/>
-    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="11">
+    <tableColumn id="12" xr3:uid="{E28116B0-6337-4365-A0F6-32D60BC978B6}" name="备注" dataDxfId="21"/>
+    <tableColumn id="19" xr3:uid="{7A53DEB6-2117-436A-BF1B-D301DAF6BCEE}" name="武器攻击" dataDxfId="20"/>
+    <tableColumn id="18" xr3:uid="{20152D2D-C68D-446B-8E46-96A7870A92B3}" name="飞镖攻击" dataDxfId="19"/>
+    <tableColumn id="17" xr3:uid="{A88072CD-F8EB-44C3-9C7B-02B153E89A1A}" name="手套攻击" dataDxfId="18"/>
+    <tableColumn id="16" xr3:uid="{D1098DDD-BCA5-4948-A22C-8762851A9BB4}" name="Link攻击" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{1D59A3FA-F5A2-4BF3-8DFD-364A71CE22EE}" name="力量" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{BBF260FC-CE43-4380-87B9-5F9EE2064698}" name="敏捷" dataDxfId="16"/>
+    <tableColumn id="5" xr3:uid="{85C70B3A-5D87-4857-BD02-D3B80CC6C80E}" name="智力" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{BBD0C02A-DFD9-4B1D-B574-6A30BAE2D997}" name="运气" dataDxfId="1"/>
+    <tableColumn id="15" xr3:uid="{19169ABF-D16F-4AB7-840E-72174B5817E9}" name="面板max" dataDxfId="14">
       <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="10">
+    <tableColumn id="14" xr3:uid="{6F6FB551-01A8-45AA-B765-56487CC9414A}" name="面板min" dataDxfId="13">
       <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="1" xr3:uid="{0600774E-6E25-4B9E-B1EF-DC7A6148D9E7}" name="攻击+1提升面板" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{0600774E-6E25-4B9E-B1EF-DC7A6148D9E7}" name="攻击+1提升面板" dataDxfId="12">
       <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
 *(
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
@@ -3875,7 +3987,7 @@
 )/100
 /表15[[#This Row],[面板max]]-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{F92D18E3-61E1-4175-A13E-DEEF72D61CB3}" name="运气+5提升面板" dataDxfId="8">
+    <tableColumn id="13" xr3:uid="{F92D18E3-61E1-4175-A13E-DEEF72D61CB3}" name="运气+5提升面板" dataDxfId="11">
       <calculatedColumnFormula array="1">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(
  常量表[面板主属性系数]*(表15[[#This Row],[运气]]+5)
@@ -3883,48 +3995,48 @@
 )/100
 /表15[[#This Row],[面板max]]-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="双飞斩max" dataDxfId="7">
+    <tableColumn id="2" xr3:uid="{219B6184-F7B6-4F19-ADA6-85DF621E3BE2}" name="双飞斩max" dataDxfId="10">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="双飞斩min" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{8B15A05C-D2B1-4EE3-A8A0-B233320DC7E0}" name="双飞斩min" dataDxfId="9">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{CC4D7A50-583C-409D-A439-41839CCB5FBE}" name="暴击伤害max" dataDxfId="8">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{02CE20E8-6B44-43C6-B599-BF6C200E0989}" name="暴击伤害min" dataDxfId="7">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{030A6DFF-61EB-463E-AC11-D16E84D830A0}" name="攻击+1提升伤害" dataDxfId="3">
+    <tableColumn id="20" xr3:uid="{030A6DFF-61EB-463E-AC11-D16E84D830A0}" name="攻击+1提升伤害" dataDxfId="6">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{E30714F7-4C29-45F8-B00B-4FBAD467D571}" name="运气+5提升伤害" dataDxfId="2">
+    <tableColumn id="21" xr3:uid="{E30714F7-4C29-45F8-B00B-4FBAD467D571}" name="运气+5提升伤害" dataDxfId="5">
       <calculatedColumnFormula array="1">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{CDE151F5-6122-4088-B163-44E497C31795}" name="实际伤害max" dataDxfId="1">
+    <tableColumn id="8" xr3:uid="{CDE151F5-6122-4088-B163-44E497C31795}" name="实际伤害max" dataDxfId="4">
       <calculatedColumnFormula array="1">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{16FD9281-FFFB-49BE-B43A-61A44174EE38}" name="实际伤害min" dataDxfId="0">
+    <tableColumn id="9" xr3:uid="{16FD9281-FFFB-49BE-B43A-61A44174EE38}" name="实际伤害min" dataDxfId="3">
       <calculatedColumnFormula array="1">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -3933,23 +4045,31 @@
 </file>
 
 <file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="17" xr:uid="{C6BEB876-D98A-44E6-96E6-52E2DABA23E5}" name="表17" displayName="表17" ref="B4:D9" totalsRowShown="0">
-  <autoFilter ref="B4:D9" xr:uid="{C6BEB876-D98A-44E6-96E6-52E2DABA23E5}">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{4E3E9F9E-192E-414F-9616-0FF8C333130F}" name="Boss"/>
-    <tableColumn id="1" xr3:uid="{E4972F37-7774-4368-83D7-CCB99D1474FC}" name="名单"/>
-    <tableColumn id="3" xr3:uid="{5DC1F052-F6EE-43C2-88A5-08AD20A56059}" name="类型"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{8FC10CA6-3516-4511-91D7-5AC2FC907D20}" name="表11" displayName="表11" ref="C9:D70" totalsRowShown="0">
+  <autoFilter ref="C9:D70" xr:uid="{8FC10CA6-3516-4511-91D7-5AC2FC907D20}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{7E8883F3-F855-4AD2-83DC-B9AEB448E0C1}" name="ID"/>
+    <tableColumn id="2" xr3:uid="{197750A0-BB97-460F-92F8-54483D18F26F}" name="频道"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{C6843B59-80DD-4C01-AC48-36878D95A000}" name="表12" displayName="表12" ref="H9:I69" totalsRowShown="0">
+  <autoFilter ref="H9:I69" xr:uid="{C6843B59-80DD-4C01-AC48-36878D95A000}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{29079E86-1107-49A2-A0DA-02BB8F4E5404}" name="频道"/>
+    <tableColumn id="2" xr3:uid="{8FFD247E-E1E8-433B-8852-DF7B95A85541}" name="ID" dataDxfId="0">
+      <calculatedColumnFormula>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}" name="金价表" displayName="金价表" ref="B5:E6" totalsRowShown="0" headerRowDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}" name="金价表" displayName="金价表" ref="B5:E6" totalsRowShown="0" headerRowDxfId="60">
   <autoFilter ref="B5:E6" xr:uid="{8D54ED8C-1516-4508-8616-5B88AC8E93A6}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3957,11 +4077,11 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{63ED9EB8-73DB-4AD9-B2A4-1D5B7478467C}" name="当前金价1w" dataDxfId="65"/>
+    <tableColumn id="1" xr3:uid="{63ED9EB8-73DB-4AD9-B2A4-1D5B7478467C}" name="当前金价1w" dataDxfId="59"/>
     <tableColumn id="2" xr3:uid="{D33CA45C-8193-4B2C-8B27-FBAD392BC340}" name="税后金价">
       <calculatedColumnFormula>金价表[[#This Row],[当前金价1w]]/0.95</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{29531BBF-B529-4F64-A29C-03F62C776778}" name="出售商品价格" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{29531BBF-B529-4F64-A29C-03F62C776778}" name="出售商品价格" dataDxfId="58"/>
     <tableColumn id="4" xr3:uid="{35F8F87C-3C60-4850-9D79-EF218F013BD7}" name="等价rmb">
       <calculatedColumnFormula>金价表[[#This Row],[出售商品价格]]*金价表[[#This Row],[当前金价1w]]*0.95</calculatedColumnFormula>
     </tableColumn>
@@ -3971,7 +4091,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}" name="表16" displayName="表16" ref="H12:N34" totalsRowShown="0" headerRowDxfId="63">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}" name="表16" displayName="表16" ref="H12:N34" totalsRowShown="0" headerRowDxfId="57">
   <autoFilter ref="H12:N34" xr:uid="{967F430E-EFC5-4A66-809D-3F5B0305E50D}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -3982,13 +4102,13 @@
     <filterColumn colId="6" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{67FFE6FF-4DC3-4141-9556-C34751EE7C54}" name="商品名称" dataDxfId="62"/>
-    <tableColumn id="2" xr3:uid="{AA234072-647C-4A37-BA00-45785241169C}" name="购买价格w" dataDxfId="61"/>
-    <tableColumn id="6" xr3:uid="{B69C23F2-12E4-49E4-B956-F35FECF6EED2}" name="制作价格" dataDxfId="60"/>
-    <tableColumn id="7" xr3:uid="{1F179FDF-DB5D-4D9E-9382-252E36157465}" name="差价（含税）" dataDxfId="59">
+    <tableColumn id="1" xr3:uid="{67FFE6FF-4DC3-4141-9556-C34751EE7C54}" name="商品名称" dataDxfId="56"/>
+    <tableColumn id="2" xr3:uid="{AA234072-647C-4A37-BA00-45785241169C}" name="购买价格w" dataDxfId="55"/>
+    <tableColumn id="6" xr3:uid="{B69C23F2-12E4-49E4-B956-F35FECF6EED2}" name="制作价格" dataDxfId="54"/>
+    <tableColumn id="7" xr3:uid="{1F179FDF-DB5D-4D9E-9382-252E36157465}" name="差价（含税）" dataDxfId="53">
       <calculatedColumnFormula>IF(表16[[#This Row],[制作价格]]&gt;0,表16[[#This Row],[购买价格w]]*0.95-表16[[#This Row],[制作价格]],0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{8A5E4DE9-C2B5-4A40-BB32-99BB0FFB6D5C}" name="等价rmb" dataDxfId="58">
+    <tableColumn id="3" xr3:uid="{8A5E4DE9-C2B5-4A40-BB32-99BB0FFB6D5C}" name="等价rmb" dataDxfId="52">
       <calculatedColumnFormula array="1">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{DFF8FCC2-0D9D-4B90-A22F-E3039B1304EA}" name="提升"/>
@@ -3999,8 +4119,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}" name="表5" displayName="表5" ref="E32:L69" totalsRowShown="0">
-  <autoFilter ref="E32:L69" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}" name="表5" displayName="表5" ref="E32:L72" totalsRowShown="0">
+  <autoFilter ref="E32:L72" xr:uid="{7472A1EC-A5A7-4173-8E9D-EB90E042B439}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
     <filterColumn colId="2" hiddenButton="1"/>
@@ -4012,11 +4132,11 @@
   </autoFilter>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{1845B151-23D6-4795-B6F2-CF21BBF78274}" name="源"/>
-    <tableColumn id="6" xr3:uid="{6745D84B-176D-410B-A732-E68A39D776C3}" name="开始lv" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{EB49316D-EA89-440F-8BED-529A7B30C022}" name="开始" dataDxfId="56"/>
-    <tableColumn id="7" xr3:uid="{D165A06A-4105-4A22-9828-A4BEF84DACDC}" name="结束lv" dataDxfId="55"/>
-    <tableColumn id="3" xr3:uid="{7BC03053-038D-41AD-84CE-B60879A78C44}" name="结束" dataDxfId="54"/>
-    <tableColumn id="8" xr3:uid="{18F6AB19-F5E3-4464-85E9-7510B0FF4FBB}" name="总经验(万)" dataDxfId="53">
+    <tableColumn id="6" xr3:uid="{6745D84B-176D-410B-A732-E68A39D776C3}" name="开始lv" dataDxfId="67"/>
+    <tableColumn id="2" xr3:uid="{EB49316D-EA89-440F-8BED-529A7B30C022}" name="开始" dataDxfId="66"/>
+    <tableColumn id="7" xr3:uid="{D165A06A-4105-4A22-9828-A4BEF84DACDC}" name="结束lv" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{7BC03053-038D-41AD-84CE-B60879A78C44}" name="结束" dataDxfId="64"/>
+    <tableColumn id="8" xr3:uid="{18F6AB19-F5E3-4464-85E9-7510B0FF4FBB}" name="总经验(万)" dataDxfId="63">
       <calculatedColumnFormula>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -4026,7 +4146,7 @@
 /10000</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{14E25966-66F6-42F8-8B80-A23CD832D12D}" name="时间min"/>
-    <tableColumn id="5" xr3:uid="{96A93011-DA20-46D8-8102-FAFE34B717F8}" name="exp/h（万）" dataDxfId="52">
+    <tableColumn id="5" xr3:uid="{96A93011-DA20-46D8-8102-FAFE34B717F8}" name="exp/h（万）" dataDxfId="62">
       <calculatedColumnFormula>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -4051,7 +4171,7 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{3C593048-19E0-4739-89F7-550D3BCA4024}" name="等级"/>
     <tableColumn id="2" xr3:uid="{7BF93B33-4DA7-41C2-A05A-738673B7622F}" name="升级所需"/>
-    <tableColumn id="3" xr3:uid="{D469DC4A-2E68-429C-9A30-B15320947E61}" name="升级所需(万)" dataDxfId="51">
+    <tableColumn id="3" xr3:uid="{D469DC4A-2E68-429C-9A30-B15320947E61}" name="升级所需(万)" dataDxfId="61">
       <calculatedColumnFormula>经验表[[#This Row],[升级所需]]/10000</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4085,13 +4205,13 @@
   </autoFilter>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{698E820D-23C3-4BF8-BEED-4FE313E53471}" name="次数"/>
-    <tableColumn id="2" xr3:uid="{84879E6A-8423-4B05-81FF-8B66F1BA776F}" name="几率" dataDxfId="50">
+    <tableColumn id="2" xr3:uid="{84879E6A-8423-4B05-81FF-8B66F1BA776F}" name="几率" dataDxfId="51">
       <calculatedColumnFormula array="1">IFERROR(1 - _xlfn.BINOM.DIST(卷轴参数[预期成功]-1, 表1[[#This Row],[次数]], 卷轴参数[卷概率], TRUE),0)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{E3DE3ED5-E666-48A5-A699-F069DF88052E}" name="成本价" dataDxfId="49">
+    <tableColumn id="4" xr3:uid="{E3DE3ED5-E666-48A5-A699-F069DF88052E}" name="成本价" dataDxfId="50">
       <calculatedColumnFormula array="1">表1[[#This Row],[次数]]*卷轴参数[卷价值]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7C2768F8-9055-4D23-BE1E-FE8B90B3316B}" name="价值" dataDxfId="48">
+    <tableColumn id="3" xr3:uid="{7C2768F8-9055-4D23-BE1E-FE8B90B3316B}" name="价值" dataDxfId="49">
       <calculatedColumnFormula array="1">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4100,7 +4220,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}" name="卷轴参数" displayName="卷轴参数" ref="B3:E4" totalsRowShown="0" headerRowDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}" name="卷轴参数" displayName="卷轴参数" ref="B3:E4" totalsRowShown="0" headerRowDxfId="48">
   <autoFilter ref="B3:E4" xr:uid="{52969EFF-D36C-4CC8-988C-25CE75BC0798}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -4108,9 +4228,9 @@
     <filterColumn colId="3" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DC107BBC-406B-498C-BD39-B974C0439AFE}" name="卷概率" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{C61182DF-822A-4A58-AE24-69A976436107}" name="预期成功" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{0F00CCD6-E594-41C1-8347-E43384BB99BE}" name="卷拍卖行价w" dataDxfId="44"/>
+    <tableColumn id="1" xr3:uid="{DC107BBC-406B-498C-BD39-B974C0439AFE}" name="卷概率" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{C61182DF-822A-4A58-AE24-69A976436107}" name="预期成功" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{0F00CCD6-E594-41C1-8347-E43384BB99BE}" name="卷拍卖行价w" dataDxfId="45"/>
     <tableColumn id="3" xr3:uid="{C4E5C7A1-FB81-480E-9C73-32F750E3D67C}" name="卷价值">
       <calculatedColumnFormula array="1">卷轴参数[[#This Row],[卷拍卖行价w]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
@@ -4138,34 +4258,34 @@
   </autoFilter>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{8F08A040-BDE1-42FF-BDBE-7E0E087A8819}" name="卷概率"/>
-    <tableColumn id="8" xr3:uid="{680FF308-0932-4EB2-8486-CA5FEE3FE305}" name="敏捷" dataDxfId="43"/>
+    <tableColumn id="8" xr3:uid="{680FF308-0932-4EB2-8486-CA5FEE3FE305}" name="敏捷" dataDxfId="44"/>
     <tableColumn id="9" xr3:uid="{A70A1698-D188-45CC-BD1C-5EB46D8790A5}" name="命中"/>
     <tableColumn id="10" xr3:uid="{DF40AD0D-56B3-4A4D-8D8F-BCBF9EC1301D}" name="移速"/>
-    <tableColumn id="3" xr3:uid="{A7118FBF-F08B-458A-BB56-4552824BA5FC}" name="单价" dataDxfId="42" totalsRowDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{CA577DD0-7258-45B9-A695-C4171373AE3D}" name="rmb" dataDxfId="40">
+    <tableColumn id="3" xr3:uid="{A7118FBF-F08B-458A-BB56-4552824BA5FC}" name="单价" dataDxfId="43" totalsRowDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{CA577DD0-7258-45B9-A695-C4171373AE3D}" name="rmb" dataDxfId="41">
       <calculatedColumnFormula array="1">表7[[#This Row],[单价]]*金价表[税后金价]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{3BF04BD0-3887-4D5A-9323-13DA842E9180}" name="每点敏捷价格" dataDxfId="39">
+    <tableColumn id="7" xr3:uid="{3BF04BD0-3887-4D5A-9323-13DA842E9180}" name="每点敏捷价格" dataDxfId="40">
       <calculatedColumnFormula>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{7B62E845-07A3-42E2-92B2-C00C85BAD066}" name="模拟数量" totalsRowFunction="custom" dataDxfId="38">
+    <tableColumn id="11" xr3:uid="{7B62E845-07A3-42E2-92B2-C00C85BAD066}" name="模拟数量" totalsRowFunction="custom" dataDxfId="39">
       <totalsRowFormula>SUM(表7[模拟数量])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{94F47A8A-0CD2-46BA-BB08-9B69181B3598}" name="成功数量" dataDxfId="37"/>
-    <tableColumn id="13" xr3:uid="{D8FA6D3D-13C9-413D-AA5C-EE25CEB6741F}" name="总敏捷" totalsRowFunction="custom" dataDxfId="36">
+    <tableColumn id="12" xr3:uid="{94F47A8A-0CD2-46BA-BB08-9B69181B3598}" name="成功数量" dataDxfId="38"/>
+    <tableColumn id="13" xr3:uid="{D8FA6D3D-13C9-413D-AA5C-EE25CEB6741F}" name="总敏捷" totalsRowFunction="custom" dataDxfId="37">
       <calculatedColumnFormula>表7[[#This Row],[成功数量]]*表7[[#This Row],[敏捷]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[总敏捷])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{55A7AE7C-6813-49F7-BF22-A6D1331D0893}" name="成本造价" totalsRowFunction="custom" dataDxfId="35">
+    <tableColumn id="14" xr3:uid="{55A7AE7C-6813-49F7-BF22-A6D1331D0893}" name="成本造价" totalsRowFunction="custom" dataDxfId="36">
       <calculatedColumnFormula>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[成本造价])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{7EE726C5-0F2C-402A-94A6-793B6B1029B8}" name="总价格" totalsRowFunction="custom" dataDxfId="34">
+    <tableColumn id="2" xr3:uid="{7EE726C5-0F2C-402A-94A6-793B6B1029B8}" name="总价格" totalsRowFunction="custom" dataDxfId="35">
       <calculatedColumnFormula>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[总价格])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{7DFA1C56-A8FE-42B5-B6C1-2058B28542ED}" name="风险造价" totalsRowFunction="custom" dataDxfId="33">
+    <tableColumn id="15" xr3:uid="{7DFA1C56-A8FE-42B5-B6C1-2058B28542ED}" name="风险造价" totalsRowFunction="custom" dataDxfId="34">
       <calculatedColumnFormula>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</calculatedColumnFormula>
       <totalsRowFormula>SUM(表7[风险造价])</totalsRowFormula>
@@ -4551,32 +4671,32 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B6" s="2">
-        <v>0.21560000000000001</v>
+        <v>0.121</v>
       </c>
       <c r="C6">
         <f>金价表[[#This Row],[当前金价1w]]/0.95</f>
-        <v>0.22694736842105265</v>
+        <v>0.12736842105263158</v>
       </c>
       <c r="D6" s="5">
-        <v>2400</v>
+        <v>9778</v>
       </c>
       <c r="E6">
         <f>金价表[[#This Row],[出售商品价格]]*金价表[[#This Row],[当前金价1w]]*0.95</f>
-        <v>491.56800000000004</v>
+        <v>1123.9811</v>
       </c>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
       <c r="I8" cm="1">
         <f t="array" ref="I8">555*金价表[税后金价]</f>
-        <v>125.95578947368422</v>
+        <v>70.689473684210526</v>
       </c>
       <c r="J8" cm="1">
         <f t="array" ref="J8">2888.8888*金价表[当前金价1w]</f>
-        <v>622.84442528000011</v>
+        <v>349.55554480000001</v>
       </c>
       <c r="K8" cm="1">
         <f t="array" ref="K8">2888.8888*金价表[当前金价1w]</f>
-        <v>622.84442528000011</v>
+        <v>349.55554480000001</v>
       </c>
     </row>
     <row r="12" spans="2:14" ht="28.5" x14ac:dyDescent="0.2">
@@ -4616,7 +4736,7 @@
       </c>
       <c r="L13" s="3" cm="1">
         <f t="array" ref="L13">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>53.10568421052632</v>
+        <v>29.804210526315789</v>
       </c>
       <c r="M13" s="3">
         <v>0</v>
@@ -4640,14 +4760,14 @@
       </c>
       <c r="L14" s="3" cm="1">
         <f t="array" ref="L14">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>126.0817452631579</v>
+        <v>70.760163157894723</v>
       </c>
       <c r="M14" s="3">
         <v>1</v>
       </c>
       <c r="N14" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>72.976061052631579</v>
+        <v>40.955952631578938</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
@@ -4664,14 +4784,14 @@
       </c>
       <c r="L15" s="3" cm="1">
         <f t="array" ref="L15">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>224.42571082105263</v>
+        <v>125.95320505263157</v>
       </c>
       <c r="M15" s="3">
         <v>2</v>
       </c>
       <c r="N15" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>85.660013305263163</v>
+        <v>48.074497263157895</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
@@ -4688,14 +4808,14 @@
       </c>
       <c r="L16" s="3" cm="1">
         <f t="array" ref="L16">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>337.89939503157893</v>
+        <v>189.63741557894735</v>
       </c>
       <c r="M16" s="3">
         <v>3</v>
       </c>
       <c r="N16" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>94.931236940350871</v>
+        <v>53.277735017543854</v>
       </c>
     </row>
     <row r="17" spans="8:20" x14ac:dyDescent="0.2">
@@ -4712,14 +4832,14 @@
       </c>
       <c r="L17" cm="1">
         <f t="array" ref="L17">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>385.8105263157895</v>
+        <v>216.52631578947367</v>
       </c>
       <c r="M17">
         <v>4</v>
       </c>
       <c r="N17" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>83.176210526315799</v>
+        <v>46.680526315789471</v>
       </c>
     </row>
     <row r="18" spans="8:20" x14ac:dyDescent="0.2">
@@ -4736,14 +4856,14 @@
       </c>
       <c r="L18" cm="1">
         <f t="array" ref="L18">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>680.84210526315792</v>
+        <v>382.10526315789474</v>
       </c>
       <c r="M18">
         <v>5</v>
       </c>
       <c r="N18" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>125.54728421052633</v>
+        <v>70.460210526315791</v>
       </c>
       <c r="Q18">
         <f>555.555+98</f>
@@ -4751,7 +4871,7 @@
       </c>
       <c r="R18" s="1" cm="1">
         <f t="array" ref="R18">Q18*金价表[当前金价1w]</f>
-        <v>140.90645799999999</v>
+        <v>79.080154999999991</v>
       </c>
     </row>
     <row r="19" spans="8:20" x14ac:dyDescent="0.2">
@@ -4768,14 +4888,14 @@
       </c>
       <c r="L19" cm="1">
         <f t="array" ref="L19">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>678.32044766315801</v>
+        <v>380.69004715789475</v>
       </c>
       <c r="M19">
         <v>6</v>
       </c>
       <c r="N19" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>104.20246057543862</v>
+        <v>58.480972771929828</v>
       </c>
     </row>
     <row r="20" spans="8:20" x14ac:dyDescent="0.2">
@@ -4792,19 +4912,19 @@
       </c>
       <c r="L20" cm="1">
         <f t="array" ref="L20">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1815.5789473684213</v>
+        <v>1018.9473684210526</v>
       </c>
       <c r="M20">
         <v>7</v>
       </c>
       <c r="N20" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$13)/表16[[#This Row],[提升]],0)</f>
-        <v>251.78189473684213</v>
+        <v>141.30616541353382</v>
       </c>
     </row>
     <row r="21" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H21" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I21" s="2">
         <v>2666</v>
@@ -4819,7 +4939,7 @@
       </c>
       <c r="L21" cm="1">
         <f t="array" ref="L21">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>605.04168421052634</v>
+        <v>339.56421052631578</v>
       </c>
       <c r="M21">
         <v>1</v>
@@ -4831,7 +4951,7 @@
     </row>
     <row r="22" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I22" s="2">
         <v>2888</v>
@@ -4846,19 +4966,19 @@
       </c>
       <c r="L22" cm="1">
         <f t="array" ref="L22">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>655.42400000000009</v>
+        <v>367.84</v>
       </c>
       <c r="M22">
         <v>1</v>
       </c>
       <c r="N22" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>50.382315789473751</v>
+        <v>28.275789473684199</v>
       </c>
     </row>
     <row r="23" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H23" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="I23" s="2">
         <v>7777</v>
@@ -4873,13 +4993,13 @@
       </c>
       <c r="L23" cm="1">
         <f t="array" ref="L23">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1764.9696842105263</v>
+        <v>990.54421052631574</v>
       </c>
       <c r="N23" s="3"/>
     </row>
     <row r="24" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H24" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2">
@@ -4892,19 +5012,19 @@
       </c>
       <c r="L24" cm="1">
         <f t="array" ref="L24">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>1143.3356055578947</v>
+        <v>641.66794189473683</v>
       </c>
       <c r="M24">
         <v>2</v>
       </c>
       <c r="N24" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>269.14696067368419</v>
+        <v>151.05186568421053</v>
       </c>
     </row>
     <row r="25" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H25" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -4921,7 +5041,7 @@
       </c>
       <c r="N25" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-201.68056140350879</v>
+        <v>-113.1880701754386</v>
       </c>
       <c r="Q25" t="s">
         <v>110</v>
@@ -4935,7 +5055,7 @@
     </row>
     <row r="26" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
@@ -4952,7 +5072,7 @@
       </c>
       <c r="N26" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-151.26042105263159</v>
+        <v>-84.891052631578944</v>
       </c>
       <c r="Q26">
         <v>200</v>
@@ -4967,7 +5087,7 @@
     </row>
     <row r="27" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H27" s="2" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
@@ -4984,7 +5104,7 @@
       </c>
       <c r="N27" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-121.00833684210527</v>
+        <v>-67.912842105263152</v>
       </c>
       <c r="R27" s="1">
         <f>SUM(Q26:S26)</f>
@@ -4992,12 +5112,12 @@
       </c>
       <c r="T27" cm="1">
         <f t="array" ref="T27">R27/金价表[税后金价]</f>
-        <v>1414.4248608534322</v>
+        <v>2520.2479338842977</v>
       </c>
     </row>
     <row r="28" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H28" s="2" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
@@ -5014,12 +5134,12 @@
       </c>
       <c r="N28" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-86.434526315789483</v>
+        <v>-48.509172932330827</v>
       </c>
     </row>
     <row r="29" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H29" s="2" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
@@ -5036,7 +5156,7 @@
       </c>
       <c r="N29" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-75.630210526315793</v>
+        <v>-42.445526315789472</v>
       </c>
       <c r="Q29" t="s">
         <v>108</v>
@@ -5051,7 +5171,7 @@
     </row>
     <row r="30" spans="8:20" x14ac:dyDescent="0.2">
       <c r="H30" s="2" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
@@ -5068,7 +5188,7 @@
       </c>
       <c r="N30" s="3">
         <f>IFERROR((表16[[#This Row],[等价rmb]]-$L$21)/表16[[#This Row],[提升]],0)</f>
-        <v>-67.226853801169597</v>
+        <v>-37.729356725146197</v>
       </c>
       <c r="Q30" t="s">
         <v>111</v>
@@ -5092,7 +5212,7 @@
       </c>
       <c r="L31" cm="1">
         <f t="array" ref="L31">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>53.559578947368422</v>
+        <v>30.058947368421052</v>
       </c>
     </row>
     <row r="32" spans="8:20" x14ac:dyDescent="0.2">
@@ -5109,7 +5229,7 @@
       </c>
       <c r="L32" cm="1">
         <f t="array" ref="L32">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>87.601684210526315</v>
+        <v>49.164210526315784</v>
       </c>
       <c r="R32">
         <f>2200/0.35</f>
@@ -5130,7 +5250,7 @@
       </c>
       <c r="L33" cm="1">
         <f t="array" ref="L33">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>25.872000000000003</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="34" spans="8:17" x14ac:dyDescent="0.2">
@@ -5147,7 +5267,7 @@
       </c>
       <c r="L34" cm="1">
         <f t="array" ref="L34">MIN(表16[[#This Row],[购买价格w]],表16[[#This Row],[制作价格]])*金价表[税后金价]</f>
-        <v>73.984842105263169</v>
+        <v>41.522105263157897</v>
       </c>
     </row>
     <row r="41" spans="8:17" x14ac:dyDescent="0.2">
@@ -5225,7 +5345,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
@@ -5667,7 +5787,7 @@
         <v>19</v>
       </c>
       <c r="J32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K32" t="s">
         <v>16</v>
@@ -6508,7 +6628,7 @@
         <v>55.567999999999998</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F49" s="2">
         <v>56</v>
@@ -6560,7 +6680,7 @@
         <v>60.441600000000001</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F50" s="2">
         <v>59</v>
@@ -6612,7 +6732,7 @@
         <v>65.52</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F51" s="2">
         <v>61</v>
@@ -6664,7 +6784,7 @@
         <v>70.971599999999995</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F52" s="2">
         <v>70</v>
@@ -6716,7 +6836,7 @@
         <v>74.860799999999998</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F53" s="2">
         <v>70</v>
@@ -6768,7 +6888,7 @@
         <v>78.963099999999997</v>
       </c>
       <c r="E54" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F54" s="2">
         <v>71</v>
@@ -6819,7 +6939,7 @@
         <v>83.290199999999999</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F55" s="2">
         <v>71</v>
@@ -6858,8 +6978,9 @@
 /10000</f>
         <v>28.725629999999999</v>
       </c>
-      <c r="S55" t="s">
-        <v>157</v>
+      <c r="S55">
+        <f>350*25</f>
+        <v>8750</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.2">
@@ -6874,7 +6995,7 @@
         <v>87.854500000000002</v>
       </c>
       <c r="E56" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F56" s="2">
         <v>73</v>
@@ -6925,7 +7046,7 @@
         <v>92.668899999999994</v>
       </c>
       <c r="E57" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F57" s="2">
         <v>21</v>
@@ -6976,7 +7097,7 @@
         <v>97.747100000000003</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F58" s="2">
         <v>73</v>
@@ -7027,7 +7148,7 @@
         <v>103.1036</v>
       </c>
       <c r="E59" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F59" s="2">
         <v>73</v>
@@ -7078,7 +7199,7 @@
         <v>108.75360000000001</v>
       </c>
       <c r="E60" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F60" s="2">
         <v>74</v>
@@ -7129,7 +7250,7 @@
         <v>114.7132</v>
       </c>
       <c r="E61" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F61" s="2">
         <v>74</v>
@@ -7180,7 +7301,7 @@
         <v>120.99939999999999</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F62" s="2">
         <v>74</v>
@@ -7232,7 +7353,7 @@
         <v>127.6301</v>
       </c>
       <c r="E63" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F63" s="2">
         <v>75</v>
@@ -7283,7 +7404,7 @@
         <v>134.6242</v>
       </c>
       <c r="E64" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F64" s="2">
         <v>75</v>
@@ -7335,7 +7456,7 @@
         <v>142.0016</v>
       </c>
       <c r="E65" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F65" s="2">
         <v>77</v>
@@ -7386,7 +7507,7 @@
         <v>149.78319999999999</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F66" s="2">
         <v>77</v>
@@ -7438,7 +7559,7 @@
         <v>157.9913</v>
       </c>
       <c r="E67" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F67" s="2">
         <v>80</v>
@@ -7452,7 +7573,7 @@
       <c r="I67" s="2">
         <v>2708984</v>
       </c>
-      <c r="J67" s="15">
+      <c r="J67" s="2">
         <f>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -7465,7 +7586,7 @@
       <c r="K67">
         <v>17.5</v>
       </c>
-      <c r="L67" s="16">
+      <c r="L67">
         <f>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -7489,10 +7610,10 @@
         <v>166.64920000000001</v>
       </c>
       <c r="E68" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
       <c r="F68" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G68" s="2"/>
       <c r="H68" s="2">
@@ -7501,7 +7622,7 @@
       <c r="I68" s="2">
         <v>0</v>
       </c>
-      <c r="J68" s="15">
+      <c r="J68" s="2">
         <f>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -7509,13 +7630,13 @@
  -表5[[#This Row],[开始]]
 )
 /10000</f>
-        <v>4172.4310999999998</v>
+        <v>2997.3789000000002</v>
       </c>
       <c r="K68">
-        <f>60*40*4</f>
-        <v>9600</v>
-      </c>
-      <c r="L68" s="16">
+        <f>60*38*3</f>
+        <v>6840</v>
+      </c>
+      <c r="L68">
         <f>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -7524,7 +7645,7 @@
  -表5[[#This Row],[开始]]
 )
 /10000</f>
-        <v>26.077694375</v>
+        <v>26.292797368421052</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -7539,7 +7660,7 @@
         <v>175.78149999999999</v>
       </c>
       <c r="E69" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="F69" s="2">
         <v>81</v>
@@ -7547,9 +7668,13 @@
       <c r="G69" s="2">
         <v>2042534</v>
       </c>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="15">
+      <c r="H69" s="2">
+        <v>82</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1036313</v>
+      </c>
+      <c r="J69" s="2">
         <f>(
  表5[[#This Row],[结束]]
  +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
@@ -7557,9 +7682,13 @@
  -表5[[#This Row],[开始]]
 )
 /10000</f>
-        <v>12703.7359</v>
-      </c>
-      <c r="L69" s="16" t="e">
+        <v>270.36079999999998</v>
+      </c>
+      <c r="K69">
+        <f>9.5*60</f>
+        <v>570</v>
+      </c>
+      <c r="L69">
         <f>60/表5[[#This Row],[时间min]]
 *(
  表5[[#This Row],[结束]]
@@ -7568,7 +7697,7 @@
  -表5[[#This Row],[开始]]
 )
 /10000</f>
-        <v>#DIV/0!</v>
+        <v>28.459031578947364</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -7582,6 +7711,45 @@
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>185.4143</v>
       </c>
+      <c r="E70" t="s">
+        <v>131</v>
+      </c>
+      <c r="F70" s="2">
+        <v>82</v>
+      </c>
+      <c r="G70" s="2">
+        <v>2568226</v>
+      </c>
+      <c r="H70" s="2">
+        <v>82</v>
+      </c>
+      <c r="I70" s="2">
+        <v>2677316</v>
+      </c>
+      <c r="J70" s="15">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>10.909000000000001</v>
+      </c>
+      <c r="K70">
+        <v>19</v>
+      </c>
+      <c r="L70" s="16">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>34.449473684210531</v>
+      </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71">
@@ -7594,6 +7762,45 @@
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>195.57499999999999</v>
       </c>
+      <c r="E71" t="s">
+        <v>131</v>
+      </c>
+      <c r="F71" s="2">
+        <v>83</v>
+      </c>
+      <c r="G71" s="2">
+        <v>3539025</v>
+      </c>
+      <c r="H71" s="2">
+        <v>83</v>
+      </c>
+      <c r="I71" s="2">
+        <v>3611699</v>
+      </c>
+      <c r="J71" s="15">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>7.2674000000000003</v>
+      </c>
+      <c r="K71">
+        <v>13</v>
+      </c>
+      <c r="L71" s="16">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>33.541846153846151</v>
+      </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72">
@@ -7605,6 +7812,44 @@
       <c r="C72">
         <f>经验表[[#This Row],[升级所需]]/10000</f>
         <v>206.29249999999999</v>
+      </c>
+      <c r="E72" t="s">
+        <v>176</v>
+      </c>
+      <c r="F72" s="2">
+        <v>85</v>
+      </c>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2">
+        <v>100</v>
+      </c>
+      <c r="I72" s="2">
+        <v>0</v>
+      </c>
+      <c r="J72" s="15">
+        <f>(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>10275.244699999999</v>
+      </c>
+      <c r="K72">
+        <f>60*350</f>
+        <v>21000</v>
+      </c>
+      <c r="L72" s="16">
+        <f>60/表5[[#This Row],[时间min]]
+*(
+ 表5[[#This Row],[结束]]
+ +SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[开始lv]])
+ -SUMIFS(经验表[升级所需],经验表[等级],"&gt;="&amp;表5[[#This Row],[结束lv]])
+ -表5[[#This Row],[开始]]
+)
+/10000</f>
+        <v>29.357841999999998</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -8019,7 +8264,7 @@
       </c>
       <c r="E4" cm="1">
         <f t="array" ref="E4">卷轴参数[[#This Row],[卷拍卖行价w]]*金价表[税后金价]</f>
-        <v>15.886315789473686</v>
+        <v>8.9157894736842103</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.2">
@@ -8030,7 +8275,7 @@
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -8046,7 +8291,7 @@
       </c>
       <c r="D7" cm="1">
         <f t="array" ref="D7">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>15.886315789473686</v>
+        <v>8.9157894736842103</v>
       </c>
       <c r="E7" t="str" cm="1">
         <f t="array" ref="E7">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -8063,7 +8308,7 @@
       </c>
       <c r="D8" cm="1">
         <f t="array" ref="D8">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>31.772631578947372</v>
+        <v>17.831578947368421</v>
       </c>
       <c r="E8" t="str" cm="1">
         <f t="array" ref="E8">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -8080,7 +8325,7 @@
       </c>
       <c r="D9" cm="1">
         <f t="array" ref="D9">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>47.65894736842106</v>
+        <v>26.747368421052631</v>
       </c>
       <c r="E9" t="str" cm="1">
         <f t="array" ref="E9">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -8097,7 +8342,7 @@
       </c>
       <c r="D10" cm="1">
         <f t="array" ref="D10">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>63.545263157894745</v>
+        <v>35.663157894736841</v>
       </c>
       <c r="E10" t="str" cm="1">
         <f t="array" ref="E10">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
@@ -8114,11 +8359,11 @@
       </c>
       <c r="D11" cm="1">
         <f t="array" ref="D11">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>79.431578947368436</v>
+        <v>44.578947368421055</v>
       </c>
       <c r="E11" cm="1">
         <f t="array" ref="E11">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>1021.4966428416715</v>
+        <v>573.28893220706038</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.2">
@@ -8131,11 +8376,11 @@
       </c>
       <c r="D12" cm="1">
         <f t="array" ref="D12">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>95.317894736842121</v>
+        <v>53.494736842105262</v>
       </c>
       <c r="E12" cm="1">
         <f t="array" ref="E12">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>408.59865713666903</v>
+        <v>229.3155728828244</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.2">
@@ -8148,11 +8393,11 @@
       </c>
       <c r="D13" cm="1">
         <f t="array" ref="D13">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>111.2042105263158</v>
+        <v>62.410526315789468</v>
       </c>
       <c r="E13" cm="1">
         <f t="array" ref="E13">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>264.83246295895214</v>
+        <v>148.63046390553436</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.2">
@@ -8165,11 +8410,11 @@
       </c>
       <c r="D14" cm="1">
         <f t="array" ref="D14">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>127.09052631578949</v>
+        <v>71.326315789473682</v>
       </c>
       <c r="E14" cm="1">
         <f t="array" ref="E14">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>213.92599850087379</v>
+        <v>120.06050936273527</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.2">
@@ -8182,11 +8427,11 @@
       </c>
       <c r="D15" cm="1">
         <f t="array" ref="D15">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>142.97684210526319</v>
+        <v>80.242105263157896</v>
       </c>
       <c r="E15" cm="1">
         <f t="array" ref="E15">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>194.94210741253286</v>
+        <v>109.40628477233986</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.2">
@@ -8199,11 +8444,11 @@
       </c>
       <c r="D16" cm="1">
         <f t="array" ref="D16">表1[[#This Row],[次数]]*卷轴参数[卷价值]</f>
-        <v>158.86315789473687</v>
+        <v>89.15789473684211</v>
       </c>
       <c r="E16" cm="1">
         <f t="array" ref="E16">IFERROR(1/表1[[#This Row],[几率]]*卷轴参数[卷价值]*表1[[#This Row],[次数]],"-")</f>
-        <v>190.53791798013705</v>
+        <v>106.93454580517894</v>
       </c>
     </row>
     <row r="28" spans="3:15" x14ac:dyDescent="0.2">
@@ -8265,12 +8510,12 @@
       </c>
       <c r="H29" cm="1">
         <f t="array" ref="H29">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>4.3120000000000003</v>
+        <v>2.42</v>
       </c>
       <c r="I29">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>8.6240000000000006</v>
+        <v>4.84</v>
       </c>
       <c r="J29" s="2">
         <v>6</v>
@@ -8284,16 +8529,16 @@
       </c>
       <c r="M29">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
-        <v>25.872</v>
+        <v>14.52</v>
       </c>
       <c r="N29">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
-        <v>129.36000000000001</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="O29">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
-        <v>1632.3028391167161</v>
+        <v>916.08832807570798</v>
       </c>
     </row>
     <row r="30" spans="3:15" x14ac:dyDescent="0.2">
@@ -8312,12 +8557,12 @@
       </c>
       <c r="H30" cm="1">
         <f t="array" ref="H30">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>31.091789473684212</v>
+        <v>17.449473684210524</v>
       </c>
       <c r="I30">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>25.909824561403511</v>
+        <v>14.541228070175437</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
@@ -8358,12 +8603,12 @@
       </c>
       <c r="H31" cm="1">
         <f t="array" ref="H31">表7[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>0.79431578947368431</v>
+        <v>0.44578947368421051</v>
       </c>
       <c r="I31">
         <f>表7[[#This Row],[rmb]]
 /(表7[[#This Row],[卷概率]]*表7[[#This Row],[敏捷]])</f>
-        <v>0.79431578947368431</v>
+        <v>0.44578947368421051</v>
       </c>
       <c r="J31" s="2">
         <v>4</v>
@@ -8378,16 +8623,16 @@
       </c>
       <c r="M31">
         <f>表7[[#This Row],[模拟数量]]*表7[[#This Row],[rmb]]</f>
-        <v>3.1772631578947372</v>
+        <v>1.7831578947368421</v>
       </c>
       <c r="N31">
         <f>表7[[#This Row],[总敏捷]]*表7[[#This Row],[每点敏捷价格]]</f>
-        <v>3.1772631578947372</v>
+        <v>1.7831578947368421</v>
       </c>
       <c r="O31">
         <f>表7[[#This Row],[成本造价]]
 /IFERROR((1 - _xlfn.BINOM.DIST(表7[[#This Row],[成功数量]]-1, 表7[[#This Row],[模拟数量]], 表7[[#This Row],[卷概率]], TRUE)),0)</f>
-        <v>3.1772631578947372</v>
+        <v>1.7831578947368421</v>
       </c>
     </row>
     <row r="32" spans="3:15" x14ac:dyDescent="0.2">
@@ -8402,11 +8647,11 @@
       </c>
       <c r="M32">
         <f>SUM(表7[成本造价])</f>
-        <v>29.049263157894735</v>
+        <v>16.303157894736842</v>
       </c>
       <c r="N32">
         <f>SUM(表7[总价格])</f>
-        <v>132.53726315789476</v>
+        <v>74.38315789473684</v>
       </c>
       <c r="O32" t="e">
         <f>SUM(表7[风险造价])</f>
@@ -8469,12 +8714,12 @@
       </c>
       <c r="H40" cm="1">
         <f t="array" ref="H40">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>4.3120000000000003</v>
+        <v>2.42</v>
       </c>
       <c r="I40">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>8.6240000000000006</v>
+        <v>4.84</v>
       </c>
       <c r="J40" s="2">
         <v>7</v>
@@ -8488,12 +8733,12 @@
       </c>
       <c r="M40">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
-        <v>30.184000000000001</v>
+        <v>16.939999999999998</v>
       </c>
       <c r="N40">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
-        <v>335.67522332288917</v>
+        <v>188.38915594651942</v>
       </c>
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.2">
@@ -8512,12 +8757,12 @@
       </c>
       <c r="H41" cm="1">
         <f t="array" ref="H41">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>31.091789473684212</v>
+        <v>17.449473684210524</v>
       </c>
       <c r="I41">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>25.909824561403511</v>
+        <v>14.541228070175437</v>
       </c>
       <c r="J41" s="2">
         <v>3</v>
@@ -8531,12 +8776,12 @@
       </c>
       <c r="M41">
         <f>表7_9[[#This Row],[模拟数量]]*表7_9[[#This Row],[rmb]]</f>
-        <v>93.275368421052633</v>
+        <v>52.348421052631572</v>
       </c>
       <c r="N41">
         <f>IFERROR(1/(1 - _xlfn.BINOM.DIST(表7_9[[#This Row],[成功数量]]-1, 表7_9[[#This Row],[模拟数量]], 表7_9[[#This Row],[卷概率]], TRUE)),0)
 *表7_9[[#This Row],[敏捷价格]]</f>
-        <v>119.95289148797924</v>
+        <v>67.320500324886297</v>
       </c>
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.2">
@@ -8553,12 +8798,12 @@
       </c>
       <c r="H42" cm="1">
         <f t="array" ref="H42">表7_9[[#This Row],[单价]]*金价表[税后金价]</f>
-        <v>0.79431578947368431</v>
+        <v>0.44578947368421051</v>
       </c>
       <c r="I42">
         <f>表7_9[[#This Row],[rmb]]
 /(表7_9[[#This Row],[卷概率]]*表7_9[[#This Row],[敏捷]])</f>
-        <v>0.79431578947368431</v>
+        <v>0.44578947368421051</v>
       </c>
       <c r="J42" s="2">
         <v>0</v>
@@ -8593,11 +8838,11 @@
       </c>
       <c r="M43">
         <f>SUM(表7_9[造价])</f>
-        <v>123.45936842105263</v>
+        <v>69.288421052631577</v>
       </c>
       <c r="N43">
         <f>SUM(表7_9[风险造价])</f>
-        <v>455.6281148108684</v>
+        <v>255.70965627140572</v>
       </c>
     </row>
   </sheetData>
@@ -8673,19 +8918,19 @@
         <v>83</v>
       </c>
       <c r="E8" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>130</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>67</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>71</v>
@@ -8774,16 +9019,16 @@
         <v>85</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>68</v>
@@ -8792,28 +9037,28 @@
         <v>38</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>84</v>
       </c>
       <c r="M25" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="N25" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="O25" s="11" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="P25" s="11" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>75</v>
@@ -8822,10 +9067,10 @@
         <v>74</v>
       </c>
       <c r="U25" s="11" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="V25" s="11" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="W25" s="3" t="s">
         <v>80</v>
@@ -8836,7 +9081,7 @@
     </row>
     <row r="26" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D26" s="8" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E26" s="2">
         <v>43</v>
@@ -8848,19 +9093,19 @@
         <v>0</v>
       </c>
       <c r="H26" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J26" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K26" s="10">
         <v>6</v>
       </c>
       <c r="L26" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M26" cm="1">
         <f t="array" ref="M26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -8868,7 +9113,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>943.16</v>
+        <v>998.15400000000011</v>
       </c>
       <c r="N26" cm="1">
         <f t="array" ref="N26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -8876,7 +9121,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>543.40160000000003</v>
+        <v>574.2345600000001</v>
       </c>
       <c r="O26" s="12" cm="1">
         <f t="array" ref="O26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -8885,7 +9130,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.4705882352941124E-2</v>
+        <v>1.449275362318847E-2</v>
       </c>
       <c r="P26" s="12" cm="1">
         <f t="array" ref="P26">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -8894,35 +9139,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460817E-2</v>
+        <v>1.24429697221069E-2</v>
       </c>
       <c r="Q26" cm="1">
         <f t="array" ref="Q26">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1810.5</v>
+        <v>1919.9250000000002</v>
       </c>
       <c r="R26" cm="1">
         <f t="array" ref="R26">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>905.25</v>
+        <v>959.96250000000009</v>
       </c>
       <c r="S26" cm="1">
         <f t="array" ref="S26">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3017.5</v>
+        <v>3199.875</v>
       </c>
       <c r="T26" cm="1">
         <f t="array" ref="T26">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1508.75</v>
+        <v>1599.9375</v>
       </c>
       <c r="U26" s="14" cm="1">
         <f t="array" ref="U26">常量表[双飞斩运气系数max]
@@ -8930,7 +9175,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4705882352941124E-2</v>
+        <v>1.449275362318847E-2</v>
       </c>
       <c r="V26" s="14" cm="1">
         <f t="array" ref="V26">常量表[双飞斩运气系数max]
@@ -8938,20 +9183,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W26" s="1" cm="1">
         <f t="array" ref="W26">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2505.75</v>
+        <v>2669.8875000000003</v>
       </c>
       <c r="X26" s="1" cm="1">
         <f t="array" ref="X26">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1105.875</v>
+        <v>1187.9437500000001</v>
       </c>
     </row>
     <row r="27" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D27" s="8" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E27" s="2">
         <v>43</v>
@@ -8963,19 +9208,19 @@
         <v>1</v>
       </c>
       <c r="H27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I27" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K27" s="10">
         <v>6</v>
       </c>
       <c r="L27" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M27" cm="1">
         <f t="array" ref="M27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -8983,7 +9228,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>957.03</v>
+        <v>1012.6200000000001</v>
       </c>
       <c r="N27" cm="1">
         <f t="array" ref="N27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -8991,7 +9236,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>551.39279999999997</v>
+        <v>582.55680000000007</v>
       </c>
       <c r="O27" s="12" cm="1">
         <f t="array" ref="O27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9000,7 +9245,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.449275362318847E-2</v>
+        <v>1.4285714285714235E-2</v>
       </c>
       <c r="P27" s="12" cm="1">
         <f t="array" ref="P27">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9009,35 +9254,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460817E-2</v>
+        <v>1.2442969722107122E-2</v>
       </c>
       <c r="Q27" cm="1">
         <f t="array" ref="Q27">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1837.125</v>
+        <v>1947.75</v>
       </c>
       <c r="R27" cm="1">
         <f t="array" ref="R27">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>918.5625</v>
+        <v>973.875</v>
       </c>
       <c r="S27" cm="1">
         <f t="array" ref="S27">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3061.875</v>
+        <v>3246.25</v>
       </c>
       <c r="T27" cm="1">
         <f t="array" ref="T27">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1530.9375</v>
+        <v>1623.125</v>
       </c>
       <c r="U27" s="14" cm="1">
         <f t="array" ref="U27">常量表[双飞斩运气系数max]
@@ -9045,7 +9290,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.449275362318847E-2</v>
+        <v>1.4285714285714235E-2</v>
       </c>
       <c r="V27" s="14" cm="1">
         <f t="array" ref="V27">常量表[双飞斩运气系数max]
@@ -9053,20 +9298,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W27" s="1" cm="1">
         <f t="array" ref="W27">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2545.6875</v>
+        <v>2711.625</v>
       </c>
       <c r="X27" s="1" cm="1">
         <f t="array" ref="X27">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1125.84375</v>
+        <v>1208.8125</v>
       </c>
     </row>
     <row r="28" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D28" s="8" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="E28" s="2">
         <v>43</v>
@@ -9078,19 +9323,19 @@
         <v>2</v>
       </c>
       <c r="H28" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I28" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K28" s="10">
         <v>6</v>
       </c>
       <c r="L28" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M28" cm="1">
         <f t="array" ref="M28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9098,7 +9343,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>970.9</v>
+        <v>1027.086</v>
       </c>
       <c r="N28" cm="1">
         <f t="array" ref="N28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9106,7 +9351,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>559.38400000000001</v>
+        <v>590.87904000000015</v>
       </c>
       <c r="O28" s="12" cm="1">
         <f t="array" ref="O28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9115,7 +9360,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.4285714285714235E-2</v>
+        <v>1.4084507042253724E-2</v>
       </c>
       <c r="P28" s="12" cm="1">
         <f t="array" ref="P28">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9124,35 +9369,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460817E-2</v>
+        <v>1.24429697221069E-2</v>
       </c>
       <c r="Q28" cm="1">
         <f t="array" ref="Q28">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1863.75</v>
+        <v>1975.5749999999998</v>
       </c>
       <c r="R28" cm="1">
         <f t="array" ref="R28">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>931.875</v>
+        <v>987.78749999999991</v>
       </c>
       <c r="S28" cm="1">
         <f t="array" ref="S28">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3106.25</v>
+        <v>3292.625</v>
       </c>
       <c r="T28" cm="1">
         <f t="array" ref="T28">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1553.125</v>
+        <v>1646.3125</v>
       </c>
       <c r="U28" s="14" cm="1">
         <f t="array" ref="U28">常量表[双飞斩运气系数max]
@@ -9160,7 +9405,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4285714285714235E-2</v>
+        <v>1.4084507042253502E-2</v>
       </c>
       <c r="V28" s="14" cm="1">
         <f t="array" ref="V28">常量表[双飞斩运气系数max]
@@ -9168,20 +9413,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W28" s="1" cm="1">
         <f t="array" ref="W28">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2585.625</v>
+        <v>2753.3625000000002</v>
       </c>
       <c r="X28" s="1" cm="1">
         <f t="array" ref="X28">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1145.8125</v>
+        <v>1229.6812500000001</v>
       </c>
     </row>
     <row r="29" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D29" s="8" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E29" s="2">
         <v>43</v>
@@ -9193,19 +9438,19 @@
         <v>3</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I29" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J29" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K29" s="10">
         <v>6</v>
       </c>
       <c r="L29" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M29" cm="1">
         <f t="array" ref="M29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9213,7 +9458,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>984.77</v>
+        <v>1041.5520000000001</v>
       </c>
       <c r="N29" cm="1">
         <f t="array" ref="N29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9221,7 +9466,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>567.37519999999995</v>
+        <v>599.20128000000011</v>
       </c>
       <c r="O29" s="12" cm="1">
         <f t="array" ref="O29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9230,7 +9475,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.388888888888884E-2</v>
       </c>
       <c r="P29" s="12" cm="1">
         <f t="array" ref="P29">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9239,35 +9484,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460595E-2</v>
+        <v>1.2442969722107122E-2</v>
       </c>
       <c r="Q29" cm="1">
         <f t="array" ref="Q29">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1890.375</v>
+        <v>2003.3999999999999</v>
       </c>
       <c r="R29" cm="1">
         <f t="array" ref="R29">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>945.1875</v>
+        <v>1001.6999999999999</v>
       </c>
       <c r="S29" cm="1">
         <f t="array" ref="S29">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3150.625</v>
+        <v>3339</v>
       </c>
       <c r="T29" cm="1">
         <f t="array" ref="T29">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1575.3125</v>
+        <v>1669.5</v>
       </c>
       <c r="U29" s="14" cm="1">
         <f t="array" ref="U29">常量表[双飞斩运气系数max]
@@ -9275,7 +9520,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.388888888888884E-2</v>
       </c>
       <c r="V29" s="14" cm="1">
         <f t="array" ref="V29">常量表[双飞斩运气系数max]
@@ -9283,20 +9528,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W29" s="1" cm="1">
         <f t="array" ref="W29">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2625.5625</v>
+        <v>2795.1</v>
       </c>
       <c r="X29" s="1" cm="1">
         <f t="array" ref="X29">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1165.78125</v>
+        <v>1250.55</v>
       </c>
     </row>
     <row r="30" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D30" s="8" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="E30" s="2">
         <v>43</v>
@@ -9308,19 +9553,19 @@
         <v>4</v>
       </c>
       <c r="H30" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J30" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K30" s="10">
         <v>6</v>
       </c>
       <c r="L30" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M30" cm="1">
         <f t="array" ref="M30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9328,7 +9573,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>998.64</v>
+        <v>1056.018</v>
       </c>
       <c r="N30" cm="1">
         <f t="array" ref="N30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9336,7 +9581,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>575.3664</v>
+        <v>607.52352000000019</v>
       </c>
       <c r="O30" s="12" cm="1">
         <f t="array" ref="O30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9345,7 +9590,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.388888888888884E-2</v>
+        <v>1.3698630136986356E-2</v>
       </c>
       <c r="P30" s="12" cm="1">
         <f t="array" ref="P30">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9354,35 +9599,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460817E-2</v>
+        <v>1.2442969722107122E-2</v>
       </c>
       <c r="Q30" cm="1">
         <f t="array" ref="Q30">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1917</v>
+        <v>2031.2250000000001</v>
       </c>
       <c r="R30" cm="1">
         <f t="array" ref="R30">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>958.5</v>
+        <v>1015.6125000000001</v>
       </c>
       <c r="S30" cm="1">
         <f t="array" ref="S30">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3195</v>
+        <v>3385.375</v>
       </c>
       <c r="T30" cm="1">
         <f t="array" ref="T30">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1597.5</v>
+        <v>1692.6875</v>
       </c>
       <c r="U30" s="14" cm="1">
         <f t="array" ref="U30">常量表[双飞斩运气系数max]
@@ -9390,7 +9635,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.388888888888884E-2</v>
+        <v>1.3698630136986356E-2</v>
       </c>
       <c r="V30" s="14" cm="1">
         <f t="array" ref="V30">常量表[双飞斩运气系数max]
@@ -9398,20 +9643,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W30" s="1" cm="1">
         <f t="array" ref="W30">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2665.5</v>
+        <v>2836.8375000000001</v>
       </c>
       <c r="X30" s="1" cm="1">
         <f t="array" ref="X30">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1185.75</v>
+        <v>1271.41875</v>
       </c>
     </row>
     <row r="31" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D31" s="8" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="E31" s="2">
         <v>43</v>
@@ -9423,19 +9668,19 @@
         <v>5</v>
       </c>
       <c r="H31" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I31" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J31" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K31" s="10">
         <v>6</v>
       </c>
       <c r="L31" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M31" cm="1">
         <f t="array" ref="M31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9443,7 +9688,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1012.51</v>
+        <v>1070.4840000000002</v>
       </c>
       <c r="N31" cm="1">
         <f t="array" ref="N31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9451,7 +9696,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>583.35760000000005</v>
+        <v>615.84576000000015</v>
       </c>
       <c r="O31" s="12" cm="1">
         <f t="array" ref="O31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9460,7 +9705,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.3698630136986356E-2</v>
+        <v>1.3513513513513375E-2</v>
       </c>
       <c r="P31" s="12" cm="1">
         <f t="array" ref="P31">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9469,35 +9714,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460817E-2</v>
+        <v>1.24429697221069E-2</v>
       </c>
       <c r="Q31" cm="1">
         <f t="array" ref="Q31">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1943.625</v>
+        <v>2059.0500000000002</v>
       </c>
       <c r="R31" cm="1">
         <f t="array" ref="R31">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>971.8125</v>
+        <v>1029.5250000000001</v>
       </c>
       <c r="S31" cm="1">
         <f t="array" ref="S31">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3239.375</v>
+        <v>3431.75</v>
       </c>
       <c r="T31" cm="1">
         <f t="array" ref="T31">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1619.6875</v>
+        <v>1715.875</v>
       </c>
       <c r="U31" s="14" cm="1">
         <f t="array" ref="U31">常量表[双飞斩运气系数max]
@@ -9505,7 +9750,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.3698630136986356E-2</v>
+        <v>1.3513513513513598E-2</v>
       </c>
       <c r="V31" s="14" cm="1">
         <f t="array" ref="V31">常量表[双飞斩运气系数max]
@@ -9513,20 +9758,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W31" s="1" cm="1">
         <f t="array" ref="W31">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2705.4375</v>
+        <v>2878.5750000000003</v>
       </c>
       <c r="X31" s="1" cm="1">
         <f t="array" ref="X31">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1205.71875</v>
+        <v>1292.2875000000001</v>
       </c>
     </row>
     <row r="32" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D32" s="8" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="E32" s="2">
         <v>43</v>
@@ -9538,19 +9783,19 @@
         <v>6</v>
       </c>
       <c r="H32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I32" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J32" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K32" s="10">
         <v>6</v>
       </c>
       <c r="L32" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M32" cm="1">
         <f t="array" ref="M32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9558,7 +9803,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1026.3800000000001</v>
+        <v>1084.95</v>
       </c>
       <c r="N32" cm="1">
         <f t="array" ref="N32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9566,7 +9811,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>591.34879999999998</v>
+        <v>624.16800000000012</v>
       </c>
       <c r="O32" s="12" cm="1">
         <f t="array" ref="O32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9575,7 +9820,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.3513513513513375E-2</v>
+        <v>1.3333333333333419E-2</v>
       </c>
       <c r="P32" s="12" cm="1">
         <f t="array" ref="P32">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9584,35 +9829,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460595E-2</v>
+        <v>1.24429697221069E-2</v>
       </c>
       <c r="Q32" cm="1">
         <f t="array" ref="Q32">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1970.25</v>
+        <v>2086.875</v>
       </c>
       <c r="R32" cm="1">
         <f t="array" ref="R32">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>985.125</v>
+        <v>1043.4375</v>
       </c>
       <c r="S32" cm="1">
         <f t="array" ref="S32">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3283.75</v>
+        <v>3478.125</v>
       </c>
       <c r="T32" cm="1">
         <f t="array" ref="T32">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1641.875</v>
+        <v>1739.0625</v>
       </c>
       <c r="U32" s="14" cm="1">
         <f t="array" ref="U32">常量表[双飞斩运气系数max]
@@ -9620,7 +9865,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.3513513513513598E-2</v>
+        <v>1.3333333333333419E-2</v>
       </c>
       <c r="V32" s="14" cm="1">
         <f t="array" ref="V32">常量表[双飞斩运气系数max]
@@ -9628,20 +9873,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W32" s="1" cm="1">
         <f t="array" ref="W32">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2745.375</v>
+        <v>2920.3125</v>
       </c>
       <c r="X32" s="1" cm="1">
         <f t="array" ref="X32">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1225.6875</v>
+        <v>1313.15625</v>
       </c>
     </row>
     <row r="33" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D33" s="8" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2">
         <v>43</v>
@@ -9653,19 +9898,19 @@
         <v>7</v>
       </c>
       <c r="H33" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I33" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J33" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K33" s="10">
         <v>6</v>
       </c>
       <c r="L33" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M33" s="1" cm="1">
         <f t="array" ref="M33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9673,7 +9918,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1040.25</v>
+        <v>1099.4160000000002</v>
       </c>
       <c r="N33" s="1" cm="1">
         <f t="array" ref="N33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9681,7 +9926,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>599.34</v>
+        <v>632.49024000000009</v>
       </c>
       <c r="O33" s="13" cm="1">
         <f t="array" ref="O33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9690,7 +9935,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.3333333333333197E-2</v>
+        <v>1.3157894736842035E-2</v>
       </c>
       <c r="P33" s="13" cm="1">
         <f t="array" ref="P33">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9699,35 +9944,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460817E-2</v>
+        <v>1.24429697221069E-2</v>
       </c>
       <c r="Q33" s="1" cm="1">
         <f t="array" ref="Q33">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1996.875</v>
+        <v>2114.6999999999998</v>
       </c>
       <c r="R33" s="1" cm="1">
         <f t="array" ref="R33">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>998.4375</v>
+        <v>1057.3499999999999</v>
       </c>
       <c r="S33" s="1" cm="1">
         <f t="array" ref="S33">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3328.125</v>
+        <v>3524.5</v>
       </c>
       <c r="T33" s="1" cm="1">
         <f t="array" ref="T33">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1664.0625</v>
+        <v>1762.25</v>
       </c>
       <c r="U33" s="14" cm="1">
         <f t="array" ref="U33">常量表[双飞斩运气系数max]
@@ -9735,7 +9980,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.3333333333333419E-2</v>
+        <v>1.3157894736842035E-2</v>
       </c>
       <c r="V33" s="14" cm="1">
         <f t="array" ref="V33">常量表[双飞斩运气系数max]
@@ -9743,20 +9988,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W33" s="1" cm="1">
         <f t="array" ref="W33">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2785.3125</v>
+        <v>2962.05</v>
       </c>
       <c r="X33" s="1" cm="1">
         <f t="array" ref="X33">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1245.65625</v>
+        <v>1334.0250000000001</v>
       </c>
     </row>
     <row r="34" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D34" s="8" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="E34" s="2">
         <v>43</v>
@@ -9768,19 +10013,19 @@
         <v>8</v>
       </c>
       <c r="H34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I34" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J34" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K34" s="10">
         <v>6</v>
       </c>
       <c r="L34" s="10">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M34" cm="1">
         <f t="array" ref="M34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9788,7 +10033,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1054.1199999999999</v>
+        <v>1113.8820000000001</v>
       </c>
       <c r="N34" cm="1">
         <f t="array" ref="N34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9796,7 +10041,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>607.33120000000008</v>
+        <v>640.81248000000016</v>
       </c>
       <c r="O34" s="12" cm="1">
         <f t="array" ref="O34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9805,7 +10050,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.3157894736842257E-2</v>
+        <v>1.2987012987013102E-2</v>
       </c>
       <c r="P34" s="12" cm="1">
         <f t="array" ref="P34">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9814,35 +10059,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2977649603460817E-2</v>
+        <v>1.2442969722107122E-2</v>
       </c>
       <c r="Q34" cm="1">
         <f t="array" ref="Q34">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>2023.5</v>
+        <v>2142.5249999999996</v>
       </c>
       <c r="R34" cm="1">
         <f t="array" ref="R34">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1011.75</v>
+        <v>1071.2624999999998</v>
       </c>
       <c r="S34" s="1" cm="1">
         <f t="array" ref="S34">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3372.5</v>
+        <v>3570.875</v>
       </c>
       <c r="T34" s="1" cm="1">
         <f t="array" ref="T34">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1686.25</v>
+        <v>1785.4375</v>
       </c>
       <c r="U34" s="14" cm="1">
         <f t="array" ref="U34">常量表[双飞斩运气系数max]
@@ -9850,7 +10095,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.3157894736842035E-2</v>
+        <v>1.298701298701288E-2</v>
       </c>
       <c r="V34" s="14" cm="1">
         <f t="array" ref="V34">常量表[双飞斩运气系数max]
@@ -9858,20 +10103,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.4084507042253502E-2</v>
+        <v>1.3477088948786964E-2</v>
       </c>
       <c r="W34" s="1" cm="1">
         <f t="array" ref="W34">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2825.25</v>
+        <v>3003.7874999999999</v>
       </c>
       <c r="X34" s="1" cm="1">
         <f t="array" ref="X34">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1265.625</v>
+        <v>1354.89375</v>
       </c>
     </row>
     <row r="35" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D35" s="8" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="E35" s="2">
         <v>43</v>
@@ -9883,19 +10128,20 @@
         <v>7</v>
       </c>
       <c r="H35" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I35" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J35" s="10">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K35" s="10">
         <v>6</v>
       </c>
       <c r="L35" s="10">
-        <v>360</v>
+        <f>L34+6</f>
+        <v>377</v>
       </c>
       <c r="M35" cm="1">
         <f t="array" ref="M35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9903,7 +10149,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1053.75</v>
+        <v>1115.8319999999999</v>
       </c>
       <c r="N35" cm="1">
         <f t="array" ref="N35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9911,7 +10157,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>606.63</v>
+        <v>641.35488000000009</v>
       </c>
       <c r="O35" s="12" cm="1">
         <f t="array" ref="O35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -9920,7 +10166,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.3333333333333197E-2</v>
+        <v>1.3157894736842257E-2</v>
       </c>
       <c r="P35" s="12" cm="1">
         <f t="array" ref="P35">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -9929,35 +10175,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2811387900355964E-2</v>
+        <v>1.2259910093992632E-2</v>
       </c>
       <c r="Q35" cm="1">
         <f t="array" ref="Q35">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>2025</v>
+        <v>2148.8999999999996</v>
       </c>
       <c r="R35" cm="1">
         <f t="array" ref="R35">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1012.5</v>
+        <v>1074.4499999999998</v>
       </c>
       <c r="S35" s="1" cm="1">
         <f t="array" ref="S35">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3375</v>
+        <v>3581.5</v>
       </c>
       <c r="T35" s="1" cm="1">
         <f t="array" ref="T35">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1687.5</v>
+        <v>1790.75</v>
       </c>
       <c r="U35" s="14" cm="1">
         <f t="array" ref="U35">常量表[双飞斩运气系数max]
@@ -9965,7 +10211,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.3333333333333419E-2</v>
+        <v>1.3157894736842035E-2</v>
       </c>
       <c r="V35" s="14" cm="1">
         <f t="array" ref="V35">常量表[双飞斩运气系数max]
@@ -9973,20 +10219,20 @@
 *(表15[[#This Row],[运气]]+5)/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.388888888888884E-2</v>
+        <v>1.3262599469495928E-2</v>
       </c>
       <c r="W35" s="1" cm="1">
         <f t="array" ref="W35">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2827.5</v>
+        <v>3013.35</v>
       </c>
       <c r="X35" s="1" cm="1">
         <f t="array" ref="X35">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1266.75</v>
+        <v>1359.675</v>
       </c>
     </row>
     <row r="36" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D36" s="8" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="E36" s="2">
         <v>70</v>
@@ -9996,7 +10242,7 @@
         <v>7</v>
       </c>
       <c r="H36" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I36" s="10">
         <v>6</v>
@@ -10016,7 +10262,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1082.932</v>
+        <v>1096.6400000000001</v>
       </c>
       <c r="N36" cm="1">
         <f t="array" ref="N36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -10024,7 +10270,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>621.12327999999991</v>
+        <v>628.98559999999998</v>
       </c>
       <c r="O36" s="12" cm="1">
         <f t="array" ref="O36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -10033,7 +10279,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.2658227848101333E-2</v>
+        <v>1.2499999999999956E-2</v>
       </c>
       <c r="P36" s="12" cm="1">
         <f t="array" ref="P36">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -10049,28 +10295,28 @@
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>2091.5249999999996</v>
+        <v>2118</v>
       </c>
       <c r="R36" cm="1">
         <f t="array" ref="R36">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1045.7624999999998</v>
+        <v>1059</v>
       </c>
       <c r="S36" cm="1">
         <f t="array" ref="S36">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3485.875</v>
+        <v>3530</v>
       </c>
       <c r="T36" cm="1">
         <f t="array" ref="T36">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1742.9375</v>
+        <v>1765</v>
       </c>
       <c r="U36" s="14" cm="1">
         <f t="array" ref="U36">常量表[双飞斩运气系数max]
@@ -10078,7 +10324,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.2658227848101333E-2</v>
+        <v>1.2499999999999956E-2</v>
       </c>
       <c r="V36" s="14" cm="1">
         <f t="array" ref="V36">常量表[双飞斩运气系数max]
@@ -10090,16 +10336,16 @@
       </c>
       <c r="W36" s="1" cm="1">
         <f t="array" ref="W36">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2927.2874999999999</v>
+        <v>2967</v>
       </c>
       <c r="X36" s="1" cm="1">
         <f t="array" ref="X36">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1316.64375</v>
+        <v>1336.5</v>
       </c>
     </row>
     <row r="37" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D37" s="8" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="E37" s="2">
         <v>83</v>
@@ -10109,7 +10355,7 @@
         <v>7</v>
       </c>
       <c r="H37" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I37" s="10">
         <v>50</v>
@@ -10130,7 +10376,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1131.9680000000001</v>
+        <v>1144.2720000000002</v>
       </c>
       <c r="N37" cm="1">
         <f t="array" ref="N37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -10138,7 +10384,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>676.43552000000011</v>
+        <v>683.78808000000004</v>
       </c>
       <c r="O37" s="12" cm="1">
         <f t="array" ref="O37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -10147,7 +10393,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.0869565217391353E-2</v>
+        <v>1.0752688172042779E-2</v>
       </c>
       <c r="P37" s="12" cm="1">
         <f t="array" ref="P37">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -10156,35 +10402,35 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.4629388816644884E-2</v>
+        <v>1.4629388816645106E-2</v>
       </c>
       <c r="Q37" cm="1">
         <f t="array" ref="Q37">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>2063.1000000000004</v>
+        <v>2085.5249999999996</v>
       </c>
       <c r="R37" cm="1">
         <f t="array" ref="R37">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1031.5500000000002</v>
+        <v>1042.7624999999998</v>
       </c>
       <c r="S37" cm="1">
         <f t="array" ref="S37">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3438.5</v>
+        <v>3475.875</v>
       </c>
       <c r="T37" cm="1">
         <f t="array" ref="T37">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1719.25</v>
+        <v>1737.9375</v>
       </c>
       <c r="U37" s="14" cm="1">
         <f t="array" ref="U37">常量表[双飞斩运气系数max]
@@ -10192,7 +10438,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.0869565217391353E-2</v>
+        <v>1.0752688172043001E-2</v>
       </c>
       <c r="V37" s="14" cm="1">
         <f t="array" ref="V37">常量表[双飞斩运气系数max]
@@ -10204,16 +10450,16 @@
       </c>
       <c r="W37" s="1" cm="1">
         <f t="array" ref="W37">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2884.65</v>
+        <v>2918.2874999999999</v>
       </c>
       <c r="X37" s="1" cm="1">
         <f t="array" ref="X37">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1295.325</v>
+        <v>1312.14375</v>
       </c>
     </row>
     <row r="38" spans="4:24" x14ac:dyDescent="0.2">
       <c r="D38" s="8" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="E38" s="2">
         <v>88</v>
@@ -10223,7 +10469,7 @@
         <v>7</v>
       </c>
       <c r="H38" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I38" s="10">
         <v>55</v>
@@ -10243,7 +10489,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>1165.7459999999999</v>
+        <v>1177.7639999999999</v>
       </c>
       <c r="N38" cm="1">
         <f t="array" ref="N38">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -10251,7 +10497,7 @@
  常量表[面板主属性系数]*表15[[#This Row],[运气]]*常量表[熟练度系数]
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100</f>
-        <v>703.12584000000004</v>
+        <v>710.37455999999986</v>
       </c>
       <c r="O38" s="12" cm="1">
         <f t="array" ref="O38">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]],1)
@@ -10260,7 +10506,7 @@
  +常量表[面板副属性系数]*SUM(表15[[#This Row],[力量]],表15[[#This Row],[敏捷]])
 )/100
 /表15[[#This Row],[面板max]]-1</f>
-        <v>1.0309278350515427E-2</v>
+        <v>1.0204081632653184E-2</v>
       </c>
       <c r="P38" s="12" cm="1">
         <f t="array" ref="P38">SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
@@ -10276,28 +10522,28 @@
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>2095.1999999999998</v>
+        <v>2116.8000000000002</v>
       </c>
       <c r="R38" cm="1">
         <f t="array" ref="R38">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *常量表[技能倍率]</f>
-        <v>1047.5999999999999</v>
+        <v>1058.4000000000001</v>
       </c>
       <c r="S38" cm="1">
         <f t="array" ref="S38">常量表[双飞斩运气系数max]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>3492</v>
+        <v>3528</v>
       </c>
       <c r="T38" cm="1">
         <f t="array" ref="T38">常量表[双飞斩运气系数min]
 *SUM(表15[[#This Row],[武器攻击]],表15[[#This Row],[飞镖攻击]],表15[[#This Row],[手套攻击]],表15[[#This Row],[Link攻击]])
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])</f>
-        <v>1746</v>
+        <v>1764</v>
       </c>
       <c r="U38" s="14" cm="1">
         <f t="array" ref="U38">常量表[双飞斩运气系数max]
@@ -10305,7 +10551,7 @@
 *表15[[#This Row],[运气]]/100
 *(常量表[技能倍率]+常量表[暴击倍率])
 /表15[[#This Row],[暴击伤害max]]-1</f>
-        <v>1.0309278350515427E-2</v>
+        <v>1.0204081632652962E-2</v>
       </c>
       <c r="V38" s="14" cm="1">
         <f t="array" ref="V38">常量表[双飞斩运气系数max]
@@ -10317,11 +10563,11 @@
       </c>
       <c r="W38" s="1" cm="1">
         <f t="array" ref="W38">表15[[#This Row],[暴击伤害max]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[max系数]</f>
-        <v>2932.8</v>
+        <v>2965.2000000000003</v>
       </c>
       <c r="X38" s="1" cm="1">
         <f t="array" ref="X38">表15[[#This Row],[暴击伤害min]]*(1+0.01*怪物参数[等级差])-怪物参数[怪物防御]*怪物参数[min系数]</f>
-        <v>1319.4</v>
+        <v>1335.6000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -10338,79 +10584,892 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCFD6DD7-7869-4DDF-922E-73E264CA43BC}">
-  <dimension ref="B4:D9"/>
+  <dimension ref="C9:I70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="13.75" customWidth="1"/>
     <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="21.375" customWidth="1"/>
+    <col min="9" max="9" width="21.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C4" t="s">
-        <v>131</v>
-      </c>
-      <c r="D4" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C5" t="s">
-        <v>134</v>
-      </c>
-      <c r="D5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B7" t="s">
-        <v>137</v>
-      </c>
-      <c r="C7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B8" t="s">
-        <v>137</v>
-      </c>
-      <c r="C8" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B9" t="s">
-        <v>114</v>
-      </c>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C9" t="s">
-        <v>139</v>
+        <v>177</v>
+      </c>
+      <c r="D9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" t="s">
+        <v>179</v>
+      </c>
+      <c r="I9" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C10" t="s">
+        <v>178</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星12</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C11" t="s">
+        <v>181</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星49</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C12" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星54</v>
+      </c>
+    </row>
+    <row r="13" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D13">
+        <v>43</v>
+      </c>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星53</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14">
+        <v>13</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+      <c r="I14" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星52</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C15" t="s">
+        <v>185</v>
+      </c>
+      <c r="D15">
+        <v>34</v>
+      </c>
+      <c r="H15">
+        <v>6</v>
+      </c>
+      <c r="I15" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星48</v>
+      </c>
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C16" t="s">
+        <v>186</v>
+      </c>
+      <c r="D16">
+        <v>35</v>
+      </c>
+      <c r="H16">
+        <v>7</v>
+      </c>
+      <c r="I16" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D17">
+        <v>40</v>
+      </c>
+      <c r="H17">
+        <v>8</v>
+      </c>
+      <c r="I17" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星56</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C18" t="s">
+        <v>188</v>
+      </c>
+      <c r="D18">
+        <v>28</v>
+      </c>
+      <c r="H18">
+        <v>9</v>
+      </c>
+      <c r="I18" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星45</v>
+      </c>
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C19" t="s">
+        <v>189</v>
+      </c>
+      <c r="H19">
+        <v>10</v>
+      </c>
+      <c r="I19" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星47</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D20">
+        <v>19</v>
+      </c>
+      <c r="H20">
+        <v>11</v>
+      </c>
+      <c r="I20" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星51</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21">
+        <v>31</v>
+      </c>
+      <c r="H21">
+        <v>12</v>
+      </c>
+      <c r="I21" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星50</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>13</v>
+      </c>
+      <c r="I22" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C23" t="s">
+        <v>193</v>
+      </c>
+      <c r="D23">
+        <v>18</v>
+      </c>
+      <c r="H23">
+        <v>14</v>
+      </c>
+      <c r="I23" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星23</v>
+      </c>
+    </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C24" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24">
+        <v>20</v>
+      </c>
+      <c r="H24">
+        <v>15</v>
+      </c>
+      <c r="I24" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星43</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25">
+        <v>32</v>
+      </c>
+      <c r="H25">
+        <v>16</v>
+      </c>
+      <c r="I25" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星46</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C26" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26">
+        <v>23</v>
+      </c>
+      <c r="H26">
+        <v>17</v>
+      </c>
+      <c r="I26" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C27" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27">
+        <v>21</v>
+      </c>
+      <c r="H27">
+        <v>18</v>
+      </c>
+      <c r="I27" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星13</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C28" t="s">
+        <v>198</v>
+      </c>
+      <c r="D28">
+        <v>22</v>
+      </c>
+      <c r="H28">
+        <v>19</v>
+      </c>
+      <c r="I28" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星10</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C29" t="s">
+        <v>199</v>
+      </c>
+      <c r="D29">
+        <v>24</v>
+      </c>
+      <c r="H29">
+        <v>20</v>
+      </c>
+      <c r="I29" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星14</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C30" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30">
+        <v>38</v>
+      </c>
+      <c r="H30">
+        <v>21</v>
+      </c>
+      <c r="I30" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星17</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C31" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31">
+        <v>26</v>
+      </c>
+      <c r="H31">
+        <v>22</v>
+      </c>
+      <c r="I31" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星18</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C32" t="s">
+        <v>202</v>
+      </c>
+      <c r="H32">
+        <v>23</v>
+      </c>
+      <c r="I32" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星16</v>
+      </c>
+    </row>
+    <row r="33" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C33" t="s">
+        <v>203</v>
+      </c>
+      <c r="D33">
+        <v>14</v>
+      </c>
+      <c r="H33">
+        <v>24</v>
+      </c>
+      <c r="I33" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星19</v>
+      </c>
+    </row>
+    <row r="34" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C34" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34">
+        <v>27</v>
+      </c>
+      <c r="H34">
+        <v>25</v>
+      </c>
+      <c r="I34" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C35" t="s">
+        <v>205</v>
+      </c>
+      <c r="H35">
+        <v>26</v>
+      </c>
+      <c r="I35" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星21</v>
+      </c>
+    </row>
+    <row r="36" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C36" t="s">
+        <v>206</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="H36">
+        <v>27</v>
+      </c>
+      <c r="I36" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星24</v>
+      </c>
+    </row>
+    <row r="37" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C37" t="s">
+        <v>207</v>
+      </c>
+      <c r="H37">
+        <v>28</v>
+      </c>
+      <c r="I37" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星8</v>
+      </c>
+    </row>
+    <row r="38" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C38" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38">
+        <v>39</v>
+      </c>
+      <c r="H38">
+        <v>29</v>
+      </c>
+      <c r="I38" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星55</v>
+      </c>
+    </row>
+    <row r="39" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C39" t="s">
+        <v>209</v>
+      </c>
+      <c r="D39">
+        <v>42</v>
+      </c>
+      <c r="H39">
+        <v>30</v>
+      </c>
+      <c r="I39" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星26</v>
+      </c>
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C40" t="s">
+        <v>210</v>
+      </c>
+      <c r="H40">
+        <v>31</v>
+      </c>
+      <c r="I40" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星11</v>
+      </c>
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C41" t="s">
+        <v>211</v>
+      </c>
+      <c r="H41">
+        <v>32</v>
+      </c>
+      <c r="I41" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星15</v>
+      </c>
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C42" t="s">
+        <v>212</v>
+      </c>
+      <c r="H42">
+        <v>33</v>
+      </c>
+      <c r="I42" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星2</v>
+      </c>
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C43" t="s">
+        <v>213</v>
+      </c>
+      <c r="H43">
+        <v>34</v>
+      </c>
+      <c r="I43" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星5</v>
+      </c>
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C44" t="s">
+        <v>214</v>
+      </c>
+      <c r="H44">
+        <v>35</v>
+      </c>
+      <c r="I44" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星6</v>
+      </c>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C45" t="s">
+        <v>215</v>
+      </c>
+      <c r="H45">
+        <v>36</v>
+      </c>
+      <c r="I45" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C46" t="s">
+        <v>216</v>
+      </c>
+      <c r="H46">
+        <v>37</v>
+      </c>
+      <c r="I46" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星58</v>
+      </c>
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C47" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47">
+        <v>38</v>
+      </c>
+      <c r="I47" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星20</v>
+      </c>
+    </row>
+    <row r="48" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C48" t="s">
+        <v>218</v>
+      </c>
+      <c r="H48">
+        <v>39</v>
+      </c>
+      <c r="I48" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星28</v>
+      </c>
+    </row>
+    <row r="49" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C49" t="s">
+        <v>219</v>
+      </c>
+      <c r="H49">
+        <v>40</v>
+      </c>
+      <c r="I49" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星7</v>
+      </c>
+    </row>
+    <row r="50" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C50" t="s">
+        <v>220</v>
+      </c>
+      <c r="H50">
+        <v>41</v>
+      </c>
+      <c r="I50" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星59</v>
+      </c>
+    </row>
+    <row r="51" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C51" t="s">
+        <v>221</v>
+      </c>
+      <c r="D51">
+        <v>23</v>
+      </c>
+      <c r="H51">
+        <v>42</v>
+      </c>
+      <c r="I51" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星29</v>
+      </c>
+    </row>
+    <row r="52" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C52" t="s">
+        <v>222</v>
+      </c>
+      <c r="D52">
+        <v>47</v>
+      </c>
+      <c r="H52">
+        <v>43</v>
+      </c>
+      <c r="I52" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C53" t="s">
+        <v>223</v>
+      </c>
+      <c r="D53">
+        <v>15</v>
+      </c>
+      <c r="H53">
+        <v>44</v>
+      </c>
+      <c r="I53" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星60</v>
+      </c>
+    </row>
+    <row r="54" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C54" t="s">
+        <v>224</v>
+      </c>
+      <c r="D54">
+        <v>45</v>
+      </c>
+      <c r="H54">
+        <v>45</v>
+      </c>
+      <c r="I54" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星44</v>
+      </c>
+    </row>
+    <row r="55" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C55" t="s">
+        <v>225</v>
+      </c>
+      <c r="D55">
+        <v>9</v>
+      </c>
+      <c r="H55">
+        <v>46</v>
+      </c>
+      <c r="I55" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星57</v>
+      </c>
+    </row>
+    <row r="56" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C56" t="s">
+        <v>226</v>
+      </c>
+      <c r="D56">
+        <v>16</v>
+      </c>
+      <c r="H56">
+        <v>47</v>
+      </c>
+      <c r="I56" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v>蝙蝠魔克星42</v>
+      </c>
+    </row>
+    <row r="57" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C57" t="s">
+        <v>227</v>
+      </c>
+      <c r="D57">
+        <v>10</v>
+      </c>
+      <c r="H57">
+        <v>48</v>
+      </c>
+      <c r="I57" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C58" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58">
+        <v>6</v>
+      </c>
+      <c r="H58">
+        <v>49</v>
+      </c>
+      <c r="I58" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C59" t="s">
+        <v>229</v>
+      </c>
+      <c r="D59">
+        <v>2</v>
+      </c>
+      <c r="H59">
+        <v>50</v>
+      </c>
+      <c r="I59" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C60" t="s">
+        <v>230</v>
+      </c>
+      <c r="D60">
+        <v>12</v>
+      </c>
+      <c r="H60">
+        <v>51</v>
+      </c>
+      <c r="I60" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C61" t="s">
+        <v>231</v>
+      </c>
+      <c r="D61">
+        <v>11</v>
+      </c>
+      <c r="H61">
+        <v>52</v>
+      </c>
+      <c r="I61" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C62" t="s">
+        <v>232</v>
+      </c>
+      <c r="D62">
+        <v>5</v>
+      </c>
+      <c r="H62">
+        <v>53</v>
+      </c>
+      <c r="I62" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C63" t="s">
+        <v>233</v>
+      </c>
+      <c r="D63">
+        <v>4</v>
+      </c>
+      <c r="H63">
+        <v>54</v>
+      </c>
+      <c r="I63" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C64" t="s">
+        <v>234</v>
+      </c>
+      <c r="D64">
+        <v>3</v>
+      </c>
+      <c r="H64">
+        <v>55</v>
+      </c>
+      <c r="I64" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C65" t="s">
+        <v>235</v>
+      </c>
+      <c r="D65">
+        <v>29</v>
+      </c>
+      <c r="H65">
+        <v>56</v>
+      </c>
+      <c r="I65" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C66" t="s">
+        <v>236</v>
+      </c>
+      <c r="D66">
+        <v>8</v>
+      </c>
+      <c r="H66">
+        <v>57</v>
+      </c>
+      <c r="I66" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C67" t="s">
+        <v>237</v>
+      </c>
+      <c r="D67">
+        <v>46</v>
+      </c>
+      <c r="H67">
+        <v>58</v>
+      </c>
+      <c r="I67" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C68" t="s">
+        <v>238</v>
+      </c>
+      <c r="D68">
+        <v>37</v>
+      </c>
+      <c r="H68">
+        <v>59</v>
+      </c>
+      <c r="I68" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C69" t="s">
+        <v>239</v>
+      </c>
+      <c r="D69">
+        <v>41</v>
+      </c>
+      <c r="H69">
+        <v>60</v>
+      </c>
+      <c r="I69" t="str">
+        <f>_xlfn.XLOOKUP(表12[[#This Row],[频道]],表11[频道],表11[ID],"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="3:9" x14ac:dyDescent="0.2">
+      <c r="C70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D70">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
+  <tableParts count="2">
     <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -10425,7 +11484,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="7:15" x14ac:dyDescent="0.2">
@@ -10433,7 +11492,7 @@
         <v>2</v>
       </c>
       <c r="H105" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106" spans="7:15" x14ac:dyDescent="0.2">
@@ -10441,7 +11500,7 @@
         <v>3</v>
       </c>
       <c r="H106" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="107" spans="7:15" x14ac:dyDescent="0.2">
@@ -10449,7 +11508,7 @@
         <v>31</v>
       </c>
       <c r="O107" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="108" spans="7:15" x14ac:dyDescent="0.2">
@@ -10457,7 +11516,7 @@
         <v>32</v>
       </c>
       <c r="O108" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="109" spans="7:15" x14ac:dyDescent="0.2">
@@ -10465,13 +11524,13 @@
         <v>19</v>
       </c>
       <c r="H109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="N109">
         <v>33</v>
       </c>
       <c r="O109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="110" spans="7:15" x14ac:dyDescent="0.2">
@@ -10479,13 +11538,13 @@
         <v>23</v>
       </c>
       <c r="H110" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N110">
         <v>36</v>
       </c>
       <c r="O110" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="7:15" x14ac:dyDescent="0.2">
@@ -10493,7 +11552,7 @@
         <v>39</v>
       </c>
       <c r="O111" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="112" spans="7:15" x14ac:dyDescent="0.2">
@@ -10501,7 +11560,7 @@
         <v>41</v>
       </c>
       <c r="O112" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="113" spans="14:15" x14ac:dyDescent="0.2">
@@ -10509,7 +11568,7 @@
         <v>54</v>
       </c>
       <c r="O113" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
